--- a/assets/Housing Study/Job Market/Telluride Times print help-wanted with pay.xlsx
+++ b/assets/Housing Study/Job Market/Telluride Times print help-wanted with pay.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method and limits" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Every ad'!$A$4:$H$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Every ad'!$A$4:$H$125</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -142,11 +142,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -260,12 +260,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$G$4</f>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$G$4</f>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
             </numRef>
           </val>
         </ser>
@@ -279,12 +279,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$G$4</f>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$5:$G$5</f>
+              <f>'Jobs by Category'!$B$5:$M$5</f>
             </numRef>
           </val>
         </ser>
@@ -298,12 +298,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$G$4</f>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$6:$G$6</f>
+              <f>'Jobs by Category'!$B$6:$M$6</f>
             </numRef>
           </val>
         </ser>
@@ -317,12 +317,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$G$4</f>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$7:$G$7</f>
+              <f>'Jobs by Category'!$B$7:$M$7</f>
             </numRef>
           </val>
         </ser>
@@ -336,12 +336,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$G$4</f>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$8:$G$8</f>
+              <f>'Jobs by Category'!$B$8:$M$8</f>
             </numRef>
           </val>
         </ser>
@@ -355,12 +355,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$G$4</f>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$9:$G$9</f>
+              <f>'Jobs by Category'!$B$9:$M$9</f>
             </numRef>
           </val>
         </ser>
@@ -374,12 +374,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$G$4</f>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$10:$G$10</f>
+              <f>'Jobs by Category'!$B$10:$M$10</f>
             </numRef>
           </val>
         </ser>
@@ -393,12 +393,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$G$4</f>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$11:$G$11</f>
+              <f>'Jobs by Category'!$B$11:$M$11</f>
             </numRef>
           </val>
         </ser>
@@ -412,12 +412,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$G$4</f>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$12:$G$12</f>
+              <f>'Jobs by Category'!$B$12:$M$12</f>
             </numRef>
           </val>
         </ser>
@@ -431,12 +431,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$G$4</f>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$13:$G$13</f>
+              <f>'Jobs by Category'!$B$13:$M$13</f>
             </numRef>
           </val>
         </ser>
@@ -450,12 +450,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$G$4</f>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$14:$G$14</f>
+              <f>'Jobs by Category'!$B$14:$M$14</f>
             </numRef>
           </val>
         </ser>
@@ -469,12 +469,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$G$4</f>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$15:$G$15</f>
+              <f>'Jobs by Category'!$B$15:$M$15</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$G$4</f>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$16:$G$16</f>
+              <f>'Jobs by Category'!$B$16:$M$16</f>
             </numRef>
           </val>
         </ser>
@@ -507,12 +507,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$G$4</f>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$17:$G$17</f>
+              <f>'Jobs by Category'!$B$17:$M$17</f>
             </numRef>
           </val>
         </ser>
@@ -526,12 +526,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$G$4</f>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$18:$G$18</f>
+              <f>'Jobs by Category'!$B$18:$M$18</f>
             </numRef>
           </val>
         </ser>
@@ -545,12 +545,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$G$4</f>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$19:$G$19</f>
+              <f>'Jobs by Category'!$B$19:$M$19</f>
             </numRef>
           </val>
         </ser>
@@ -564,12 +564,69 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$G$4</f>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$20:$G$20</f>
+              <f>'Jobs by Category'!$B$20:$M$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="17"/>
+          <order val="17"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Jobs by Category'!$B$21:$M$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="18"/>
+          <order val="18"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Jobs by Category'!$B$22:$M$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="19"/>
+          <order val="19"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Jobs by Category'!$B$4:$M$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Jobs by Category'!$B$23:$M$23</f>
             </numRef>
           </val>
         </ser>
@@ -631,7 +688,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3960000"/>
@@ -941,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -952,6 +1009,12 @@
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -976,35 +1039,65 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
+          <t>April 23-29, 2026</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>April 30-May 6, 2026</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>May 7-13, 2026</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>May 21-27, 2026</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>May 28-June 3, 2026</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>June 4-10, 2026</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
           <t>June 18-24, 2026</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>June 25-July 1, 2026</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>July 2-8, 2026</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>July 9-15, 2026</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>July 23-29, 2026</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>July 30-August 5, 2026</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -1013,66 +1106,94 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="I5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="7" t="n">
-        <v>9</v>
+      <c r="K5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="7" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="M6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="7" t="n">
-        <v>8</v>
+      <c r="N6" s="7" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="C7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>1</v>
@@ -1081,35 +1202,67 @@
         <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="I7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="7" t="n">
-        <v>7</v>
+      <c r="J7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="D8" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="7" t="n">
-        <v>6</v>
+      <c r="G8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+      <c r="N8" s="7" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -1119,51 +1272,69 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>5</v>
+      <c r="I9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>1</v>
-      </c>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>4</v>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" s="6" t="n"/>
+      <c r="N10" s="7" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>53-0000 Transportation and Material Moving</t>
+          <t>33-0000 Protective Service</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
@@ -1172,290 +1343,524 @@
       <c r="C11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
+      <c r="D11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="7" t="n">
-        <v>3</v>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="6" t="n"/>
+      <c r="N11" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>49-0000 Installation, Maintenance, and Repair</t>
+          <t>39-0000 Personal Care and Service</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
-      <c r="H12" s="7" t="n">
-        <v>2</v>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>33-0000 Protective Service</t>
+          <t>53-0000 Transportation and Material Moving</t>
         </is>
       </c>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="7" t="n">
-        <v>2</v>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>43-0000 Office and Administrative Support</t>
+          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
+      <c r="D14" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="E14" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="6" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="G14" s="6" t="n"/>
-      <c r="H14" s="7" t="n">
-        <v>2</v>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>1</v>
-      </c>
+          <t>15-0000 Computer and Mathematical</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="7" t="n">
-        <v>1</v>
+      <c r="E15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
+      <c r="N15" s="7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>17-0000 Architecture and Engineering</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>1</v>
-      </c>
+          <t>49-0000 Installation, Maintenance, and Repair</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
-      <c r="H16" s="7" t="n">
-        <v>1</v>
+      <c r="H16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n"/>
+      <c r="N16" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>47-0000 Construction and Extraction</t>
+          <t>17-0000 Architecture and Engineering</t>
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="7" t="n">
-        <v>1</v>
+      <c r="F17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n"/>
+      <c r="N17" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>19-0000 Life, Physical, and Social Science</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
+          <t>47-0000 Construction and Extraction</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>1</v>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>15-0000 Computer and Mathematical</t>
+          <t>13-0000 Business and Financial Operations</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="G19" s="6" t="n"/>
-      <c r="H19" s="7" t="n">
-        <v>1</v>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
+      <c r="N19" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>13-0000 Business and Financial Operations</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n">
-        <v>1</v>
-      </c>
+          <t>43-0000 Office and Administrative Support</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
-      <c r="H20" s="7" t="n">
-        <v>1</v>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6" t="n"/>
+      <c r="N20" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>19-0000 Life, Physical, and Social Science</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Other or not stated</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
+      <c r="N22" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>23-0000 Legal</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
+      <c r="N23" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>All help-wanted ads</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n">
+      <c r="B24" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="I24" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="J24" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K24" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="L24" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="M24" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="N24" s="9" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Ads stating a wage</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E25" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G21" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Ads stating a wage</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n">
+      <c r="F25" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="C22" s="11" t="n">
+      <c r="I25" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="J25" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="K25" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="L25" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="M25" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="H22" s="11" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="N25" s="11" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Ads saying pay DOE</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
+      <c r="B26" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C26" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="J26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="K26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="9" t="n"/>
+      <c r="M26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="9" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Ads offering housing</t>
         </is>
       </c>
-      <c r="B24" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="11" t="n">
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="J27" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="K27" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="F24" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="11" t="n">
-        <v>9</v>
+      <c r="L27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="11" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1470,7 +1875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1524,115 +1929,115 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>49920</v>
+        <v>25293</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>59960</v>
+        <v>65000</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>70000</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>65000</v>
+        <v>30000</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>65000</v>
+        <v>40000</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>65000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
+          <t>41-0000 Sales and Related</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>37440</v>
+        <v>49920</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>56160</v>
+        <v>59960</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>72800</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>29-0000 Healthcare Practitioners and Technical</t>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>37440</v>
+        <v>15000</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>65520</v>
+        <v>55120</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>158000</v>
+        <v>58240</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>43680</v>
+        <v>37440</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>45760</v>
+        <v>65520</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>47840</v>
+        <v>158000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>53-0000 Transportation and Material Moving</t>
+          <t>35-0000 Food Preparation and Serving Related</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>45760</v>
+        <v>37440</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>57200</v>
+        <v>55640</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>68640</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="11">
@@ -1642,72 +2047,110 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>37440</v>
+        <v>25293</v>
       </c>
       <c r="D11" s="13" t="n">
         <v>55460</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>72800</v>
+        <v>158000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+          <t>39-0000 Personal Care and Service</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>15000</v>
+        <v>43680</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>20000</v>
+        <v>45760</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>25000</v>
+        <v>47840</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>17-0000 Architecture and Engineering</t>
+          <t>53-0000 Transportation and Material Moving</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>24523</v>
+        <v>45760</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>47622</v>
+        <v>57200</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>70720</v>
+        <v>68640</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
+          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>37440</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>42640</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>47840</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>17-0000 Architecture and Engineering</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>24523</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>47622</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>70720</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
           <t>13-0000 Business and Financial Operations</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="13" t="n">
+      <c r="B16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13" t="n">
         <v>24523</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D16" s="13" t="n">
         <v>47622</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E16" s="13" t="n">
         <v>70720</v>
       </c>
     </row>
@@ -1722,7 +2165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1794,7 +2237,7 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
@@ -1802,106 +2245,86 @@
           <t>11-0000 Management</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>$65,000.00/year</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="n">
-        <v>65000</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>65000</v>
-      </c>
-      <c r="F5" s="14" t="inlineStr"/>
+      <c r="C5" s="14" t="inlineStr"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G5" s="14" t="inlineStr"/>
-      <c r="H5" s="16" t="inlineStr">
-        <is>
-          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>Top Telluride GC seeks experienced superintendent. Top benefits and pay. DOE. Email resume to: telluridesuper@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr"/>
       <c r="D6" s="14" t="n"/>
       <c r="E6" s="14" t="n"/>
-      <c r="F6" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F6" s="14" t="inlineStr"/>
       <c r="G6" s="14" t="inlineStr"/>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top benefits and pay DOE. Email resume to: telluridesuper@gmail.com</t>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>Looking for a part-time teacher well-versed in AI/Claude/Agents applications to educate an ambitious 14 yr old boy going into 9th grade. Qualified coaches only please. Email jmasst@me.com or text (310)916-6132.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>17-0000 Architecture and Engineering</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>$26.00-$28.00/hour; $20.00-$22.50/hour; $25.00-$30.00/hour; $24.00-$34.00/hour; $22.00-$24.00/hour; $12.14-$14.00/hour; $12.14-$14.00/hour; $19.06/hour; $13.39/hour; $11.79/hour</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="n">
-        <v>24523</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>70720</v>
-      </c>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n"/>
       <c r="F7" s="14" t="inlineStr"/>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Night Auditor (Seasonal/$26-$28/hr), Reservations Agent ($20-$22.50/hr), Engineer ($25-$30/hr), Room Attendant (Seasonal/Piece Rate, $24-$34/hr), AM/ PM Houseperson (Seasonal/$19.06/ hr), Public Area Attendant (Seasonal/$19.06/hr), Host (Seasonal/$13.39/</t>
+      <c r="G7" s="14" t="inlineStr"/>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>Looking for a private part-time educator for a 14 yr old boy going into 9th grade. Mostly afternoons. Qualified educators only who can develop a creative curriculum. If interested please email jmasst@me.com or text (310) 916-6132.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>$15,000.00-$25,000.00/year</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>25000</v>
+          <t>$45,000.00-$50,000.00/year</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>50000</v>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
@@ -1909,107 +2332,107 @@
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr"/>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>Junior Nordic Director and Head Coach TSSC seeking experienced Nordic Director and Head Coach. Part time Oct-Mar. 15K-25K DOE. Email nordic@tssc.org https://tssc.org/wanted-nordicdirector/</t>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telluride Mountain School is hiring a Montessori Assistant Teacher Guide and inspire students in pre-school through kindergarten in developing their academic, social, and emotional growth. This is currently a full-time position. Salary in the $45k-50k range based on experience. To apply please send </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>29-0000 Healthcare Practitioners and Technical</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>$23.00-$40.00/hour</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="n">
-        <v>47840</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>83200</v>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="14" t="inlineStr"/>
       <c r="G9" s="14" t="inlineStr"/>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>Telluride Whole Health is seeking a Medical Assistant or RN. Part-time or full-time. $23-40/hr DOE. Call 970239-8674 to apply.</t>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teachers Wanted West End Public Schools RE-2 located in Nucla, CO is seeking the following certified teaching positions (ATL candidates encouraged to apply) for the upcoming 26-27 school year: Kindergarten Teacher, K-12th Grade Performing Arts Teacher, Special Education Teacher/ Generalist. For job </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>29-0000 Healthcare Practitioners and Technical</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>$19.00-$21.00/hour; $19.00-$20.00/hour; $50.00/hour</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>39520</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>104000</v>
-      </c>
-      <c r="F10" s="14" t="inlineStr"/>
+          <t>$30,000.00-$50,000.00/year</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G10" s="14" t="inlineStr"/>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>1099 Handyman/Maintenance Runner needed. $50/hr. Experience required. Send resume to vendors@avantstay.com � A46 CLASSIFIEDS THE TELLURIDE TIMES WEEK OF JUNE 18-24, 2026 NOW HIRING: Dental Assistant (Will Train) Full-Time | $19–$21/hour While previous dental or healthcare experience is preferred, we</t>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>Telluride Mountain School is hiring an All School Art Teacher Teach and inspire students in kindergarten through 8th grade in developing artistic skill, creative confidence, visual literacy, and habits of observation and expression. This is currently an exempt, part-time position. Salary in the $30K</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>$26.00-$28.00/hour</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>54080</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>58240</v>
+      </c>
       <c r="F11" s="14" t="inlineStr"/>
       <c r="G11" s="14" t="inlineStr"/>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>Paddle Board Guide Telluride Outside is hiring a Paddle Board Guide for the summer. Please contact reservations@tellurideoutside.com.</t>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>Office Admin Coldwell Banker; Hiring for Part-time Receptionist/Office Mgr. Must be professional, friendly &amp;organized. Responsibilities: Front desk reception, office operations, agent support, &amp; marketing assistance. 20 hours/week; $26 - $28/hour. Send resume to: resume@cbdistinctive.com</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr"/>
@@ -2017,197 +2440,173 @@
       <c r="E12" s="14" t="n"/>
       <c r="F12" s="14" t="inlineStr"/>
       <c r="G12" s="14" t="inlineStr"/>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enchanted Forest Toy Shoppe is hiring! Our fast-paced, fun shoppe needs a committed and energetic person to join our team! 20 hours to start. Retail experience preferred. Yearround commitment a plus. Competitive wages and immediate start. Please send us a brief letter of interest and your resume to </t>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>Norwood Public Schools is looking for a High School Volleyball Coach. Please check out the full job description at https://www.norwoodk12.org/jobs and «click here for job listings and to apply online.» We will be accepting applications on an ongoing basis until positions are filled.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>$24.00-$27.00/hour; $70,000.00/year</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>49920</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>70000</v>
-      </c>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
       <c r="F13" s="14" t="inlineStr"/>
       <c r="G13" s="14" t="inlineStr"/>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for full-time depending on qualifications and schedule flexibil- </t>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>Telluride R-1 School District is hiring IT Systems Administrator, School Nurse (2026-27 school year). To learn more and apply tellurideschool.org/employment</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>49-0000 Installation, Maintenance, and Repair</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
+          <t>33-0000 Protective Service</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>$18.00/hour; $30,000.00-$35,000.00/year; $80,000.00/year; $100,000.00/year</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>100000</v>
+      </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr"/>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>Farmers Water Development Co. full-time, year-round Ditch Rider. Equipment/CDL preferred. Pay DOE. Send resume to farmerswdc@yahoo.com. Deadline 6/26/26</t>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>Telluride Mountain School is hiring a Middle School Humanities Teacher Teach and inspire students in 5th through 8th grades in developing strong reading, writing, discussion, and critical thinking skills, while deepening their understanding of history, literature, and the human experience.This is cu</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>53-0000 Transportation and Material Moving</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>$22.00/hour; $33.00/hour</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="n">
-        <v>45760</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>68640</v>
-      </c>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
       <c r="F15" s="14" t="inlineStr"/>
       <c r="G15" s="14" t="inlineStr"/>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>DESTINATION SYSTEMS dba Telluride Express HIRING CDL and Non CDL Drivers LIVE IN THE MOUNTAINS. DRIVE WITH PURPOSE. GET PAID WELL. Destination Systems is NOW HIRING drivers in Telluride &amp; Mountain Village! Whether you want full-time work or just extra income a few days a week, we have flexible sched</t>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>Reservationist Telluride Outside is hiring a summer/fall reservationist. Please contact Kristen Haaker: reservations@tellurideoutside.com / (970) 728-3895 ext 1. https://www.sanmiguelcountyco. gov/198/Planning The official designated posting place for all meeting notices is online at https://www.san</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>41-0000 Sales and Related</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr"/>
       <c r="D16" s="14" t="n"/>
       <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F16" s="14" t="inlineStr"/>
       <c r="G16" s="14" t="inlineStr"/>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top beneﬁts and pay DOE. Email resume to: telluridesuper@gmail.com</t>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>Retail P/T, 20 hrs to start. Committed, hard working team player wanted for our busy retail shoppe in town. Prefer year-round commitment. Send resume and brief letter of interest to: info@eftoyshoppe.com</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>41-0000 Sales and Related</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>$65,000.00/year</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="n">
-        <v>65000</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>65000</v>
+          <t>$25.00/hour</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>52000</v>
       </c>
       <c r="F17" s="14" t="inlineStr"/>
       <c r="G17" s="14" t="inlineStr"/>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>The Telluride Toggery is hiring! Join our fun and motivated sales team at Telluride’s longest running clothing store. Full-time salesperson positions are now available starting at $25/hr. Apply in person at 109 East Colorado Ave or email: wendy@thetelluridetoggery.com</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>13-0000 Business and Financial Operations</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>$26.00-$28.00/hour; $20.00-$22.50/hour; $23.00-$25.00/hour; $24.00-$34.00/hour; $22.00-$24.00/hour; $12.14-$14.00/hour; $12.14-$14.00/hour; $19.06/hour; $13.39/hour; $11.79/hour</t>
-        </is>
-      </c>
-      <c r="D18" s="15" t="n">
-        <v>24523</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>70720</v>
-      </c>
+          <t>43-0000 Office and Administrative Support</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
       <c r="F18" s="14" t="inlineStr"/>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Night Auditor (Seasonal/$26-$28/hr), Reservations Agent ($20- $22.50/hr), Expo - Seasonal (EXPOS)/Service Worker ($23-$25/hr), Room Attendant (Seasonal/Piece Rate, $24-$34/ hr), AM/PM Houseperson (Seasonal/$19.06/hr), Public Area Attendant (Seasonal/$19.</t>
+      <c r="G18" s="14" t="inlineStr"/>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>Store Clerk Summer season is quickly approaching, work in the middle of all the beauty and happenings! Morning and Afternoon shifts available, Part time or Full time at the Ridgway Conoco! Discounts and Perks included! Starting pay $16 and up for experience or willingness to learn. Apply on indeed o</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
+          <t>47-0000 Construction and Extraction</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr"/>
@@ -2215,59 +2614,47 @@
       <c r="E19" s="14" t="n"/>
       <c r="F19" s="14" t="inlineStr"/>
       <c r="G19" s="14" t="inlineStr"/>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>Rainbow Preschool is seeking a loving and dedicated PT Preschool Teacher to join our nurturing early childhood education program. Experience in ECE preferred. We oﬀer a supportive, friendly work environment, opportunities for professional development and competitive pay. Please email resume to rainb</t>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>PUBLIC HEARING NOTICE The San Miguel County Planning Commission has been asked to consider an application submitted by John Miller, Ponderosa Planning &amp; Design, on behalf of Kurt Works Inc. and Kurt Crockett, owner of a 44.13-acre parcel, located at 488 S. Avalon Dr., Norwood, CO, Parcel #4527261030</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>29-0000 Healthcare Practitioners and Technical</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>$20.00-$22.00/hour; $19.00-$20.00/hour; $19.00-$21.00/hour; $25.00/hour; $18.00/hour; $35.00/hour; $158,000.00/year</t>
-        </is>
-      </c>
-      <c r="D20" s="15" t="n">
-        <v>37440</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>158000</v>
-      </c>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
       <c r="F20" s="14" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>Lumiere by Dunton Come join our 5* hotel and restaurant! Housing available PM Bell PT ($20hr +tips), PM Concierge (PT $25hr +tips), Bartender ($18hr +tips or $35hr), PM Server ($18 +tips or $35hr), AM Server ($22hr +tips). Email: famaral@lumieretelluride.com ■ $75 caviar-topped tots. A day’s pay wor</t>
+      <c r="G20" s="14" t="inlineStr"/>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>Top Telluride GC seeks experienced superintendent. Top benefits and pay. DOE. Email resume to: telluridesuper@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr"/>
@@ -2275,21 +2662,21 @@
       <c r="E21" s="14" t="n"/>
       <c r="F21" s="14" t="inlineStr"/>
       <c r="G21" s="14" t="inlineStr"/>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>Paddle Board Guide Telluride Outside is hiring a Paddle Board Guide for the summer. Please contact reservations@tellurideoutside.com.</t>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>Looking for a part-time teacher well-versed in AI/Claude/Agents applications to educate an ambitious 14 yr old boy going into 9th grade. Qualified coaches only please. Email jmasst@me.com or text (310)916-6132.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr"/>
@@ -2297,163 +2684,175 @@
       <c r="E22" s="14" t="n"/>
       <c r="F22" s="14" t="inlineStr"/>
       <c r="G22" s="14" t="inlineStr"/>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>Enchanted Forest Toy Shoppe is hiring! Our fast-paced, fun shoppe needs a committed and energetic person to join our team! 20 hours to start. Retail experience preferred. Year-round commitment a plus. Competitive wages and immediate start. Please send us a brief letter of interest and your resume to</t>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>Looking for a private part-time educator for a 14 yr old boy going into 9th grade. Mostly afternoons. Qualified educators only who can develop a creative curriculum. If interested please email jmasst@me.com or text (310)916-6132.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>$24.00-$27.00/hour; $70,000.00/year</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="n">
-        <v>49920</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>70000</v>
-      </c>
-      <c r="F23" s="14" t="inlineStr"/>
+          <t>$45,000.00-$50,000.00/year</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G23" s="14" t="inlineStr"/>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility.</t>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telluride Mountain School is hiring a Montessori Assistant Teacher Guide and inspire students in pre-school through kindergarten in developing their academic, social, and emotional growth. This is currently a full-time position. Salary in the $45k-50k range based on experience. To apply please send </t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>49-0000 Installation, Maintenance, and Repair</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr"/>
       <c r="D24" s="14" t="n"/>
       <c r="E24" s="14" t="n"/>
-      <c r="F24" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F24" s="14" t="inlineStr"/>
       <c r="G24" s="14" t="inlineStr"/>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>Farmers Water Development Co. full-time, year-round Ditch Rider. Equipment/CDL preferred. Pay DOE. Send resume to farmerswdc@yahoo.com. Deadline 6/26/26</t>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>Teachers Wanted West End Public Schools RE–2. located in Nucla, CO is seeking the following certified teaching positions (ATL candidates encouraged to apply) for the upcoming 26–27 school year: Kindergarten Teacher, K–12th Grade Performing Arts Teacher, Special Education Teacher/Generalist For job d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>53-0000 Transportation and Material Moving</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>$22.00/hour; $33.00/hour</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="n">
-        <v>45760</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>68640</v>
-      </c>
-      <c r="F25" s="14" t="inlineStr"/>
+          <t>$30,000.00-$50,000.00/year</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G25" s="14" t="inlineStr"/>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>DESTINATION SYSTEMS dba Telluride Express HIRING CDL and Non CDL Drivers LIVE IN THE MOUNTAINS. DRIVE WITH PURPOSE. GET PAID WELL. Destination Systems is NOW HIRING drivers in • Page A45 Telluride &amp; Mountain Village! Whether you want full-time work or just extra income a few days a week, we have ﬂex</t>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>Telluride Mountain School is hiring an All School Art Teacher Teach and inspire students in kindergarten through 8th grade in developing artistic skill, creative confidence, visual literacy, and habits of observation and expression. This is currently an exempt, part-time position. Salary in the $30K</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>July 2-8, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr"/>
-      <c r="D26" s="14" t="n"/>
-      <c r="E26" s="14" t="n"/>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>$30,000.00-$35,000.00/year</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>35000</v>
+      </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr"/>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top beneﬁts and pay DOE. Email resume to: telluridesuper@gmail.com</t>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>Telluride Mountain School is hiring a Middle School Humanities Teacher Teach and inspire students in 5th through 8th grades in developing strong reading, writing, discussion, and critical thinking skills, while deepening their understanding of history, literature, and the human experience.This is cu</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>July 2-8, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>$65,000.00/year</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="n">
-        <v>65000</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>65000</v>
+          <t>$26.00-$28.00/hour</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>54080</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>58240</v>
       </c>
       <c r="F27" s="14" t="inlineStr"/>
       <c r="G27" s="14" t="inlineStr"/>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>Office Admin Coldwell Banker; Hiring for Part-time Receptionist/ Office Mgr. Must be professional, friendly &amp;organized. Responsibilities: Front desk reception, office operations, agent support, &amp; marketing assistance. 20 hours/week; $26 - $28/hour. Send resume to: resume@cbdistinctive.com</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>July 2-8, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr"/>
@@ -2461,33 +2860,33 @@
       <c r="E28" s="14" t="n"/>
       <c r="F28" s="14" t="inlineStr"/>
       <c r="G28" s="14" t="inlineStr"/>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>Rainbow Preschool is seeking a loving and dedicated PT Preschool • Page A73 Deadline for Public Notices Submission 9:00 a.m. on Thursday. Teacher to join our nurturing early childhood education program. Experience in ECE preferred. We oﬀer a supportive, friendly work environment, opportunities for p</t>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>Norwood Public Schools is looking for a High School Volleyball Coach. Please check out the full job description at https://www.norwoodk12.org/jobs and «Click here for job listings and to apply online.» We will be accepting applications on an ongoing basis until positions are filled.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>July 2-8, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>29-0000 Healthcare Practitioners and Technical</t>
+          <t>33-0000 Protective Service</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>$24.00-$27.00/hour; $20.00-$22.00/hour; $19.00-$21.00/hour; $19.00-$20.00/hour; $70,000.00/year</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>39520</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>70000</v>
+          <t>$20.00-$25.00/hour; $18.00/hour; $12.16/hour; $65,000.00/year; $80,000.00/year; $100,000.00/year; $158,000.00/year</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>25293</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>158000</v>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
@@ -2495,89 +2894,73 @@
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr"/>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility.</t>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>Telluride Brewing Craft Kitchen and Pizza is hiring (Lawson Hill Location). Kitchen Manager: $65,000 (could increase based on experience)+Benefits; Back of the House: $20-$25/hour based on experience (weekends required); Food Runner: $18/hour plus tips (weekends required); Bartender: $12.16/hour plu</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>July 2-8, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>$20.00/hour; $25.00/hour; $18.00/hour; $35.00/hour; $22.00/hour</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="n">
-        <v>37440</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>72800</v>
-      </c>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
       <c r="F30" s="14" t="inlineStr"/>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>Lumiere by Dunton Come join our 5* hotel and restaurant! Housing available. PM Bell PT ($20hr +tips), PM Concierge (PT $25hr +tips), Bartender ($18hr +tips or $35hr), PM Server ($18 +tips or $35hr), AM Server ($22hr +tips). Email: famaral@lumieretelluride.com</t>
+      <c r="G30" s="14" t="inlineStr"/>
+      <c r="H30" s="15" t="inlineStr">
+        <is>
+          <t>Retail P/T, 20 hrs to start. Committed, hard working team player wanted for our busy retail shoppe in town. Prefer year-round commitment. Send resume and brief letter of interest to: info@eftoyshoppe.com</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>July 2-8, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
+          <t>41-0000 Sales and Related</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>$20.00-$22.50/hour; $24.00-$34.00/hour</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="n">
-        <v>41600</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>70720</v>
+          <t>$25.00/hour</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <v>52000</v>
       </c>
       <c r="F31" s="14" t="inlineStr"/>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
-        <is>
-          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Reservations Agent ($20-$22.50/hr), Room Attendant (Seasonal/Piece Rate, $24-$34/hr). We oﬀer amazing beneﬁts and a really fun, creative and innovative work atmosphere. Season Ski Pass, Employee Meals, Employee Shuttle, Discounted Room Rates, Discounts a</t>
+      <c r="G31" s="14" t="inlineStr"/>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>The Telluride Toggery is hiring! Join our fun and motivated sales team at Telluride’s longest running clothing store. Full-time salesperson positions are now available starting at $25/hr. Apply in person at 109 East Colorado Ave or email: wendy@thetelluridetoggery.com</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>July 2-8, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
+          <t>Other or not stated</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr"/>
@@ -2585,38 +2968,42 @@
       <c r="E32" s="14" t="n"/>
       <c r="F32" s="14" t="inlineStr"/>
       <c r="G32" s="14" t="inlineStr"/>
-      <c r="H32" s="16" t="inlineStr">
-        <is>
-          <t>Paddle Board Guide Telluride Outside is hiring a Paddle Board Guide for the summer. Please contact reservations@tellurideoutside.com.</t>
+      <c r="H32" s="15" t="inlineStr">
+        <is>
+          <t>any neighbor or potentially affected property owner who, for any reason, has not received a copy of this notice, it would be appreciated if you would inform them of this public hearing. 4/30 COL-000119</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>July 2-8, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr"/>
       <c r="D33" s="14" t="n"/>
       <c r="E33" s="14" t="n"/>
-      <c r="F33" s="14" t="inlineStr"/>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G33" s="14" t="inlineStr"/>
-      <c r="H33" s="16" t="inlineStr">
-        <is>
-          <t>Enchanted Forest Toy Shoppe is hiring! Our fast-paced, fun shoppe needs a committed and energetic person to join our team! 20 hours to start. Retail experience preferred. Year-round commitment a plus. Competitive wages and immediate start. Please send us a brief letter of interest and your resume to</t>
+      <c r="H33" s="15" t="inlineStr">
+        <is>
+          <t>Top Telluride GC seeks experienced superintendent. Top beneﬁts and pay. DOE. Email resume to: telluridesuper@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>July 9-15, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
@@ -2626,53 +3013,49 @@
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>$65,000.00/year</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="n">
-        <v>65000</v>
-      </c>
-      <c r="E34" s="15" t="n">
-        <v>65000</v>
+          <t>$50,000.00-$60,000.00/year</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>60000</v>
       </c>
       <c r="F34" s="14" t="inlineStr"/>
       <c r="G34" s="14" t="inlineStr"/>
-      <c r="H34" s="16" t="inlineStr">
-        <is>
-          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
+      <c r="H34" s="15" t="inlineStr">
+        <is>
+          <t>Front Desk Administrator (FT) Luxury real estate oﬃce seeking professional front desk support. Duties include greeting clients, answering phones, and assisting advisors. Req: Experience, strong communication &amp; organization skills. Hours: Mon–Fri | Pay: $50K–$60K+ beneﬁts. Please email lkropuenske@li</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>July 9-15, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>15-0000 Computer and Mathematical</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr"/>
       <c r="D35" s="14" t="n"/>
       <c r="E35" s="14" t="n"/>
-      <c r="F35" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F35" s="14" t="inlineStr"/>
       <c r="G35" s="14" t="inlineStr"/>
-      <c r="H35" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Norwood Public Schools is looking for a Director of Technology. Please check out the full job description at https://www.norwoodk12.org/jobs and “Click here for job listings and to apply online.” We will be accepting applications on an ongoing basis until positions are ﬁlled. ■ Who says a vegetable </t>
+      <c r="H35" s="15" t="inlineStr">
+        <is>
+          <t>Notice to First Mortgagees Regarding Consent to First Amendment to Declaration Village Creek Condominium Association, a Colorado nonproﬁt corporation Property: Village Creek Condominiums, as established by the Condominium Declaration recorded December 23, 1987 in Book 441, page 232, Reception No. 25</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>July 9-15, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
@@ -2680,154 +3063,158 @@
           <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr"/>
-      <c r="D36" s="14" t="n"/>
-      <c r="E36" s="14" t="n"/>
-      <c r="F36" s="14" t="inlineStr"/>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>$45,000.00-$50,000.00/year</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G36" s="14" t="inlineStr"/>
-      <c r="H36" s="16" t="inlineStr">
-        <is>
-          <t>Telluride School District R-1 Request for Proposal for Custodial Services The Telluride School District (TSD) is requesting proposals for custodial services to be performed at the following school building facilities: Telluride Elementary School; Telluride Intermediate School; and Telluride Middle/H</t>
+      <c r="H36" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telluride Mountain School is hiring a Montessori Assistant Teacher Guide and inspire students in pre-school through kindergarten in developing their academic, social, and emotional growth. This is currently a full-time position. Salary in the $45k-50k range based on experience. To apply please send </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>July 9-15, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>33-0000 Protective Service</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>$20.00/hour; $25.00/hour; $18.00/hour; $35.00/hour</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="n">
-        <v>37440</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>72800</v>
-      </c>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="14" t="n"/>
       <c r="F37" s="14" t="inlineStr"/>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H37" s="16" t="inlineStr">
-        <is>
-          <t>Lumiere by Dunton Come join our 5* hotel and restaurant! Housing available. PM Bell PT ($20hr +tips), PM Concierge (PT $25hr +tips), Bartender ($18hr +tips or $35hr), PM Server ($18 +tips or $35hr), San Miguel County is Hiring! The following positions are full-time, yearround and include competitive</t>
+      <c r="G37" s="14" t="inlineStr"/>
+      <c r="H37" s="15" t="inlineStr">
+        <is>
+          <t>Teachers Wanted West End Public Schools RE–2. located in Nucla, CO is seeking the following certiﬁed teaching positions (ATL candidates encouraged to apply) for the upcoming 26– 27 school year: Kindergarten Teacher, K–12th Grade Performing Arts Teacher, Special Education Teacher/Generalist For job d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>July 9-15, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>$22.00/hour</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="n">
-        <v>45760</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <v>45760</v>
-      </c>
-      <c r="F38" s="14" t="inlineStr"/>
+          <t>$30,000.00-$50,000.00/year</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G38" s="14" t="inlineStr"/>
-      <c r="H38" s="16" t="inlineStr">
-        <is>
-          <t>AM Server ($22hr +tips). Email: famaral@lumieretelluride.com</t>
+      <c r="H38" s="15" t="inlineStr">
+        <is>
+          <t>Telluride Mountain School is hiring an All School Art Teacher Teach and inspire students in kindergarten through 8th grade in developing artistic skill, creative conﬁdence, visual literacy, and habits of observation and expression. This is currently an exempt, parttime position. Salary in the $30K-5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>July 9-15, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>$20.00-$22.50/hour; $24.00-$34.00/hour</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="n">
-        <v>41600</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>70720</v>
-      </c>
-      <c r="F39" s="14" t="inlineStr"/>
-      <c r="G39" s="14" t="inlineStr">
+          <t>$30,000.00-$35,000.00/year</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>35000</v>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H39" s="16" t="inlineStr">
-        <is>
-          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Reservations Agent ($20-$22.50/ hr), Room Attendant (Seasonal/ Piece Rate, $24-$34/hr). We oﬀer amazing beneﬁts and a really fun, creative and innovative work atmosphere. Season Ski Pass, Employee Meals, Employee Shuttle, Discounted Room Rates, Discounts</t>
+      <c r="G39" s="14" t="inlineStr"/>
+      <c r="H39" s="15" t="inlineStr">
+        <is>
+          <t>Telluride Mountain School is hiring a Middle School Humanities Teacher Teach and inspire students in 5th through 8th grades in developing strong reading, writing, discussion, and critical thinking skills, while deepening their understanding of history, literature, and the human experience.This is cu</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>July 9-15, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>$24.00-$27.00/hour; $70,000.00/year</t>
-        </is>
-      </c>
-      <c r="D40" s="15" t="n">
-        <v>49920</v>
-      </c>
-      <c r="E40" s="15" t="n">
-        <v>70000</v>
+          <t>$26.00-$28.00/hour</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="n">
+        <v>54080</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>58240</v>
       </c>
       <c r="F40" s="14" t="inlineStr"/>
       <c r="G40" s="14" t="inlineStr"/>
-      <c r="H40" s="16" t="inlineStr">
-        <is>
-          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/ hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility</t>
+      <c r="H40" s="15" t="inlineStr">
+        <is>
+          <t>Oﬃce Admin Coldwell Banker; Hiring for Part-time Receptionist/Ofﬁce Mgr. Must be professional, friendly &amp;organized. Responsibilities: Front desk reception, oﬃce operations, agent support, &amp; marketing assistance. 20 hours/week; $26 - $28/hour. Send resume to: resume@cbdistinctive.com</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>July 9-15, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>43-0000 Office and Administrative Support</t>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
         </is>
       </c>
       <c r="C41" s="14" t="inlineStr"/>
@@ -2835,247 +3222,307 @@
       <c r="E41" s="14" t="n"/>
       <c r="F41" s="14" t="inlineStr"/>
       <c r="G41" s="14" t="inlineStr"/>
-      <c r="H41" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TOWN OF MOUNTAIN VILLAGE NOTICE Notice is hereby given that the following Ordinance passed on the ﬁrst reading at the Town of Mountain Village Town Council meeting held April 23, 2026. The second reading, public hearing and ﬁnal Council vote will take place on Thursday, July 16, 2026, at 2:00 p.m., </t>
+      <c r="H41" s="15" t="inlineStr">
+        <is>
+          <t>Norwood Public Schools is looking for a High School Volleyball Coach. Please check out the full job description at https://www.norwoodk12.org/jobs and «click here for job listings and to apply online.» We will be accepting applications on an ongoing basis until positions are ﬁlled.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>July 9-15, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>43-0000 Office and Administrative Support</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="inlineStr"/>
-      <c r="D42" s="14" t="n"/>
-      <c r="E42" s="14" t="n"/>
-      <c r="F42" s="14" t="inlineStr"/>
+          <t>33-0000 Protective Service</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>$30.00-$35.00/hour; $18.00/hour</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>72800</v>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G42" s="14" t="inlineStr"/>
-      <c r="H42" s="16" t="inlineStr">
-        <is>
-          <t>The Farmers’ Water Development Company (FWDC) has received written request to replace a lost, destroyed or wrongfully taken share certificate #887 currently issued in the name A.F. Newans M.D.,C.P.. Unless written notice of objection to the issuance of a replacement share certificate is filed with F</t>
+      <c r="H42" s="15" t="inlineStr">
+        <is>
+          <t>Summer Program Director Fulltime Seasonal (May–October), Telluride Adaptive Sports Program (TASP) is seeking a Summer Program Director to help lead our seasonal adaptive recreation programs in the San Juan Mountains. This full-time role oversees daily operations, instructor coordination, and multida</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>July 23-29, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="inlineStr"/>
-      <c r="D43" s="14" t="n"/>
-      <c r="E43" s="14" t="n"/>
-      <c r="F43" s="14" t="inlineStr"/>
-      <c r="G43" s="14" t="inlineStr"/>
-      <c r="H43" s="16" t="inlineStr">
-        <is>
-          <t>Norwood Public Schools is looking for a Director of Technology. Please check out the full job description at https://www.norwoodk12.org/jobs and “Click here for job listings and to apply online.” We will be accepting applications on an ongoing basis until positions are ﬁlled.</t>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>$25.00-$30.00/hour; $20.00-$22.00/hour; $23.00/hour</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>41600</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>62400</v>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="inlineStr">
+        <is>
+          <t>Lumiere by Dunton: Come join our 5* hotel and restaurant! *Housing Available* Maintenance Tech FT ($25-$30hr DOE), PM Bellman $20hr FT/PT, AM Concierge $25hr FT/PT. Dunton Kitchen: Breakfast Cook $23hr+ DOE, PM Line Cook $25hr+ DOE, Dishwasher $20-$22hr, Bartender, Server, Breakfast Server. Email: f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>July 23-29, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="inlineStr"/>
-      <c r="D44" s="14" t="n"/>
-      <c r="E44" s="14" t="n"/>
+          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>$18.00-$23.00/hour</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>47840</v>
+      </c>
       <c r="F44" s="14" t="inlineStr"/>
       <c r="G44" s="14" t="inlineStr"/>
-      <c r="H44" s="16" t="inlineStr">
-        <is>
-          <t>Norwood Public Schools is seeking a 3rd Grade Teacher. Please check out the full job description at https://www.norwoodk12.org/ jobs and “Click here for job listings and to apply online.” We will be ac- cepting applications on an ongoing basis until positions are ﬁlled.</t>
+      <c r="H44" s="15" t="inlineStr">
+        <is>
+          <t>Guest Services, Drivers, Housepersons Bear Creek Lodge is hiring for several positions: guest services, drivers, and housepersons ($18-$23/hr). Housing opportunities available. View job descriptions and apply online at telluridelodging.com/careers.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>July 23-29, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="inlineStr"/>
-      <c r="D45" s="14" t="n"/>
-      <c r="E45" s="14" t="n"/>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>$25.00/hour</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <v>52000</v>
+      </c>
       <c r="F45" s="14" t="inlineStr"/>
       <c r="G45" s="14" t="inlineStr"/>
-      <c r="H45" s="16" t="inlineStr">
-        <is>
-          <t>Rainbow Preschool is seeking a loving and dedicated PT Preschool Teacher to join our nurturing early childhood education program. Experience in ECE preferred. We oﬀer a supportive, friendly work environment, opportunities for professional development and com- petitive pay. Please email resume to rai</t>
+      <c r="H45" s="15" t="inlineStr">
+        <is>
+          <t>The Telluride Toggery is hiring! Join our fun and motivated sales team at Telluride’s longest running clothing store. Full-time salesperson positions are now available starting at $25/hr. Apply in person at 109 East Colorado Ave or email: wendy@thetelluridetoggery.com</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>July 23-29, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>33-0000 Protective Service</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="inlineStr">
-        <is>
-          <t>$24.00-$27.00/hour; $20.00-$22.00/hour; $70,000.00/year</t>
-        </is>
-      </c>
-      <c r="D46" s="15" t="n">
-        <v>41600</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>70000</v>
-      </c>
-      <c r="F46" s="14" t="inlineStr"/>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr"/>
+      <c r="D46" s="14" t="n"/>
+      <c r="E46" s="14" t="n"/>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G46" s="14" t="inlineStr"/>
-      <c r="H46" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scarpe is hiring! Seeking year-round Full-Time and PartTime Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for fulltime depending on qualiﬁcations and schedule ﬂexibility. </t>
+      <c r="H46" s="15" t="inlineStr">
+        <is>
+          <t>Wilson Mesa Home For Rent 3 bed/1 bath. Mountain views + wood burning stove. No drugs/alcohol. Maybe 1 cat. 6 months-1 year lease. $2900/month + electricity + trash. Call Polly 970-728-0600. Superintendent Top Telluride GC seeks experienced superintendent. Top beneﬁts and pay DOE. Email resume to: t</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>July 23-29, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="inlineStr"/>
-      <c r="D47" s="14" t="n"/>
-      <c r="E47" s="14" t="n"/>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>$65,000.00/year</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>65000</v>
+      </c>
       <c r="F47" s="14" t="inlineStr"/>
       <c r="G47" s="14" t="inlineStr"/>
-      <c r="H47" s="16" t="inlineStr">
-        <is>
-          <t>Excellent Second Level Oﬃce Suite For Lease / 119 W Colorado Private Oﬃces, Conference Room, Reception Area, Kitchen &amp; Bath, Plus One Dedicated Parking Spot. Immediately available. Inquire at 970-729-1577. Blue Grouse Bread Hiring delivery driver. Fun folks, free bread, beneﬁts after 1 yr. Email res</t>
+      <c r="H47" s="15" t="inlineStr">
+        <is>
+          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>July 23-29, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>$20.00-$22.50/hour; $24.00-$34.00/hour</t>
-        </is>
-      </c>
-      <c r="D48" s="15" t="n">
-        <v>41600</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>70720</v>
+          <t>$50,000.00-$60,000.00/year</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>60000</v>
       </c>
       <c r="F48" s="14" t="inlineStr"/>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H48" s="16" t="inlineStr">
-        <is>
-          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Reservations Agent ($20-$22.50/ hr), Room Attendant (Seasonal/ Piece Rate, $24-$34/hr). We offer amazing beneﬁts and a really fun, creative and innovative work atmosphere. Season Ski Pass, Employee Meals, Employee Shuttle, Discounted Room Rates, Discount</t>
+      <c r="G48" s="14" t="inlineStr"/>
+      <c r="H48" s="15" t="inlineStr">
+        <is>
+          <t>Front Desk Administrator (FT) Luxury real estate oﬃce seeking professional front desk support. Duties include greeting clients, answering phones, and assisting advisors. Req: Experience, strong communication &amp; organi- zation skills. Hours: Mon–Fri | Pay: $50K–$60K+ beneﬁts. Please email lkropuenske@</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>July 23-29, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>$25.00/hour</t>
-        </is>
-      </c>
-      <c r="D49" s="15" t="n">
-        <v>52000</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>52000</v>
+          <t>$30.00/hour; $20.00/hour; $25.00/hour</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="n">
+        <v>41600</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>62400</v>
       </c>
       <c r="F49" s="14" t="inlineStr"/>
-      <c r="G49" s="14" t="inlineStr"/>
-      <c r="H49" s="16" t="inlineStr">
-        <is>
-          <t>The Telluride Toggery is seeking a salesperson to join our team! Come and work at Telluride’s lon- • Week of July 23-29, 2026 gest running clothing store located in the heart of downtown Telluride. Pay is based upon experience starting at $25 hour for full-time employment. Apply in person or contact</t>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="inlineStr">
+        <is>
+          <t>Lumiere by Dunton/Dunton Kitchen is hiring: Join our 5* hotel &amp; restaurant! *housing available* Maintenance Tech (FT $30hr +beneﬁts), PM Bellman ($20hr FT/PT), PM Concierge ($25hr). Dunton Kitchen: Dining Room Manager, Lead Bartender, PM Server, PM Line Cook ($25+hr), AM Prep Cook ($23+hr), Breakfas</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>July 30-August 5, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>19-0000 Life, Physical, and Social Science</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="inlineStr"/>
-      <c r="D50" s="14" t="n"/>
-      <c r="E50" s="14" t="n"/>
-      <c r="F50" s="14" t="inlineStr"/>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>$20.00-$25.00/hour; $18.00/hour; $12.16/hour; $65,000.00/year</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="n">
+        <v>25293</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G50" s="14" t="inlineStr"/>
-      <c r="H50" s="16" t="inlineStr">
-        <is>
-          <t>Service Planner I-V San Miguel Power Association, Inc. (SMPA) is seeking to ﬁll the position of Service Planner I-V out of our Ridgway oﬃce location. To view the complete job posting, beneﬁts, compensation, and howto apply, please visit our website www.smpa.com.</t>
+      <c r="H50" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Telluride Brewing Craft Kitchen and Pizza is hiring (Lawson Hill Location). Kitchen Manager: $65,000 (could increase based on experience)+Beneﬁts; Back of the House: $20-$25/hour based on experience (weekends required); Food Runner: $18/hour plus tips (weekends required); Bartender:$12.16/hour plus </t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>July 30-August 5, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
+          <t>15-0000 Computer and Mathematical</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr"/>
@@ -3083,21 +3530,21 @@
       <c r="E51" s="14" t="n"/>
       <c r="F51" s="14" t="inlineStr"/>
       <c r="G51" s="14" t="inlineStr"/>
-      <c r="H51" s="16" t="inlineStr">
-        <is>
-          <t>Norwood Public Schools is seeking a 3rd Grade Teacher. Please check out the full job description at https://www.norwoodk12.org/ jobs and “Click here for job listings and to apply online.” We will be accepting applications on an ongoing basis until positions are ﬁlled.</t>
+      <c r="H51" s="15" t="inlineStr">
+        <is>
+          <t>Chief Financial Oﬃcer &amp; Manager of Information Technology San Miguel Power Association, Inc. is seeking to ﬁll a Chief Financial Oﬃcer and Manager of IT to report out of our Nucla or Ridgway oﬃce location. Please visit our website for full job details and application. www.smpa.com</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>July 30-August 5, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr"/>
@@ -3105,80 +3552,76 @@
       <c r="E52" s="14" t="n"/>
       <c r="F52" s="14" t="inlineStr"/>
       <c r="G52" s="14" t="inlineStr"/>
-      <c r="H52" s="16" t="inlineStr">
-        <is>
-          <t>Rainbow Preschool is seeking a loving and dedicated PT Preschool Teacher to join our nurturing early childhood education program. Experience in ECE preferred. We oﬀer a supportive, friendly work environment, opportunities for professional development and competitive pay. Please email resume to rainb</t>
+      <c r="H52" s="15" t="inlineStr">
+        <is>
+          <t>Norwood Public Schools is lookingfor a High School Volleyball Coach. Please check out the full job description at https://www.norwoodk12.org/jobs and «click here for job listings and to apply online.» We will be accepting applications on an ongoing basis until positions are ﬁlled.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>July 30-August 5, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>29-0000 Healthcare Practitioners and Technical</t>
+          <t>33-0000 Protective Service</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
-          <t>$20.00-$22.50/hour; $24.00-$34.00/hour; $20.00-$22.00/hour; $19.00-$20.00/hour; $26.00/hour; $22.95/hour; $19.82/hour</t>
-        </is>
-      </c>
-      <c r="D53" s="15" t="n">
-        <v>39520</v>
-      </c>
-      <c r="E53" s="15" t="n">
-        <v>70720</v>
+          <t>$18.00/hour</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>37440</v>
       </c>
       <c r="F53" s="14" t="inlineStr"/>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H53" s="16" t="inlineStr">
-        <is>
-          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Reservations Agent ($20-$22.50/hr), Room Attendant (Seasonal/Piece Rate, $24-$34/hr), Banquet Captain ($23$26/hr), Front Desk Agent/Seasonal ($22.95/hr), Bell Valet/Seasonal ($19.82/hr plus tips ). We oﬀer amazing beneﬁts and a really fun, creative and i</t>
+      <c r="G53" s="14" t="inlineStr"/>
+      <c r="H53" s="15" t="inlineStr">
+        <is>
+          <t>Teachers Wanted West End Public Schools RE–2. located in Nucla, CO is seeking the following certiﬁed teaching positions (ATL candidates encouraged to apply) for the upcoming 26–27 school year: Kindergarten Teacher, K–12th Grade SERVICES Vacation Rental Specialist Cleaning Call our team for your vaca</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>July 30-August 5, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
+          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>$21.00-$23.00/hour</t>
-        </is>
-      </c>
-      <c r="D54" s="15" t="n">
-        <v>43680</v>
-      </c>
-      <c r="E54" s="15" t="n">
+          <t>$18.00-$23.00/hour</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E54" s="16" t="n">
         <v>47840</v>
       </c>
       <c r="F54" s="14" t="inlineStr"/>
       <c r="G54" s="14" t="inlineStr"/>
-      <c r="H54" s="16" t="inlineStr">
-        <is>
-          <t>Guest Services Associate PT &amp; FT Guest Service positions available at Bear Creek Lodge. $21-$23/hour. Apply: telluridelodging.com/careers</t>
+      <c r="H54" s="15" t="inlineStr">
+        <is>
+          <t>Guest Services, Drivers, Housepersons Bear Creek Lodge is hiring for several positions: guest services, drivers, and housepersons ($18-$23/hr). Housing opportunities available. View job descriptions and apply online at telluridelodging.com/careers.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>July 30-August 5, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B55" s="14" t="inlineStr">
@@ -3188,88 +3631,80 @@
       </c>
       <c r="C55" s="14" t="inlineStr">
         <is>
-          <t>$25.00/hour</t>
-        </is>
-      </c>
-      <c r="D55" s="15" t="n">
-        <v>52000</v>
-      </c>
-      <c r="E55" s="15" t="n">
-        <v>52000</v>
+          <t>$24.00-$27.00/hour; $70,000.00/year</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="n">
+        <v>49920</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <v>70000</v>
       </c>
       <c r="F55" s="14" t="inlineStr"/>
       <c r="G55" s="14" t="inlineStr"/>
-      <c r="H55" s="16" t="inlineStr">
-        <is>
-          <t>The Telluride Toggery is seeking a salesperson to join our team! Come and work at Telluride’s longest running clothing store located in the heart of downtown Telluride. • Page A53 Pay is based upon experience starting at $25 hour for full-time employment. Apply in person or contact Wendy at (970)728</t>
+      <c r="H55" s="15" t="inlineStr">
+        <is>
+          <t>Scarpe is hiring! Seeking FullTime and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility. Stop by Sc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>July 30-August 5, 2026</t>
+          <t>May 28-June 3, 2026</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="inlineStr">
-        <is>
-          <t>$24.00-$27.00/hour; $70,000.00/year</t>
-        </is>
-      </c>
-      <c r="D56" s="15" t="n">
-        <v>49920</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>70000</v>
-      </c>
-      <c r="F56" s="14" t="inlineStr"/>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr"/>
+      <c r="D56" s="14" t="n"/>
+      <c r="E56" s="14" t="n"/>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G56" s="14" t="inlineStr"/>
-      <c r="H56" s="16" t="inlineStr">
-        <is>
-          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/ hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility</t>
+      <c r="H56" s="15" t="inlineStr">
+        <is>
+          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top benefits and pay DOE. Email resume to: telluridesuper@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
-          <t>July 30-August 5, 2026</t>
+          <t>May 28-June 3, 2026</t>
         </is>
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>47-0000 Construction and Extraction</t>
+          <t>13-0000 Business and Financial Operations</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr"/>
       <c r="D57" s="14" t="n"/>
       <c r="E57" s="14" t="n"/>
-      <c r="F57" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F57" s="14" t="inlineStr"/>
       <c r="G57" s="14" t="inlineStr"/>
-      <c r="H57" s="16" t="inlineStr">
-        <is>
-          <t>Machine Operator Dillsworth Technical Tree Services looking for experienced Excavator and Grapple operator. $35-$40 DOE. 716-713-2983</t>
+      <c r="H57" s="15" t="inlineStr">
+        <is>
+          <t>Wedding &amp; Special-Events Coordinator Telluride Ski &amp; Golf is seeking a detail-oriented, energetic Wedding &amp; Special Events Coordinator to join our team! For full details on compensation, benefits, and to apply, please visit www. tellurideskiresort.com/employment or reach out to Rae Perry at rperry@t</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>July 30-August 5, 2026</t>
+          <t>May 28-June 3, 2026</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>53-0000 Transportation and Material Moving</t>
+          <t>15-0000 Computer and Mathematical</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr"/>
@@ -3277,14 +3712,1892 @@
       <c r="E58" s="14" t="n"/>
       <c r="F58" s="14" t="inlineStr"/>
       <c r="G58" s="14" t="inlineStr"/>
-      <c r="H58" s="16" t="inlineStr">
+      <c r="H58" s="15" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer &amp; Manager of Information Technology San Miguel Power Association, Inc. is seeking to fill a Chief Financial Officer and Manager of IT to report out of our Nucla or Ridgway office location. Please visit our website for full job details and application. www.smpa.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>May 28-June 3, 2026</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>17-0000 Architecture and Engineering</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>$24.00-$26.00/hour; $20.00-$22.50/hour; $24.00-$34.00/hour; $19.06-$20.00/hour; $19.50-$21.00/hour; $22.00-$24.00/hour; $22.95/hour; $19.82/hour; $30.00/hour; $22.28/hour; $13.50/hour; $11.79/hour</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="n">
+        <v>24523</v>
+      </c>
+      <c r="E59" s="16" t="n">
+        <v>70720</v>
+      </c>
+      <c r="F59" s="14" t="inlineStr"/>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="inlineStr">
+        <is>
+          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* We›re Hiring: Night Auditor (Season- al/$24-$26/hr), Front Desk Agent ($22.95/hr), Reservations Agent ($20-$22.50/hr), Bell/Valet (Seasonal/$19.82/hr + tips), Engineer ($25 $30/hr), Concierge (Seasonal/$22.28/hr), Room Attendant (Seasonal/Piece Rate, $24</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>May 28-June 3, 2026</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>23-0000 Legal</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr"/>
+      <c r="D60" s="14" t="n"/>
+      <c r="E60" s="14" t="n"/>
+      <c r="F60" s="14" t="inlineStr"/>
+      <c r="G60" s="14" t="inlineStr"/>
+      <c r="H60" s="15" t="inlineStr">
+        <is>
+          <t>Assistant General Manager Telluride Conference Center is seeking said Evidence of Debt secured by the Deed of Trust, plus attorneys’ fees, the expenses of sale and other items allowed by law, and will issue to the purchaser a Certificate of Purchase, all as provided by law. First Publication 5/21/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>May 28-June 3, 2026</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr"/>
+      <c r="D61" s="14" t="n"/>
+      <c r="E61" s="14" t="n"/>
+      <c r="F61" s="14" t="inlineStr"/>
+      <c r="G61" s="14" t="inlineStr"/>
+      <c r="H61" s="15" t="inlineStr">
+        <is>
+          <t>Norwood Public Schools is looking for a High School Volleyball Coach. Please check out the full job description at https://www.nor- woodk12.org/jobs and «click here for job listings and to apply online.» We will be accepting applications on an ongoing basis until positions are filled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>May 28-June 3, 2026</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>$25.00/hour; $27.00/hour</t>
+        </is>
+      </c>
+      <c r="D62" s="16" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E62" s="16" t="n">
+        <v>56160</v>
+      </c>
+      <c r="F62" s="14" t="inlineStr"/>
+      <c r="G62" s="14" t="inlineStr"/>
+      <c r="H62" s="15" t="inlineStr">
+        <is>
+          <t>Gallery Associate. The Gordon Collection is hiring! Come join our team! Looking for individuals with interest in Southwestern Native American Arts. Part-Time/ Full-Time Summer Sales Associate - Starting at $25/hour - based on hourly + Commission. YearRound Gallery Associate position to include websi</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>May 28-June 3, 2026</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>$23.00-$40.00/hour; $158,000.00/year</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="n">
+        <v>47840</v>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>158000</v>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr"/>
+      <c r="H63" s="15" t="inlineStr">
+        <is>
+          <t>Telluride Whole Health is seeking a Medical Assistant or RN. Parttime with the potential for full-time. $23-40/hr DOE. Call 970-239-8674 to apply. � THE TELLURIDE TIMES WEEK OF MAY 28-JUNE 3, 2026 CLASSIFIEDS A39 Join our one-of-a-kind team! Open roles in Guest Services, F&amp;B, Culinary, Housekeeping,</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>May 28-June 3, 2026</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>$18.00-$23.00/hour</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>47840</v>
+      </c>
+      <c r="F64" s="14" t="inlineStr"/>
+      <c r="G64" s="14" t="inlineStr"/>
+      <c r="H64" s="15" t="inlineStr">
+        <is>
+          <t>Guest Services, Drivers, Housepersons Bear Creek Lodge is hiring for several positions: guest services, drivers, and housepersons ($18-$23/hr). Housing opportunities available. View job descriptions and apply online at telluridelodging. com/careers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>May 28-June 3, 2026</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>$24.00-$27.00/hour; $70,000.00/year</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="n">
+        <v>49920</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F65" s="14" t="inlineStr"/>
+      <c r="G65" s="14" t="inlineStr"/>
+      <c r="H65" s="15" t="inlineStr">
+        <is>
+          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/ hr for part-time, $60-$70k/year for full-time depending on qualifications and schedule flexibili</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>June 4-10, 2026</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr"/>
+      <c r="D66" s="14" t="n"/>
+      <c r="E66" s="14" t="n"/>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr"/>
+      <c r="H66" s="15" t="inlineStr">
+        <is>
+          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top benefits and pay DOE. Email resume to: telluridesuper@ gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>June 4-10, 2026</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>$65,000.00/year</t>
+        </is>
+      </c>
+      <c r="D67" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E67" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="F67" s="14" t="inlineStr"/>
+      <c r="G67" s="14" t="inlineStr"/>
+      <c r="H67" s="15" t="inlineStr">
+        <is>
+          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>June 4-10, 2026</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>$30.00/hour; $20.00/hour; $25.00/hour</t>
+        </is>
+      </c>
+      <c r="D68" s="16" t="n">
+        <v>41600</v>
+      </c>
+      <c r="E68" s="16" t="n">
+        <v>62400</v>
+      </c>
+      <c r="F68" s="14" t="inlineStr"/>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H68" s="15" t="inlineStr">
+        <is>
+          <t>Lumiere by Dunton/Dunton Kitchen is hiring: Join our 5* hotel &amp; restaurant! *housing available* Maintenance Tech (FT $30hr +benefits), PM Bellman ($20hr FT/PT), PM Concierge ($25hr). Dunton Kitchen: Dining Room Manager, Lead Bartender, PM Server, PM Line Cook ($25+hr), AM Prep Cook ($23+hr), Breakfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>June 4-10, 2026</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>15-0000 Computer and Mathematical</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr"/>
+      <c r="D69" s="14" t="n"/>
+      <c r="E69" s="14" t="n"/>
+      <c r="F69" s="14" t="inlineStr"/>
+      <c r="G69" s="14" t="inlineStr"/>
+      <c r="H69" s="15" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer &amp; Manager of Information Technology San Miguel Power Association, Inc. is seeking to fill a Chief Financial Officer and Manager of IT to report out of our Nucla or Ridgway office location. Please visit our website for full job details and application. www. smpa.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>June 4-10, 2026</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>$25.00/hour; $27.00/hour</t>
+        </is>
+      </c>
+      <c r="D70" s="16" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>56160</v>
+      </c>
+      <c r="F70" s="14" t="inlineStr"/>
+      <c r="G70" s="14" t="inlineStr"/>
+      <c r="H70" s="15" t="inlineStr">
+        <is>
+          <t>Gallery Associate. The Gordon Collection is hiring! Come join our team! Looking for individuals with interest in Southwestern Native American Arts. Part-Time/Full-Time Summer Sales Associate - Starting at $25/hour - based on hourly + Commission. Year-Round Gallery Associate position to include websi</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>June 4-10, 2026</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>$23.00-$40.00/hour</t>
+        </is>
+      </c>
+      <c r="D71" s="16" t="n">
+        <v>47840</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>83200</v>
+      </c>
+      <c r="F71" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr"/>
+      <c r="H71" s="15" t="inlineStr">
+        <is>
+          <t>Telluride Whole Health is seeking a Medical Assistant or RN. Parttime or full-time. $23-40/hr DOE. Call 970-239-8674 to apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>June 4-10, 2026</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>$24.00-$27.00/hour; $70,000.00/year</t>
+        </is>
+      </c>
+      <c r="D72" s="16" t="n">
+        <v>49920</v>
+      </c>
+      <c r="E72" s="16" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F72" s="14" t="inlineStr"/>
+      <c r="G72" s="14" t="inlineStr"/>
+      <c r="H72" s="15" t="inlineStr">
+        <is>
+          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/ hr for part-time, $60-$70k/year for full-time depending on qualifications and schedule flexibili</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>June 4-10, 2026</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>53-0000 Transportation and Material Moving</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr"/>
+      <c r="D73" s="14" t="n"/>
+      <c r="E73" s="14" t="n"/>
+      <c r="F73" s="14" t="inlineStr"/>
+      <c r="G73" s="14" t="inlineStr"/>
+      <c r="H73" s="15" t="inlineStr">
+        <is>
+          <t>Delivery Driver Blue Grouse Bread hiring delivery driver for Monday and Wednesday route. Email resume to bluegrousebread@gmail. com for more info.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="14" t="inlineStr">
+        <is>
+          <t>June 18-24, 2026</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>$65,000.00/year</t>
+        </is>
+      </c>
+      <c r="D74" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="F74" s="14" t="inlineStr"/>
+      <c r="G74" s="14" t="inlineStr"/>
+      <c r="H74" s="15" t="inlineStr">
+        <is>
+          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>June 18-24, 2026</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr"/>
+      <c r="D75" s="14" t="n"/>
+      <c r="E75" s="14" t="n"/>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr"/>
+      <c r="H75" s="15" t="inlineStr">
+        <is>
+          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top benefits and pay DOE. Email resume to: telluridesuper@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>June 18-24, 2026</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>17-0000 Architecture and Engineering</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>$26.00-$28.00/hour; $20.00-$22.50/hour; $25.00-$30.00/hour; $24.00-$34.00/hour; $22.00-$24.00/hour; $12.14-$14.00/hour; $12.14-$14.00/hour; $19.06/hour; $13.39/hour; $11.79/hour</t>
+        </is>
+      </c>
+      <c r="D76" s="16" t="n">
+        <v>24523</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>70720</v>
+      </c>
+      <c r="F76" s="14" t="inlineStr"/>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H76" s="15" t="inlineStr">
+        <is>
+          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Night Auditor (Seasonal/$26-$28/hr), Reservations Agent ($20-$22.50/hr), Engineer ($25-$30/hr), Room Attendant (Seasonal/Piece Rate, $24-$34/hr), AM/ PM Houseperson (Seasonal/$19.06/ hr), Public Area Attendant (Seasonal/$19.06/hr), Host (Seasonal/$13.39/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="14" t="inlineStr">
+        <is>
+          <t>June 18-24, 2026</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>$15,000.00-$25,000.00/year</t>
+        </is>
+      </c>
+      <c r="D77" s="16" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E77" s="16" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G77" s="14" t="inlineStr"/>
+      <c r="H77" s="15" t="inlineStr">
+        <is>
+          <t>Junior Nordic Director and Head Coach TSSC seeking experienced Nordic Director and Head Coach. Part time Oct-Mar. 15K-25K DOE. Email nordic@tssc.org https://tssc.org/wanted-nordicdirector/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>June 18-24, 2026</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>$23.00-$40.00/hour</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="n">
+        <v>47840</v>
+      </c>
+      <c r="E78" s="16" t="n">
+        <v>83200</v>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr"/>
+      <c r="H78" s="15" t="inlineStr">
+        <is>
+          <t>Telluride Whole Health is seeking a Medical Assistant or RN. Part-time or full-time. $23-40/hr DOE. Call 970239-8674 to apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>June 18-24, 2026</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="inlineStr">
+        <is>
+          <t>$19.00-$21.00/hour; $19.00-$20.00/hour; $50.00/hour</t>
+        </is>
+      </c>
+      <c r="D79" s="16" t="n">
+        <v>39520</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>104000</v>
+      </c>
+      <c r="F79" s="14" t="inlineStr"/>
+      <c r="G79" s="14" t="inlineStr"/>
+      <c r="H79" s="15" t="inlineStr">
+        <is>
+          <t>1099 Handyman/Maintenance Runner needed. $50/hr. Experience required. Send resume to vendors@avantstay.com � A46 CLASSIFIEDS THE TELLURIDE TIMES WEEK OF JUNE 18-24, 2026 NOW HIRING: Dental Assistant (Will Train) Full-Time | $19–$21/hour While previous dental or healthcare experience is preferred, we</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>June 18-24, 2026</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr"/>
+      <c r="D80" s="14" t="n"/>
+      <c r="E80" s="14" t="n"/>
+      <c r="F80" s="14" t="inlineStr"/>
+      <c r="G80" s="14" t="inlineStr"/>
+      <c r="H80" s="15" t="inlineStr">
+        <is>
+          <t>Paddle Board Guide Telluride Outside is hiring a Paddle Board Guide for the summer. Please contact reservations@tellurideoutside.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>June 18-24, 2026</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C81" s="14" t="inlineStr"/>
+      <c r="D81" s="14" t="n"/>
+      <c r="E81" s="14" t="n"/>
+      <c r="F81" s="14" t="inlineStr"/>
+      <c r="G81" s="14" t="inlineStr"/>
+      <c r="H81" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enchanted Forest Toy Shoppe is hiring! Our fast-paced, fun shoppe needs a committed and energetic person to join our team! 20 hours to start. Retail experience preferred. Yearround commitment a plus. Competitive wages and immediate start. Please send us a brief letter of interest and your resume to </t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>June 18-24, 2026</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="inlineStr">
+        <is>
+          <t>$24.00-$27.00/hour; $70,000.00/year</t>
+        </is>
+      </c>
+      <c r="D82" s="16" t="n">
+        <v>49920</v>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F82" s="14" t="inlineStr"/>
+      <c r="G82" s="14" t="inlineStr"/>
+      <c r="H82" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for full-time depending on qualifications and schedule flexibil- </t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>June 18-24, 2026</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>49-0000 Installation, Maintenance, and Repair</t>
+        </is>
+      </c>
+      <c r="C83" s="14" t="inlineStr"/>
+      <c r="D83" s="14" t="n"/>
+      <c r="E83" s="14" t="n"/>
+      <c r="F83" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G83" s="14" t="inlineStr"/>
+      <c r="H83" s="15" t="inlineStr">
+        <is>
+          <t>Farmers Water Development Co. full-time, year-round Ditch Rider. Equipment/CDL preferred. Pay DOE. Send resume to farmerswdc@yahoo.com. Deadline 6/26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>June 18-24, 2026</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>53-0000 Transportation and Material Moving</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>$22.00/hour; $33.00/hour</t>
+        </is>
+      </c>
+      <c r="D84" s="16" t="n">
+        <v>45760</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>68640</v>
+      </c>
+      <c r="F84" s="14" t="inlineStr"/>
+      <c r="G84" s="14" t="inlineStr"/>
+      <c r="H84" s="15" t="inlineStr">
+        <is>
+          <t>DESTINATION SYSTEMS dba Telluride Express HIRING CDL and Non CDL Drivers LIVE IN THE MOUNTAINS. DRIVE WITH PURPOSE. GET PAID WELL. Destination Systems is NOW HIRING drivers in Telluride &amp; Mountain Village! Whether you want full-time work or just extra income a few days a week, we have flexible sched</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C85" s="14" t="inlineStr"/>
+      <c r="D85" s="14" t="n"/>
+      <c r="E85" s="14" t="n"/>
+      <c r="F85" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G85" s="14" t="inlineStr"/>
+      <c r="H85" s="15" t="inlineStr">
+        <is>
+          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top beneﬁts and pay DOE. Email resume to: telluridesuper@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>$65,000.00/year</t>
+        </is>
+      </c>
+      <c r="D86" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="F86" s="14" t="inlineStr"/>
+      <c r="G86" s="14" t="inlineStr"/>
+      <c r="H86" s="15" t="inlineStr">
+        <is>
+          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>13-0000 Business and Financial Operations</t>
+        </is>
+      </c>
+      <c r="C87" s="14" t="inlineStr">
+        <is>
+          <t>$26.00-$28.00/hour; $20.00-$22.50/hour; $23.00-$25.00/hour; $24.00-$34.00/hour; $22.00-$24.00/hour; $12.14-$14.00/hour; $12.14-$14.00/hour; $19.06/hour; $13.39/hour; $11.79/hour</t>
+        </is>
+      </c>
+      <c r="D87" s="16" t="n">
+        <v>24523</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>70720</v>
+      </c>
+      <c r="F87" s="14" t="inlineStr"/>
+      <c r="G87" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H87" s="15" t="inlineStr">
+        <is>
+          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Night Auditor (Seasonal/$26-$28/hr), Reservations Agent ($20- $22.50/hr), Expo - Seasonal (EXPOS)/Service Worker ($23-$25/hr), Room Attendant (Seasonal/Piece Rate, $24-$34/ hr), AM/PM Houseperson (Seasonal/$19.06/hr), Public Area Attendant (Seasonal/$19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="inlineStr"/>
+      <c r="D88" s="14" t="n"/>
+      <c r="E88" s="14" t="n"/>
+      <c r="F88" s="14" t="inlineStr"/>
+      <c r="G88" s="14" t="inlineStr"/>
+      <c r="H88" s="15" t="inlineStr">
+        <is>
+          <t>Rainbow Preschool is seeking a loving and dedicated PT Preschool Teacher to join our nurturing early childhood education program. Experience in ECE preferred. We oﬀer a supportive, friendly work environment, opportunities for professional development and competitive pay. Please email resume to rainb</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="inlineStr">
+        <is>
+          <t>$20.00-$22.00/hour; $19.00-$20.00/hour; $19.00-$21.00/hour; $25.00/hour; $18.00/hour; $35.00/hour; $158,000.00/year</t>
+        </is>
+      </c>
+      <c r="D89" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>158000</v>
+      </c>
+      <c r="F89" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G89" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H89" s="15" t="inlineStr">
+        <is>
+          <t>Lumiere by Dunton Come join our 5* hotel and restaurant! Housing available PM Bell PT ($20hr +tips), PM Concierge (PT $25hr +tips), Bartender ($18hr +tips or $35hr), PM Server ($18 +tips or $35hr), AM Server ($22hr +tips). Email: famaral@lumieretelluride.com ■ $75 caviar-topped tots. A day’s pay wor</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="inlineStr"/>
+      <c r="D90" s="14" t="n"/>
+      <c r="E90" s="14" t="n"/>
+      <c r="F90" s="14" t="inlineStr"/>
+      <c r="G90" s="14" t="inlineStr"/>
+      <c r="H90" s="15" t="inlineStr">
+        <is>
+          <t>Paddle Board Guide Telluride Outside is hiring a Paddle Board Guide for the summer. Please contact reservations@tellurideoutside.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B91" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C91" s="14" t="inlineStr"/>
+      <c r="D91" s="14" t="n"/>
+      <c r="E91" s="14" t="n"/>
+      <c r="F91" s="14" t="inlineStr"/>
+      <c r="G91" s="14" t="inlineStr"/>
+      <c r="H91" s="15" t="inlineStr">
+        <is>
+          <t>Enchanted Forest Toy Shoppe is hiring! Our fast-paced, fun shoppe needs a committed and energetic person to join our team! 20 hours to start. Retail experience preferred. Year-round commitment a plus. Competitive wages and immediate start. Please send us a brief letter of interest and your resume to</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>$24.00-$27.00/hour; $70,000.00/year</t>
+        </is>
+      </c>
+      <c r="D92" s="16" t="n">
+        <v>49920</v>
+      </c>
+      <c r="E92" s="16" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F92" s="14" t="inlineStr"/>
+      <c r="G92" s="14" t="inlineStr"/>
+      <c r="H92" s="15" t="inlineStr">
+        <is>
+          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B93" s="14" t="inlineStr">
+        <is>
+          <t>49-0000 Installation, Maintenance, and Repair</t>
+        </is>
+      </c>
+      <c r="C93" s="14" t="inlineStr"/>
+      <c r="D93" s="14" t="n"/>
+      <c r="E93" s="14" t="n"/>
+      <c r="F93" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G93" s="14" t="inlineStr"/>
+      <c r="H93" s="15" t="inlineStr">
+        <is>
+          <t>Farmers Water Development Co. full-time, year-round Ditch Rider. Equipment/CDL preferred. Pay DOE. Send resume to farmerswdc@yahoo.com. Deadline 6/26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>53-0000 Transportation and Material Moving</t>
+        </is>
+      </c>
+      <c r="C94" s="14" t="inlineStr">
+        <is>
+          <t>$22.00/hour; $33.00/hour</t>
+        </is>
+      </c>
+      <c r="D94" s="16" t="n">
+        <v>45760</v>
+      </c>
+      <c r="E94" s="16" t="n">
+        <v>68640</v>
+      </c>
+      <c r="F94" s="14" t="inlineStr"/>
+      <c r="G94" s="14" t="inlineStr"/>
+      <c r="H94" s="15" t="inlineStr">
+        <is>
+          <t>DESTINATION SYSTEMS dba Telluride Express HIRING CDL and Non CDL Drivers LIVE IN THE MOUNTAINS. DRIVE WITH PURPOSE. GET PAID WELL. Destination Systems is NOW HIRING drivers in • Page A45 Telluride &amp; Mountain Village! Whether you want full-time work or just extra income a few days a week, we have ﬂex</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="14" t="inlineStr">
+        <is>
+          <t>July 2-8, 2026</t>
+        </is>
+      </c>
+      <c r="B95" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C95" s="14" t="inlineStr"/>
+      <c r="D95" s="14" t="n"/>
+      <c r="E95" s="14" t="n"/>
+      <c r="F95" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G95" s="14" t="inlineStr"/>
+      <c r="H95" s="15" t="inlineStr">
+        <is>
+          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top beneﬁts and pay DOE. Email resume to: telluridesuper@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>July 2-8, 2026</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C96" s="14" t="inlineStr">
+        <is>
+          <t>$65,000.00/year</t>
+        </is>
+      </c>
+      <c r="D96" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E96" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="F96" s="14" t="inlineStr"/>
+      <c r="G96" s="14" t="inlineStr"/>
+      <c r="H96" s="15" t="inlineStr">
+        <is>
+          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="14" t="inlineStr">
+        <is>
+          <t>July 2-8, 2026</t>
+        </is>
+      </c>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
+        </is>
+      </c>
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>$24.00-$27.00/hour; $20.00-$22.00/hour; $19.00-$21.00/hour; $19.00-$20.00/hour; $70,000.00/year</t>
+        </is>
+      </c>
+      <c r="D97" s="16" t="n">
+        <v>39520</v>
+      </c>
+      <c r="E97" s="16" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F97" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G97" s="14" t="inlineStr"/>
+      <c r="H97" s="15" t="inlineStr">
+        <is>
+          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="14" t="inlineStr">
+        <is>
+          <t>July 2-8, 2026</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="inlineStr">
+        <is>
+          <t>$20.00/hour; $25.00/hour; $18.00/hour; $35.00/hour; $22.00/hour</t>
+        </is>
+      </c>
+      <c r="D98" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E98" s="16" t="n">
+        <v>72800</v>
+      </c>
+      <c r="F98" s="14" t="inlineStr"/>
+      <c r="G98" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H98" s="15" t="inlineStr">
+        <is>
+          <t>Lumiere by Dunton Come join our 5* hotel and restaurant! Housing available. PM Bell PT ($20hr +tips), PM Concierge (PT $25hr +tips), Bartender ($18hr +tips or $35hr), PM Server ($18 +tips or $35hr), AM Server ($22hr +tips). Email: famaral@lumieretelluride.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="14" t="inlineStr">
+        <is>
+          <t>July 2-8, 2026</t>
+        </is>
+      </c>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="C99" s="14" t="inlineStr">
+        <is>
+          <t>$20.00-$22.50/hour; $24.00-$34.00/hour</t>
+        </is>
+      </c>
+      <c r="D99" s="16" t="n">
+        <v>41600</v>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>70720</v>
+      </c>
+      <c r="F99" s="14" t="inlineStr"/>
+      <c r="G99" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H99" s="15" t="inlineStr">
+        <is>
+          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Reservations Agent ($20-$22.50/hr), Room Attendant (Seasonal/Piece Rate, $24-$34/hr). We oﬀer amazing beneﬁts and a really fun, creative and innovative work atmosphere. Season Ski Pass, Employee Meals, Employee Shuttle, Discounted Room Rates, Discounts a</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="14" t="inlineStr">
+        <is>
+          <t>July 2-8, 2026</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+      <c r="C100" s="14" t="inlineStr"/>
+      <c r="D100" s="14" t="n"/>
+      <c r="E100" s="14" t="n"/>
+      <c r="F100" s="14" t="inlineStr"/>
+      <c r="G100" s="14" t="inlineStr"/>
+      <c r="H100" s="15" t="inlineStr">
+        <is>
+          <t>Paddle Board Guide Telluride Outside is hiring a Paddle Board Guide for the summer. Please contact reservations@tellurideoutside.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="14" t="inlineStr">
+        <is>
+          <t>July 2-8, 2026</t>
+        </is>
+      </c>
+      <c r="B101" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C101" s="14" t="inlineStr"/>
+      <c r="D101" s="14" t="n"/>
+      <c r="E101" s="14" t="n"/>
+      <c r="F101" s="14" t="inlineStr"/>
+      <c r="G101" s="14" t="inlineStr"/>
+      <c r="H101" s="15" t="inlineStr">
+        <is>
+          <t>Enchanted Forest Toy Shoppe is hiring! Our fast-paced, fun shoppe needs a committed and energetic person to join our team! 20 hours to start. Retail experience preferred. Year-round commitment a plus. Competitive wages and immediate start. Please send us a brief letter of interest and your resume to</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="14" t="inlineStr">
+        <is>
+          <t>July 9-15, 2026</t>
+        </is>
+      </c>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>$65,000.00/year</t>
+        </is>
+      </c>
+      <c r="D102" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E102" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="F102" s="14" t="inlineStr"/>
+      <c r="G102" s="14" t="inlineStr"/>
+      <c r="H102" s="15" t="inlineStr">
+        <is>
+          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="14" t="inlineStr">
+        <is>
+          <t>July 9-15, 2026</t>
+        </is>
+      </c>
+      <c r="B103" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C103" s="14" t="inlineStr"/>
+      <c r="D103" s="14" t="n"/>
+      <c r="E103" s="14" t="n"/>
+      <c r="F103" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G103" s="14" t="inlineStr"/>
+      <c r="H103" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Norwood Public Schools is looking for a Director of Technology. Please check out the full job description at https://www.norwoodk12.org/jobs and “Click here for job listings and to apply online.” We will be accepting applications on an ongoing basis until positions are ﬁlled. ■ Who says a vegetable </t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="14" t="inlineStr">
+        <is>
+          <t>July 9-15, 2026</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C104" s="14" t="inlineStr"/>
+      <c r="D104" s="14" t="n"/>
+      <c r="E104" s="14" t="n"/>
+      <c r="F104" s="14" t="inlineStr"/>
+      <c r="G104" s="14" t="inlineStr"/>
+      <c r="H104" s="15" t="inlineStr">
+        <is>
+          <t>Telluride School District R-1 Request for Proposal for Custodial Services The Telluride School District (TSD) is requesting proposals for custodial services to be performed at the following school building facilities: Telluride Elementary School; Telluride Intermediate School; and Telluride Middle/H</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="14" t="inlineStr">
+        <is>
+          <t>July 9-15, 2026</t>
+        </is>
+      </c>
+      <c r="B105" s="14" t="inlineStr">
+        <is>
+          <t>33-0000 Protective Service</t>
+        </is>
+      </c>
+      <c r="C105" s="14" t="inlineStr">
+        <is>
+          <t>$20.00/hour; $25.00/hour; $18.00/hour; $35.00/hour</t>
+        </is>
+      </c>
+      <c r="D105" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>72800</v>
+      </c>
+      <c r="F105" s="14" t="inlineStr"/>
+      <c r="G105" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H105" s="15" t="inlineStr">
+        <is>
+          <t>Lumiere by Dunton Come join our 5* hotel and restaurant! Housing available. PM Bell PT ($20hr +tips), PM Concierge (PT $25hr +tips), Bartender ($18hr +tips or $35hr), PM Server ($18 +tips or $35hr), San Miguel County is Hiring! The following positions are full-time, yearround and include competitive</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="14" t="inlineStr">
+        <is>
+          <t>July 9-15, 2026</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="C106" s="14" t="inlineStr">
+        <is>
+          <t>$22.00/hour</t>
+        </is>
+      </c>
+      <c r="D106" s="16" t="n">
+        <v>45760</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>45760</v>
+      </c>
+      <c r="F106" s="14" t="inlineStr"/>
+      <c r="G106" s="14" t="inlineStr"/>
+      <c r="H106" s="15" t="inlineStr">
+        <is>
+          <t>AM Server ($22hr +tips). Email: famaral@lumieretelluride.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="14" t="inlineStr">
+        <is>
+          <t>July 9-15, 2026</t>
+        </is>
+      </c>
+      <c r="B107" s="14" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="C107" s="14" t="inlineStr">
+        <is>
+          <t>$20.00-$22.50/hour; $24.00-$34.00/hour</t>
+        </is>
+      </c>
+      <c r="D107" s="16" t="n">
+        <v>41600</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>70720</v>
+      </c>
+      <c r="F107" s="14" t="inlineStr"/>
+      <c r="G107" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H107" s="15" t="inlineStr">
+        <is>
+          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Reservations Agent ($20-$22.50/ hr), Room Attendant (Seasonal/ Piece Rate, $24-$34/hr). We oﬀer amazing beneﬁts and a really fun, creative and innovative work atmosphere. Season Ski Pass, Employee Meals, Employee Shuttle, Discounted Room Rates, Discounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="14" t="inlineStr">
+        <is>
+          <t>July 9-15, 2026</t>
+        </is>
+      </c>
+      <c r="B108" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C108" s="14" t="inlineStr">
+        <is>
+          <t>$24.00-$27.00/hour; $70,000.00/year</t>
+        </is>
+      </c>
+      <c r="D108" s="16" t="n">
+        <v>49920</v>
+      </c>
+      <c r="E108" s="16" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F108" s="14" t="inlineStr"/>
+      <c r="G108" s="14" t="inlineStr"/>
+      <c r="H108" s="15" t="inlineStr">
+        <is>
+          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/ hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="14" t="inlineStr">
+        <is>
+          <t>July 9-15, 2026</t>
+        </is>
+      </c>
+      <c r="B109" s="14" t="inlineStr">
+        <is>
+          <t>43-0000 Office and Administrative Support</t>
+        </is>
+      </c>
+      <c r="C109" s="14" t="inlineStr"/>
+      <c r="D109" s="14" t="n"/>
+      <c r="E109" s="14" t="n"/>
+      <c r="F109" s="14" t="inlineStr"/>
+      <c r="G109" s="14" t="inlineStr"/>
+      <c r="H109" s="15" t="inlineStr">
+        <is>
+          <t>The Farmers’ Water Development Company (FWDC) has received written request to replace a lost, destroyed or wrongfully taken share certificate #887 currently issued in the name A.F. Newans M.D.,C.P.. Unless written notice of objection to the issuance of a replacement share certificate is filed with F</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="14" t="inlineStr">
+        <is>
+          <t>July 23-29, 2026</t>
+        </is>
+      </c>
+      <c r="B110" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C110" s="14" t="inlineStr"/>
+      <c r="D110" s="14" t="n"/>
+      <c r="E110" s="14" t="n"/>
+      <c r="F110" s="14" t="inlineStr"/>
+      <c r="G110" s="14" t="inlineStr"/>
+      <c r="H110" s="15" t="inlineStr">
+        <is>
+          <t>Norwood Public Schools is looking for a Director of Technology. Please check out the full job description at https://www.norwoodk12.org/jobs and “Click here for job listings and to apply online.” We will be accepting applications on an ongoing basis until positions are ﬁlled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="14" t="inlineStr">
+        <is>
+          <t>July 23-29, 2026</t>
+        </is>
+      </c>
+      <c r="B111" s="14" t="inlineStr">
+        <is>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C111" s="14" t="inlineStr"/>
+      <c r="D111" s="14" t="n"/>
+      <c r="E111" s="14" t="n"/>
+      <c r="F111" s="14" t="inlineStr"/>
+      <c r="G111" s="14" t="inlineStr"/>
+      <c r="H111" s="15" t="inlineStr">
+        <is>
+          <t>Norwood Public Schools is seeking a 3rd Grade Teacher. Please check out the full job description at https://www.norwoodk12.org/ jobs and “Click here for job listings and to apply online.” We will be ac- cepting applications on an ongoing basis until positions are ﬁlled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="14" t="inlineStr">
+        <is>
+          <t>July 23-29, 2026</t>
+        </is>
+      </c>
+      <c r="B112" s="14" t="inlineStr">
+        <is>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C112" s="14" t="inlineStr"/>
+      <c r="D112" s="14" t="n"/>
+      <c r="E112" s="14" t="n"/>
+      <c r="F112" s="14" t="inlineStr"/>
+      <c r="G112" s="14" t="inlineStr"/>
+      <c r="H112" s="15" t="inlineStr">
+        <is>
+          <t>Rainbow Preschool is seeking a loving and dedicated PT Preschool Teacher to join our nurturing early childhood education program. Experience in ECE preferred. We oﬀer a supportive, friendly work environment, opportunities for professional development and com- petitive pay. Please email resume to rai</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="14" t="inlineStr">
+        <is>
+          <t>July 23-29, 2026</t>
+        </is>
+      </c>
+      <c r="B113" s="14" t="inlineStr">
+        <is>
+          <t>33-0000 Protective Service</t>
+        </is>
+      </c>
+      <c r="C113" s="14" t="inlineStr">
+        <is>
+          <t>$24.00-$27.00/hour; $20.00-$22.00/hour; $70,000.00/year</t>
+        </is>
+      </c>
+      <c r="D113" s="16" t="n">
+        <v>41600</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F113" s="14" t="inlineStr"/>
+      <c r="G113" s="14" t="inlineStr"/>
+      <c r="H113" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scarpe is hiring! Seeking year-round Full-Time and PartTime Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for fulltime depending on qualiﬁcations and schedule ﬂexibility. </t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="14" t="inlineStr">
+        <is>
+          <t>July 23-29, 2026</t>
+        </is>
+      </c>
+      <c r="B114" s="14" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="C114" s="14" t="inlineStr"/>
+      <c r="D114" s="14" t="n"/>
+      <c r="E114" s="14" t="n"/>
+      <c r="F114" s="14" t="inlineStr"/>
+      <c r="G114" s="14" t="inlineStr"/>
+      <c r="H114" s="15" t="inlineStr">
+        <is>
+          <t>Excellent Second Level Oﬃce Suite For Lease / 119 W Colorado Private Oﬃces, Conference Room, Reception Area, Kitchen &amp; Bath, Plus One Dedicated Parking Spot. Immediately available. Inquire at 970-729-1577. Blue Grouse Bread Hiring delivery driver. Fun folks, free bread, beneﬁts after 1 yr. Email res</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="14" t="inlineStr">
+        <is>
+          <t>July 23-29, 2026</t>
+        </is>
+      </c>
+      <c r="B115" s="14" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="C115" s="14" t="inlineStr">
+        <is>
+          <t>$20.00-$22.50/hour; $24.00-$34.00/hour</t>
+        </is>
+      </c>
+      <c r="D115" s="16" t="n">
+        <v>41600</v>
+      </c>
+      <c r="E115" s="16" t="n">
+        <v>70720</v>
+      </c>
+      <c r="F115" s="14" t="inlineStr"/>
+      <c r="G115" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H115" s="15" t="inlineStr">
+        <is>
+          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Reservations Agent ($20-$22.50/ hr), Room Attendant (Seasonal/ Piece Rate, $24-$34/hr). We offer amazing beneﬁts and a really fun, creative and innovative work atmosphere. Season Ski Pass, Employee Meals, Employee Shuttle, Discounted Room Rates, Discount</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="14" t="inlineStr">
+        <is>
+          <t>July 23-29, 2026</t>
+        </is>
+      </c>
+      <c r="B116" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C116" s="14" t="inlineStr">
+        <is>
+          <t>$25.00/hour</t>
+        </is>
+      </c>
+      <c r="D116" s="16" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E116" s="16" t="n">
+        <v>52000</v>
+      </c>
+      <c r="F116" s="14" t="inlineStr"/>
+      <c r="G116" s="14" t="inlineStr"/>
+      <c r="H116" s="15" t="inlineStr">
+        <is>
+          <t>The Telluride Toggery is seeking a salesperson to join our team! Come and work at Telluride’s lon- • Week of July 23-29, 2026 gest running clothing store located in the heart of downtown Telluride. Pay is based upon experience starting at $25 hour for full-time employment. Apply in person or contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="14" t="inlineStr">
+        <is>
+          <t>July 30-August 5, 2026</t>
+        </is>
+      </c>
+      <c r="B117" s="14" t="inlineStr">
+        <is>
+          <t>19-0000 Life, Physical, and Social Science</t>
+        </is>
+      </c>
+      <c r="C117" s="14" t="inlineStr"/>
+      <c r="D117" s="14" t="n"/>
+      <c r="E117" s="14" t="n"/>
+      <c r="F117" s="14" t="inlineStr"/>
+      <c r="G117" s="14" t="inlineStr"/>
+      <c r="H117" s="15" t="inlineStr">
+        <is>
+          <t>Service Planner I-V San Miguel Power Association, Inc. (SMPA) is seeking to ﬁll the position of Service Planner I-V out of our Ridgway oﬃce location. To view the complete job posting, beneﬁts, compensation, and howto apply, please visit our website www.smpa.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="14" t="inlineStr">
+        <is>
+          <t>July 30-August 5, 2026</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="inlineStr">
+        <is>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C118" s="14" t="inlineStr"/>
+      <c r="D118" s="14" t="n"/>
+      <c r="E118" s="14" t="n"/>
+      <c r="F118" s="14" t="inlineStr"/>
+      <c r="G118" s="14" t="inlineStr"/>
+      <c r="H118" s="15" t="inlineStr">
+        <is>
+          <t>Norwood Public Schools is seeking a 3rd Grade Teacher. Please check out the full job description at https://www.norwoodk12.org/ jobs and “Click here for job listings and to apply online.” We will be accepting applications on an ongoing basis until positions are ﬁlled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="14" t="inlineStr">
+        <is>
+          <t>July 30-August 5, 2026</t>
+        </is>
+      </c>
+      <c r="B119" s="14" t="inlineStr">
+        <is>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C119" s="14" t="inlineStr"/>
+      <c r="D119" s="14" t="n"/>
+      <c r="E119" s="14" t="n"/>
+      <c r="F119" s="14" t="inlineStr"/>
+      <c r="G119" s="14" t="inlineStr"/>
+      <c r="H119" s="15" t="inlineStr">
+        <is>
+          <t>Rainbow Preschool is seeking a loving and dedicated PT Preschool Teacher to join our nurturing early childhood education program. Experience in ECE preferred. We oﬀer a supportive, friendly work environment, opportunities for professional development and competitive pay. Please email resume to rainb</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="14" t="inlineStr">
+        <is>
+          <t>July 30-August 5, 2026</t>
+        </is>
+      </c>
+      <c r="B120" s="14" t="inlineStr">
+        <is>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
+        </is>
+      </c>
+      <c r="C120" s="14" t="inlineStr">
+        <is>
+          <t>$20.00-$22.50/hour; $24.00-$34.00/hour; $20.00-$22.00/hour; $19.00-$20.00/hour; $26.00/hour; $22.95/hour; $19.82/hour</t>
+        </is>
+      </c>
+      <c r="D120" s="16" t="n">
+        <v>39520</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>70720</v>
+      </c>
+      <c r="F120" s="14" t="inlineStr"/>
+      <c r="G120" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H120" s="15" t="inlineStr">
+        <is>
+          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Reservations Agent ($20-$22.50/hr), Room Attendant (Seasonal/Piece Rate, $24-$34/hr), Banquet Captain ($23$26/hr), Front Desk Agent/Seasonal ($22.95/hr), Bell Valet/Seasonal ($19.82/hr plus tips ). We oﬀer amazing beneﬁts and a really fun, creative and i</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="14" t="inlineStr">
+        <is>
+          <t>July 30-August 5, 2026</t>
+        </is>
+      </c>
+      <c r="B121" s="14" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+      <c r="C121" s="14" t="inlineStr">
+        <is>
+          <t>$21.00-$23.00/hour</t>
+        </is>
+      </c>
+      <c r="D121" s="16" t="n">
+        <v>43680</v>
+      </c>
+      <c r="E121" s="16" t="n">
+        <v>47840</v>
+      </c>
+      <c r="F121" s="14" t="inlineStr"/>
+      <c r="G121" s="14" t="inlineStr"/>
+      <c r="H121" s="15" t="inlineStr">
+        <is>
+          <t>Guest Services Associate PT &amp; FT Guest Service positions available at Bear Creek Lodge. $21-$23/hour. Apply: telluridelodging.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="14" t="inlineStr">
+        <is>
+          <t>July 30-August 5, 2026</t>
+        </is>
+      </c>
+      <c r="B122" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C122" s="14" t="inlineStr">
+        <is>
+          <t>$25.00/hour</t>
+        </is>
+      </c>
+      <c r="D122" s="16" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E122" s="16" t="n">
+        <v>52000</v>
+      </c>
+      <c r="F122" s="14" t="inlineStr"/>
+      <c r="G122" s="14" t="inlineStr"/>
+      <c r="H122" s="15" t="inlineStr">
+        <is>
+          <t>The Telluride Toggery is seeking a salesperson to join our team! Come and work at Telluride’s longest running clothing store located in the heart of downtown Telluride. • Page A53 Pay is based upon experience starting at $25 hour for full-time employment. Apply in person or contact Wendy at (970)728</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="14" t="inlineStr">
+        <is>
+          <t>July 30-August 5, 2026</t>
+        </is>
+      </c>
+      <c r="B123" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C123" s="14" t="inlineStr">
+        <is>
+          <t>$24.00-$27.00/hour; $70,000.00/year</t>
+        </is>
+      </c>
+      <c r="D123" s="16" t="n">
+        <v>49920</v>
+      </c>
+      <c r="E123" s="16" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F123" s="14" t="inlineStr"/>
+      <c r="G123" s="14" t="inlineStr"/>
+      <c r="H123" s="15" t="inlineStr">
+        <is>
+          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/ hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="14" t="inlineStr">
+        <is>
+          <t>July 30-August 5, 2026</t>
+        </is>
+      </c>
+      <c r="B124" s="14" t="inlineStr">
+        <is>
+          <t>47-0000 Construction and Extraction</t>
+        </is>
+      </c>
+      <c r="C124" s="14" t="inlineStr"/>
+      <c r="D124" s="14" t="n"/>
+      <c r="E124" s="14" t="n"/>
+      <c r="F124" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G124" s="14" t="inlineStr"/>
+      <c r="H124" s="15" t="inlineStr">
+        <is>
+          <t>Machine Operator Dillsworth Technical Tree Services looking for experienced Excavator and Grapple operator. $35-$40 DOE. 716-713-2983</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="14" t="inlineStr">
+        <is>
+          <t>July 30-August 5, 2026</t>
+        </is>
+      </c>
+      <c r="B125" s="14" t="inlineStr">
+        <is>
+          <t>53-0000 Transportation and Material Moving</t>
+        </is>
+      </c>
+      <c r="C125" s="14" t="inlineStr"/>
+      <c r="D125" s="14" t="n"/>
+      <c r="E125" s="14" t="n"/>
+      <c r="F125" s="14" t="inlineStr"/>
+      <c r="G125" s="14" t="inlineStr"/>
+      <c r="H125" s="15" t="inlineStr">
         <is>
           <t>Blue Grouse Bread Hiring delivery driver. Fun folks, free bread, beneﬁts after 1 yr. Email resume to bluegrousebread@gmail.com.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H58"/>
+  <autoFilter ref="A4:H125"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3320,7 +5633,7 @@
       </c>
       <c r="B3" s="18" t="inlineStr">
         <is>
-          <t>The printed classified section of six weekly Telluride Times e-editions, from the week of June 18 through the week of July 30, 2026. The week of July 16 was not available. Ads are taken from the HELP WANTED section only.</t>
+          <t>The printed classified section of six weekly Telluride Times e-editions, from the week of April 23 through the week of July 30, 2026. Three weeks were not available: May 14-20, June 11-17, and July 16-22. Ads are taken from the HELP WANTED section only.</t>
         </is>
       </c>
     </row>
@@ -3390,12 +5703,12 @@
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>Limit 3: six weeks in summer</t>
+          <t>Limit 3: spring and summer only</t>
         </is>
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>This covers six consecutive summer editions. Seasonal hiring in a resort economy varies a great deal across the year, so these counts describe summer and should not be read as an annual picture.</t>
+          <t>This covers twelve editions from late April through early August, which spans the quiet shoulder season and the summer peak. Winter hiring is a separate season in a resort economy and is not represented here, so these counts should not be read as an annual picture.</t>
         </is>
       </c>
     </row>

--- a/assets/Housing Study/Job Market/Telluride Times print help-wanted with pay.xlsx
+++ b/assets/Housing Study/Job Market/Telluride Times print help-wanted with pay.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method and limits" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Every ad'!$A$4:$H$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Every ad'!$A$4:$H$176</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -260,12 +260,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </val>
         </ser>
@@ -279,12 +279,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$5:$M$5</f>
+              <f>'Jobs by Category'!$B$5:$R$5</f>
             </numRef>
           </val>
         </ser>
@@ -298,12 +298,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$6:$M$6</f>
+              <f>'Jobs by Category'!$B$6:$R$6</f>
             </numRef>
           </val>
         </ser>
@@ -317,12 +317,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$7:$M$7</f>
+              <f>'Jobs by Category'!$B$7:$R$7</f>
             </numRef>
           </val>
         </ser>
@@ -336,12 +336,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$8:$M$8</f>
+              <f>'Jobs by Category'!$B$8:$R$8</f>
             </numRef>
           </val>
         </ser>
@@ -355,12 +355,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$9:$M$9</f>
+              <f>'Jobs by Category'!$B$9:$R$9</f>
             </numRef>
           </val>
         </ser>
@@ -374,12 +374,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$10:$M$10</f>
+              <f>'Jobs by Category'!$B$10:$R$10</f>
             </numRef>
           </val>
         </ser>
@@ -393,12 +393,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$11:$M$11</f>
+              <f>'Jobs by Category'!$B$11:$R$11</f>
             </numRef>
           </val>
         </ser>
@@ -412,12 +412,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$12:$M$12</f>
+              <f>'Jobs by Category'!$B$12:$R$12</f>
             </numRef>
           </val>
         </ser>
@@ -431,12 +431,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$13:$M$13</f>
+              <f>'Jobs by Category'!$B$13:$R$13</f>
             </numRef>
           </val>
         </ser>
@@ -450,12 +450,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$14:$M$14</f>
+              <f>'Jobs by Category'!$B$14:$R$14</f>
             </numRef>
           </val>
         </ser>
@@ -469,12 +469,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$15:$M$15</f>
+              <f>'Jobs by Category'!$B$15:$R$15</f>
             </numRef>
           </val>
         </ser>
@@ -488,12 +488,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$16:$M$16</f>
+              <f>'Jobs by Category'!$B$16:$R$16</f>
             </numRef>
           </val>
         </ser>
@@ -507,12 +507,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$17:$M$17</f>
+              <f>'Jobs by Category'!$B$17:$R$17</f>
             </numRef>
           </val>
         </ser>
@@ -526,12 +526,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$18:$M$18</f>
+              <f>'Jobs by Category'!$B$18:$R$18</f>
             </numRef>
           </val>
         </ser>
@@ -545,12 +545,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$19:$M$19</f>
+              <f>'Jobs by Category'!$B$19:$R$19</f>
             </numRef>
           </val>
         </ser>
@@ -564,12 +564,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$20:$M$20</f>
+              <f>'Jobs by Category'!$B$20:$R$20</f>
             </numRef>
           </val>
         </ser>
@@ -583,12 +583,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$21:$M$21</f>
+              <f>'Jobs by Category'!$B$21:$R$21</f>
             </numRef>
           </val>
         </ser>
@@ -602,12 +602,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$22:$M$22</f>
+              <f>'Jobs by Category'!$B$22:$R$22</f>
             </numRef>
           </val>
         </ser>
@@ -621,12 +621,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Jobs by Category'!$B$4:$M$4</f>
+              <f>'Jobs by Category'!$B$4:$R$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Jobs by Category'!$B$23:$M$23</f>
+              <f>'Jobs by Category'!$B$23:$R$23</f>
             </numRef>
           </val>
         </ser>
@@ -998,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1015,6 +1015,11 @@
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1027,7 +1032,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: the printed classified section of six weekly editions. Each column is one edition.</t>
+          <t>Source: the printed classified section, seventeen consecutive weekly editions. Each column is one edition.</t>
         </is>
       </c>
     </row>
@@ -1039,65 +1044,90 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
+          <t>April 9-15, 2026</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>April 16-22, 2026</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
           <t>April 23-29, 2026</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>April 30-May 6, 2026</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>May 7-13, 2026</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>May 14-20, 2026</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>May 21-27, 2026</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>May 28-June 3, 2026</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>June 4-10, 2026</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>June 11-17, 2026</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>June 18-24, 2026</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>June 25-July 1, 2026</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>July 2-8, 2026</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>July 9-15, 2026</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>July 16-22, 2026</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>July 23-29, 2026</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>July 30-August 5, 2026</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -1106,70 +1136,85 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="R5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="6" t="n"/>
-      <c r="N5" s="7" t="n">
-        <v>23</v>
+      <c r="S5" s="7" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
       <c r="I6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="6" t="n"/>
+      <c r="J6" s="6" t="n">
+        <v>3</v>
+      </c>
       <c r="K6" s="6" t="n">
         <v>1</v>
       </c>
@@ -1179,8 +1224,21 @@
       <c r="M6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="N6" s="7" t="n">
-        <v>21</v>
+      <c r="N6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="6" t="n"/>
+      <c r="S6" s="7" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -1190,16 +1248,16 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>1</v>
@@ -1208,25 +1266,38 @@
         <v>1</v>
       </c>
       <c r="H7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="6" t="n">
         <v>2</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>1</v>
       </c>
       <c r="M7" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="N7" s="7" t="n">
-        <v>17</v>
+      <c r="N7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" s="7" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -1236,7 +1307,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>2</v>
@@ -1245,7 +1316,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>2</v>
@@ -1256,13 +1327,22 @@
       <c r="H8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="6" t="n"/>
+      <c r="I8" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="J8" s="6" t="n"/>
       <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
+      <c r="L8" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="M8" s="6" t="n"/>
-      <c r="N8" s="7" t="n">
-        <v>11</v>
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="6" t="n"/>
+      <c r="P8" s="6" t="n"/>
+      <c r="Q8" s="6" t="n"/>
+      <c r="R8" s="6" t="n"/>
+      <c r="S8" s="7" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -1274,31 +1354,40 @@
       <c r="B9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
+      <c r="C9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="6" t="n">
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-      <c r="M9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" s="7" t="n">
-        <v>8</v>
+      <c r="L9" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="6" t="n"/>
+      <c r="P9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="6" t="n"/>
+      <c r="R9" s="6" t="n"/>
+      <c r="S9" s="7" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -1309,32 +1398,41 @@
       </c>
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
+      <c r="F10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="H10" s="6" t="n"/>
       <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
+      <c r="N10" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="O10" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="P10" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="M10" s="6" t="n"/>
-      <c r="N10" s="7" t="n">
-        <v>7</v>
+      <c r="Q10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" s="6" t="n"/>
+      <c r="S10" s="7" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>33-0000 Protective Service</t>
+          <t>39-0000 Personal Care and Service</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
@@ -1346,9 +1444,7 @@
       <c r="D11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
       <c r="H11" s="6" t="n"/>
@@ -1360,190 +1456,257 @@
       <c r="L11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="M11" s="6" t="n"/>
-      <c r="N11" s="7" t="n">
-        <v>6</v>
+      <c r="M11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n"/>
+      <c r="Q11" s="6" t="n"/>
+      <c r="R11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" s="7" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
+          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="6" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
+      <c r="F12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="H12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="J12" s="6" t="n"/>
       <c r="K12" s="6" t="n"/>
       <c r="L12" s="6" t="n"/>
-      <c r="M12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>5</v>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="6" t="n"/>
+      <c r="Q12" s="6" t="n"/>
+      <c r="R12" s="6" t="n"/>
+      <c r="S12" s="7" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>53-0000 Transportation and Material Moving</t>
+          <t>33-0000 Protective Service</t>
         </is>
       </c>
       <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="C13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="6" t="n"/>
       <c r="H13" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="K13" s="6" t="n"/>
       <c r="L13" s="6" t="n"/>
-      <c r="M13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" s="7" t="n">
-        <v>4</v>
+      <c r="M13" s="6" t="n"/>
+      <c r="N13" s="6" t="n"/>
+      <c r="O13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="6" t="n"/>
+      <c r="Q13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" s="6" t="n"/>
+      <c r="S13" s="7" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
+          <t>53-0000 Transportation and Material Moving</t>
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
-      <c r="M14" s="6" t="n"/>
-      <c r="N14" s="7" t="n">
-        <v>3</v>
+      <c r="J14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="6" t="n"/>
+      <c r="P14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="6" t="n"/>
+      <c r="R14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" s="7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>15-0000 Computer and Mathematical</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>1</v>
-      </c>
+          <t>43-0000 Office and Administrative Support</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
       <c r="H15" s="6" t="n"/>
       <c r="I15" s="6" t="n"/>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="6" t="n"/>
       <c r="L15" s="6" t="n"/>
       <c r="M15" s="6" t="n"/>
-      <c r="N15" s="7" t="n">
-        <v>3</v>
+      <c r="N15" s="6" t="n"/>
+      <c r="O15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="6" t="n"/>
+      <c r="R15" s="6" t="n"/>
+      <c r="S15" s="7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>49-0000 Installation, Maintenance, and Repair</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
+          <t>Other or not stated</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
+      <c r="E16" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
       <c r="J16" s="6" t="n"/>
       <c r="K16" s="6" t="n"/>
       <c r="L16" s="6" t="n"/>
       <c r="M16" s="6" t="n"/>
-      <c r="N16" s="7" t="n">
-        <v>2</v>
+      <c r="N16" s="6" t="n"/>
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="6" t="n"/>
+      <c r="Q16" s="6" t="n"/>
+      <c r="R16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>17-0000 Architecture and Engineering</t>
+          <t>15-0000 Computer and Mathematical</t>
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="H17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
+      <c r="I17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="K17" s="6" t="n"/>
       <c r="L17" s="6" t="n"/>
       <c r="M17" s="6" t="n"/>
-      <c r="N17" s="7" t="n">
-        <v>2</v>
+      <c r="N17" s="6" t="n"/>
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="6" t="n"/>
+      <c r="Q17" s="6" t="n"/>
+      <c r="R17" s="6" t="n"/>
+      <c r="S17" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>47-0000 Construction and Extraction</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>1</v>
-      </c>
+          <t>49-0000 Installation, Maintenance, and Repair</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
@@ -1552,28 +1715,35 @@
       <c r="H18" s="6" t="n"/>
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
+      <c r="K18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="M18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="N18" s="7" t="n">
-        <v>2</v>
+      <c r="N18" s="6" t="n"/>
+      <c r="O18" s="6" t="n"/>
+      <c r="P18" s="6" t="n"/>
+      <c r="Q18" s="6" t="n"/>
+      <c r="R18" s="6" t="n"/>
+      <c r="S18" s="7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>13-0000 Business and Financial Operations</t>
+          <t>17-0000 Architecture and Engineering</t>
         </is>
       </c>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="6" t="n"/>
       <c r="I19" s="6" t="n">
@@ -1581,42 +1751,54 @@
       </c>
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
+      <c r="L19" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="M19" s="6" t="n"/>
-      <c r="N19" s="7" t="n">
+      <c r="N19" s="6" t="n"/>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="6" t="n"/>
+      <c r="R19" s="6" t="n"/>
+      <c r="S19" s="7" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>43-0000 Office and Administrative Support</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>1</v>
-      </c>
+          <t>47-0000 Construction and Extraction</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
+      <c r="D20" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
       <c r="H20" s="6" t="n"/>
       <c r="I20" s="6" t="n"/>
       <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="K20" s="6" t="n"/>
       <c r="L20" s="6" t="n"/>
       <c r="M20" s="6" t="n"/>
-      <c r="N20" s="7" t="n">
+      <c r="N20" s="6" t="n"/>
+      <c r="O20" s="6" t="n"/>
+      <c r="P20" s="6" t="n"/>
+      <c r="Q20" s="6" t="n"/>
+      <c r="R20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" s="7" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>19-0000 Life, Physical, and Social Science</t>
+          <t>13-0000 Business and Financial Operations</t>
         </is>
       </c>
       <c r="B21" s="6" t="n"/>
@@ -1626,27 +1808,32 @@
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
+      <c r="I21" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="6" t="n"/>
       <c r="L21" s="6" t="n"/>
       <c r="M21" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="N21" s="7" t="n">
-        <v>1</v>
+      <c r="N21" s="6" t="n"/>
+      <c r="O21" s="6" t="n"/>
+      <c r="P21" s="6" t="n"/>
+      <c r="Q21" s="6" t="n"/>
+      <c r="R21" s="6" t="n"/>
+      <c r="S21" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Other or not stated</t>
+          <t>19-0000 Life, Physical, and Social Science</t>
         </is>
       </c>
       <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
@@ -1657,7 +1844,14 @@
       <c r="K22" s="6" t="n"/>
       <c r="L22" s="6" t="n"/>
       <c r="M22" s="6" t="n"/>
-      <c r="N22" s="7" t="n">
+      <c r="N22" s="6" t="n"/>
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="n"/>
+      <c r="Q22" s="6" t="n"/>
+      <c r="R22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1671,17 +1865,22 @@
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="n"/>
       <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
+      <c r="I23" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="6" t="n"/>
       <c r="M23" s="6" t="n"/>
-      <c r="N23" s="7" t="n">
+      <c r="N23" s="6" t="n"/>
+      <c r="O23" s="6" t="n"/>
+      <c r="P23" s="6" t="n"/>
+      <c r="Q23" s="6" t="n"/>
+      <c r="R23" s="6" t="n"/>
+      <c r="S23" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1692,43 +1891,58 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="D24" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="E24" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="F24" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="G24" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="H24" s="9" t="n">
         <v>10</v>
-      </c>
-      <c r="G24" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>11</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>10</v>
       </c>
       <c r="J24" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="K24" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="K24" s="9" t="n">
-        <v>8</v>
-      </c>
       <c r="L24" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M24" s="9" t="n">
         <v>9</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>121</v>
+        <v>8</v>
+      </c>
+      <c r="O24" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P24" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q24" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="R24" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="S24" s="9" t="n">
+        <v>172</v>
       </c>
     </row>
     <row r="25">
@@ -1738,22 +1952,22 @@
         </is>
       </c>
       <c r="B25" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C25" s="11" t="n">
+      <c r="D25" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="F25" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="G25" s="11" t="n">
         <v>7</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" s="11" t="n">
-        <v>5</v>
       </c>
       <c r="H25" s="11" t="n">
         <v>7</v>
@@ -1762,19 +1976,34 @@
         <v>5</v>
       </c>
       <c r="J25" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="K25" s="11" t="n">
-        <v>5</v>
-      </c>
       <c r="L25" s="11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M25" s="11" t="n">
         <v>4</v>
       </c>
       <c r="N25" s="11" t="n">
-        <v>65</v>
+        <v>4</v>
+      </c>
+      <c r="O25" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="P25" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q25" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S25" s="11" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="26">
@@ -1784,41 +2013,56 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
       <c r="D26" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="9" t="n">
         <v>6</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>2</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J26" s="9" t="n">
         <v>2</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" s="9" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="L26" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="M26" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>32</v>
+        <v>2</v>
+      </c>
+      <c r="O26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="9" t="n"/>
+      <c r="R26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" s="9" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="27">
@@ -1827,14 +2071,14 @@
           <t>Ads offering housing</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="B27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
       <c r="F27" s="11" t="n">
         <v>1</v>
       </c>
@@ -1845,22 +2089,35 @@
         <v>1</v>
       </c>
       <c r="I27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="11" t="n">
+      <c r="O27" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="K27" s="11" t="n">
+      <c r="P27" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" s="11" t="n">
-        <v>13</v>
+      <c r="Q27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" s="11" t="n"/>
+      <c r="S27" s="11" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1929,39 +2186,39 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>25293</v>
+        <v>30000</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>65000</v>
+        <v>40000</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>65000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>30000</v>
+        <v>25293</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>40000</v>
+        <v>55000</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>50000</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="7">
@@ -1971,7 +2228,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>49920</v>
@@ -1990,13 +2247,13 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>15000</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>55120</v>
+        <v>56160</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>58240</v>
@@ -2009,10 +2266,10 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>37440</v>
+        <v>24523</v>
       </c>
       <c r="D9" s="13" t="n">
         <v>65520</v>
@@ -2028,13 +2285,13 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>37440</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>55640</v>
+        <v>55120</v>
       </c>
       <c r="E10" s="13" t="n">
         <v>72800</v>
@@ -2043,77 +2300,77 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>33-0000 Protective Service</t>
+          <t>39-0000 Personal Care and Service</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>25293</v>
+        <v>43680</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>55460</v>
+        <v>45760</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>158000</v>
+        <v>47840</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
+          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>43680</v>
+        <v>37440</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>45760</v>
+        <v>42640</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>47840</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>53-0000 Transportation and Material Moving</t>
+          <t>33-0000 Protective Service</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>45760</v>
+        <v>25293</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>57200</v>
+        <v>55460</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>68640</v>
+        <v>158000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
+          <t>53-0000 Transportation and Material Moving</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
         <v>3</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>37440</v>
+        <v>45760</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>42640</v>
+        <v>57200</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>47840</v>
+        <v>68640</v>
       </c>
     </row>
     <row r="15">
@@ -2165,7 +2422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2237,33 +2494,29 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>April 23-29, 2026</t>
+          <t>April 9-15, 2026</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr"/>
       <c r="D5" s="14" t="n"/>
       <c r="E5" s="14" t="n"/>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F5" s="14" t="inlineStr"/>
       <c r="G5" s="14" t="inlineStr"/>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>Top Telluride GC seeks experienced superintendent. Top benefits and pay. DOE. Email resume to: telluridesuper@gmail.com</t>
+          <t>Teachers Wanted West End Public Schools RE-2 located in Nucla, CO is seeking the following certiﬁed teaching positions (ATL candidates encouraged to apply) for the upcoming 26-27 school year: Kindergarten Teacher, K-12th Grade Performing Arts Teacher, Special Education Teacher/Generalist. For job de</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>April 23-29, 2026</t>
+          <t>April 9-15, 2026</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
@@ -2278,19 +2531,19 @@
       <c r="G6" s="14" t="inlineStr"/>
       <c r="H6" s="15" t="inlineStr">
         <is>
-          <t>Looking for a part-time teacher well-versed in AI/Claude/Agents applications to educate an ambitious 14 yr old boy going into 9th grade. Qualified coaches only please. Email jmasst@me.com or text (310)916-6132.</t>
+          <t>Looking for a part-time teacher well-versed in AI/Claude/Agents applications to educate an ambitious 14 yr old boy going into 9th grade. Qualiﬁed coaches only please. Email jmasst@me.com or text (310)916-6132.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>April 23-29, 2026</t>
+          <t>April 9-15, 2026</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr"/>
@@ -2300,139 +2553,131 @@
       <c r="G7" s="14" t="inlineStr"/>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>Looking for a private part-time educator for a 14 yr old boy going into 9th grade. Mostly afternoons. Qualified educators only who can develop a creative curriculum. If interested please email jmasst@me.com or text (310) 916-6132.</t>
+          <t>• Page A25 Norwood Public Schools is looking for a High School Volleyball Coach. Please check out the full job description at https://www.norwoodk12.org/jobs and «Click here for job listings and to apply online.» We will be accepting applications on an ongoing basis until positions are ﬁlled.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>April 23-29, 2026</t>
+          <t>April 9-15, 2026</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>$45,000.00-$50,000.00/year</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>45000</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="inlineStr"/>
       <c r="G8" s="14" t="inlineStr"/>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telluride Mountain School is hiring a Montessori Assistant Teacher Guide and inspire students in pre-school through kindergarten in developing their academic, social, and emotional growth. This is currently a full-time position. Salary in the $45k-50k range based on experience. To apply please send </t>
+          <t>Telluride R-1 School District is hiring IT Systems Administrator, School Nurse (2026-27 school year). To learn more and apply tellurideschool.org/employment</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>April 23-29, 2026</t>
+          <t>April 9-15, 2026</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
+          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>$30.00/hour</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>62400</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>62400</v>
+      </c>
       <c r="F9" s="14" t="inlineStr"/>
       <c r="G9" s="14" t="inlineStr"/>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teachers Wanted West End Public Schools RE-2 located in Nucla, CO is seeking the following certified teaching positions (ATL candidates encouraged to apply) for the upcoming 26-27 school year: Kindergarten Teacher, K-12th Grade Performing Arts Teacher, Special Education Teacher/ Generalist. For job </t>
+          <t>Landscaper Box Canyon Yard &amp; Garden is looking for new members to join our landscape main- tenance team. Starting at $30/hr. Contact Peter at (970) 846-0016</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>April 23-29, 2026</t>
+          <t>April 9-15, 2026</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>$30,000.00-$50,000.00/year</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>50000</v>
-      </c>
+          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
       <c r="F10" s="14" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr"/>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>Telluride Mountain School is hiring an All School Art Teacher Teach and inspire students in kindergarten through 8th grade in developing artistic skill, creative confidence, visual literacy, and habits of observation and expression. This is currently an exempt, part-time position. Salary in the $30K</t>
+          <t>Irrigation Tech Wild Iris Greenhouse &amp; Gardens is hiring! Irrigation Tech &amp; Landscape Laborer. Transportation provided, housing available. $24-$28 DOE. Email info@ wildirisplants.com, or text 970-7080531 to learn more.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>April 23-29, 2026</t>
+          <t>April 9-15, 2026</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>$26.00-$28.00/hour</t>
+          <t>$22.00-$30.00/hour</t>
         </is>
       </c>
       <c r="D11" s="16" t="n">
-        <v>54080</v>
+        <v>45760</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>58240</v>
+        <v>62400</v>
       </c>
       <c r="F11" s="14" t="inlineStr"/>
       <c r="G11" s="14" t="inlineStr"/>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>Office Admin Coldwell Banker; Hiring for Part-time Receptionist/Office Mgr. Must be professional, friendly &amp;organized. Responsibilities: Front desk reception, office operations, agent support, &amp; marketing assistance. 20 hours/week; $26 - $28/hour. Send resume to: resume@cbdistinctive.com</t>
+          <t>Make up for a lean Winter. Join our landscaping team looking to expand. Need Laborers, crew leader, mechanic that can operate. Apply on line at www.modernlandscaping. net. Good pay; $22-$30/hr. Most work around Ridgway.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>April 23-29, 2026</t>
+          <t>April 9-15, 2026</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+          <t>39-0000 Personal Care and Service</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr"/>
@@ -2442,19 +2687,19 @@
       <c r="G12" s="14" t="inlineStr"/>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>Norwood Public Schools is looking for a High School Volleyball Coach. Please check out the full job description at https://www.norwoodk12.org/jobs and «click here for job listings and to apply online.» We will be accepting applications on an ongoing basis until positions are filled.</t>
+          <t>Reservationist Telluride Outside is hiring a summer/fall reservationist. Please contact Kristen Haaker: reservations@tellurideoutside.com / (970) 728-3895 ext 1.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>April 23-29, 2026</t>
+          <t>April 9-15, 2026</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>29-0000 Healthcare Practitioners and Technical</t>
+          <t>41-0000 Sales and Related</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr"/>
@@ -2464,53 +2709,41 @@
       <c r="G13" s="14" t="inlineStr"/>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>Telluride R-1 School District is hiring IT Systems Administrator, School Nurse (2026-27 school year). To learn more and apply tellurideschool.org/employment</t>
+          <t>Retail P/T, 20 hrs to start. Committed, hard working team player wanted for our busy retail shoppe in town. Prefer year-round commitment. Send resume and brief letter of interest to: info@eftoyshoppe.com</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>April 23-29, 2026</t>
+          <t>April 9-15, 2026</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>33-0000 Protective Service</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>$18.00/hour; $30,000.00-$35,000.00/year; $80,000.00/year; $100,000.00/year</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>100000</v>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>43-0000 Office and Administrative Support</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="14" t="inlineStr"/>
       <c r="G14" s="14" t="inlineStr"/>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>Telluride Mountain School is hiring a Middle School Humanities Teacher Teach and inspire students in 5th through 8th grades in developing strong reading, writing, discussion, and critical thinking skills, while deepening their understanding of history, literature, and the human experience.This is cu</t>
+          <t>Store Clerk Summer season is quickly approaching, work in the middle of all the beauty and happenings! Morning and Afternoon shifts available, Part time or Full time at the Ridgway Conoco! Discounts and Perks included! Starting pay $16 and up for experience or willingness to learn. Apply on indeed o</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>April 23-29, 2026</t>
+          <t>April 9-15, 2026</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
+          <t>Other or not stated</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr"/>
@@ -2520,71 +2753,67 @@
       <c r="G15" s="14" t="inlineStr"/>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>Reservationist Telluride Outside is hiring a summer/fall reservationist. Please contact Kristen Haaker: reservations@tellurideoutside.com / (970) 728-3895 ext 1. https://www.sanmiguelcountyco. gov/198/Planning The official designated posting place for all meeting notices is online at https://www.san</t>
+          <t>NOTICE PURSUANT TO THE Planning and Zoning LAWS OF COLORADO the Norwood Public Schools HAS REQUESTED THE LICENSING OFFICIALS OF THE TOWN OF NORWOOD TO: Approve Application and Set for Public Hearing APPLICATION FOR Re-Zoning WAS FILED ON: March 09, 2026 BY OFFICER: Reilly O’ Brien ADDRESS OF PROPOSE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>April 23-29, 2026</t>
+          <t>April 16-22, 2026</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr"/>
       <c r="D16" s="14" t="n"/>
       <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="inlineStr"/>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G16" s="14" t="inlineStr"/>
       <c r="H16" s="15" t="inlineStr">
         <is>
-          <t>Retail P/T, 20 hrs to start. Committed, hard working team player wanted for our busy retail shoppe in town. Prefer year-round commitment. Send resume and brief letter of interest to: info@eftoyshoppe.com</t>
+          <t>Top Telluride GC seeks experienced superintendent. Top beneﬁts and pay. DOE. Email resume to: telluridesuper@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>April 23-29, 2026</t>
+          <t>April 16-22, 2026</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>$25.00/hour</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>52000</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>52000</v>
-      </c>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
       <c r="F17" s="14" t="inlineStr"/>
       <c r="G17" s="14" t="inlineStr"/>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>The Telluride Toggery is hiring! Join our fun and motivated sales team at Telluride’s longest running clothing store. Full-time salesperson positions are now available starting at $25/hr. Apply in person at 109 East Colorado Ave or email: wendy@thetelluridetoggery.com</t>
+          <t>Looking for a part-time teacher well-versed in AI/Claude/Agents applications to educate an ambitious 14 yr old boy going into 9th grade. Qualiﬁed coaches only please. Email jmasst@me.com or text (310)916-6132.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>April 23-29, 2026</t>
+          <t>April 16-22, 2026</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>43-0000 Office and Administrative Support</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr"/>
@@ -2594,62 +2823,70 @@
       <c r="G18" s="14" t="inlineStr"/>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>Store Clerk Summer season is quickly approaching, work in the middle of all the beauty and happenings! Morning and Afternoon shifts available, Part time or Full time at the Ridgway Conoco! Discounts and Perks included! Starting pay $16 and up for experience or willingness to learn. Apply on indeed o</t>
+          <t>Looking for a private part-time educator for a 14 yr old boy going into 9th grade. Mostly afternoons. Qualiﬁed educators only who can develop a creative curriculum. If interested please email jmasst@ me.com or text (310) 916-6132.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>April 23-29, 2026</t>
+          <t>April 16-22, 2026</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>47-0000 Construction and Extraction</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr"/>
-      <c r="D19" s="14" t="n"/>
-      <c r="E19" s="14" t="n"/>
-      <c r="F19" s="14" t="inlineStr"/>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>$45,000.00-$50,000.00/year</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G19" s="14" t="inlineStr"/>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>PUBLIC HEARING NOTICE The San Miguel County Planning Commission has been asked to consider an application submitted by John Miller, Ponderosa Planning &amp; Design, on behalf of Kurt Works Inc. and Kurt Crockett, owner of a 44.13-acre parcel, located at 488 S. Avalon Dr., Norwood, CO, Parcel #4527261030</t>
+          <t>Telluride Mountain School is hiring a Montessori Assistant Teacher Guide and inspire students in preschool through kindergarten in developing their academic, social, and emotional growth. This is currently a full-time position. Salary in the $45k-50k range based on experience. To apply please send a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>April 30-May 6, 2026</t>
+          <t>April 16-22, 2026</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr"/>
       <c r="D20" s="14" t="n"/>
       <c r="E20" s="14" t="n"/>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F20" s="14" t="inlineStr"/>
       <c r="G20" s="14" t="inlineStr"/>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>Top Telluride GC seeks experienced superintendent. Top benefits and pay. DOE. Email resume to: telluridesuper@gmail.com</t>
+          <t>Teachers Wanted West End Public Schools RE-2 located in Nucla, CO is seeking the following certiﬁed teaching positions (ATL candidates into electrical signals that are sent to the brain. These include a surgically inserted component and can take months to get used to. Hearing aids are an adjustment,</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>April 30-May 6, 2026</t>
+          <t>April 16-22, 2026</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -2657,82 +2894,90 @@
           <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr"/>
-      <c r="D21" s="14" t="n"/>
-      <c r="E21" s="14" t="n"/>
-      <c r="F21" s="14" t="inlineStr"/>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>$30,000.00-$50,000.00/year</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G21" s="14" t="inlineStr"/>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>Looking for a part-time teacher well-versed in AI/Claude/Agents applications to educate an ambitious 14 yr old boy going into 9th grade. Qualified coaches only please. Email jmasst@me.com or text (310)916-6132.</t>
+          <t>Telluride Mountain School is hiring an All School Art Teacher Teach and inspire students in kindergarten through 8th grade in developing artistic skill, creative conﬁdence, visual literacy, and habits of observation and expression. This is currently an exempt, part-time position. Salary in the $30K-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>April 30-May 6, 2026</t>
+          <t>April 16-22, 2026</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr"/>
-      <c r="D22" s="14" t="n"/>
-      <c r="E22" s="14" t="n"/>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>$28.00/hour</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>58240</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>58240</v>
+      </c>
       <c r="F22" s="14" t="inlineStr"/>
       <c r="G22" s="14" t="inlineStr"/>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>Looking for a private part-time educator for a 14 yr old boy going into 9th grade. Mostly afternoons. Qualified educators only who can develop a creative curriculum. If interested please email jmasst@me.com or text (310)916-6132.</t>
+          <t>Oﬃce Admin Coldwell Banker; Hiring for Part-time Receptionist/ Oﬃce Mgr. Must be professional, friendly &amp;organized. Responsibilities: Front desk reception, oﬃce operations, agent support, &amp; marketing assistance. 20 hours/week; $26 $28/hour. Send resume to: resume@ cbdistinctive.com</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>April 30-May 6, 2026</t>
+          <t>April 16-22, 2026</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>$45,000.00-$50,000.00/year</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>45000</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="inlineStr"/>
       <c r="G23" s="14" t="inlineStr"/>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telluride Mountain School is hiring a Montessori Assistant Teacher Guide and inspire students in pre-school through kindergarten in developing their academic, social, and emotional growth. This is currently a full-time position. Salary in the $45k-50k range based on experience. To apply please send </t>
+          <t>Norwood Public Schools is looking for a High School Volleyball Coach. Please check out the full job description at https://www.norwoodk12.org/jobs and «Click here for job listings and to apply online.» We will be accepting applications on an ongoing basis until positions are ﬁlled.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>April 30-May 6, 2026</t>
+          <t>April 16-22, 2026</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr"/>
@@ -2742,31 +2987,31 @@
       <c r="G24" s="14" t="inlineStr"/>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>Teachers Wanted West End Public Schools RE–2. located in Nucla, CO is seeking the following certified teaching positions (ATL candidates encouraged to apply) for the upcoming 26–27 school year: Kindergarten Teacher, K–12th Grade Performing Arts Teacher, Special Education Teacher/Generalist For job d</t>
+          <t>Telluride R-1 School District is hiring IT Systems Administrator, School Nurse (2026-27 school year). To learn more and apply tellurideschool.org/employment</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>April 30-May 6, 2026</t>
+          <t>April 16-22, 2026</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
+          <t>33-0000 Protective Service</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>$30,000.00-$50,000.00/year</t>
+          <t>$30,000.00-$35,000.00/year; $80,000.00/year; $100,000.00/year</t>
         </is>
       </c>
       <c r="D25" s="16" t="n">
         <v>30000</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
@@ -2776,83 +3021,71 @@
       <c r="G25" s="14" t="inlineStr"/>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>Telluride Mountain School is hiring an All School Art Teacher Teach and inspire students in kindergarten through 8th grade in developing artistic skill, creative confidence, visual literacy, and habits of observation and expression. This is currently an exempt, part-time position. Salary in the $30K</t>
+          <t>Telluride Mountain School is hiring a Middle School Humanities Teacher Teach and inspire students in 5th through 8th grades in developing strong reading, writing, discussion, and critical thinking skills, while deepening their understanding of history, literature, and the human experience.This is cu</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>April 30-May 6, 2026</t>
+          <t>April 16-22, 2026</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>$30,000.00-$35,000.00/year</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>35000</v>
-      </c>
+          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="14" t="n"/>
       <c r="F26" s="14" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="G26" s="14" t="inlineStr"/>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H26" s="15" t="inlineStr">
         <is>
-          <t>Telluride Mountain School is hiring a Middle School Humanities Teacher Teach and inspire students in 5th through 8th grades in developing strong reading, writing, discussion, and critical thinking skills, while deepening their understanding of history, literature, and the human experience.This is cu</t>
+          <t>Irrigation Tech Wild Iris Greenhouse &amp; Gardens is hiring! Irrigation Tech &amp; Landscape Laborer. Transportation provided, housing available. $24-$28 DOE. Email info@wildirisplants.com, or text 970-708-0531 to learn more.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>April 30-May 6, 2026</t>
+          <t>April 16-22, 2026</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>$26.00-$28.00/hour</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>54080</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>58240</v>
-      </c>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
       <c r="F27" s="14" t="inlineStr"/>
       <c r="G27" s="14" t="inlineStr"/>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>Office Admin Coldwell Banker; Hiring for Part-time Receptionist/ Office Mgr. Must be professional, friendly &amp;organized. Responsibilities: Front desk reception, office operations, agent support, &amp; marketing assistance. 20 hours/week; $26 - $28/hour. Send resume to: resume@cbdistinctive.com</t>
+          <t>Reservationist Telluride Outside is hiring a summer/fall reservationist. Please contact Kristen Haaker: reservations@tellurideoutside.com / (970) 728-3895 ext 1.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>April 30-May 6, 2026</t>
+          <t>April 16-22, 2026</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+          <t>41-0000 Sales and Related</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr"/>
@@ -2862,53 +3095,49 @@
       <c r="G28" s="14" t="inlineStr"/>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>Norwood Public Schools is looking for a High School Volleyball Coach. Please check out the full job description at https://www.norwoodk12.org/jobs and «Click here for job listings and to apply online.» We will be accepting applications on an ongoing basis until positions are filled.</t>
+          <t>Retail P/T, 20 hrs to start. Committed, hard working team player wanted for our busy retail shoppe actually going on — like whether your ears are just plugged up with wax or ﬂuid. Hearing aids ﬁne-tune the sound signal that enters the brain, enhancing speech while lowering background noise. They can</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>April 30-May 6, 2026</t>
+          <t>April 16-22, 2026</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>33-0000 Protective Service</t>
+          <t>41-0000 Sales and Related</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>$20.00-$25.00/hour; $18.00/hour; $12.16/hour; $65,000.00/year; $80,000.00/year; $100,000.00/year; $158,000.00/year</t>
+          <t>$25.00/hour</t>
         </is>
       </c>
       <c r="D29" s="16" t="n">
-        <v>25293</v>
+        <v>52000</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>158000</v>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+        <v>52000</v>
+      </c>
+      <c r="F29" s="14" t="inlineStr"/>
       <c r="G29" s="14" t="inlineStr"/>
       <c r="H29" s="15" t="inlineStr">
         <is>
-          <t>Telluride Brewing Craft Kitchen and Pizza is hiring (Lawson Hill Location). Kitchen Manager: $65,000 (could increase based on experience)+Benefits; Back of the House: $20-$25/hour based on experience (weekends required); Food Runner: $18/hour plus tips (weekends required); Bartender: $12.16/hour plu</t>
+          <t>The Telluride Toggery is hiring for the summer season! Join our fun and motivated sales team at Telluride›s longest running clothing store. Full-time salesperson positions are now available starting at $25/hr. Apply in person at 109 East Colorado Ave or email: wendy@thetelluridetoggery.com</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>April 30-May 6, 2026</t>
+          <t>April 16-22, 2026</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
+          <t>43-0000 Office and Administrative Support</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr"/>
@@ -2918,144 +3147,140 @@
       <c r="G30" s="14" t="inlineStr"/>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Retail P/T, 20 hrs to start. Committed, hard working team player wanted for our busy retail shoppe in town. Prefer year-round commitment. Send resume and brief letter of interest to: info@eftoyshoppe.com</t>
+          <t>Store Clerk Summer season is quickly approaching, work in the middle of all the beauty and happenings! Morning and Afternoon shifts available, Part time or Full time at the Ridgway Conoco! Discounts and Perks included! Starting pay $16 and up for experience or willingness to learn. Apply on indeed o</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>April 30-May 6, 2026</t>
+          <t>April 16-22, 2026</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>$25.00/hour</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="n">
-        <v>52000</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>52000</v>
-      </c>
+          <t>Other or not stated</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
       <c r="F31" s="14" t="inlineStr"/>
       <c r="G31" s="14" t="inlineStr"/>
       <c r="H31" s="15" t="inlineStr">
         <is>
-          <t>The Telluride Toggery is hiring! Join our fun and motivated sales team at Telluride’s longest running clothing store. Full-time salesperson positions are now available starting at $25/hr. Apply in person at 109 East Colorado Ave or email: wendy@thetelluridetoggery.com</t>
+          <t>NOTICE PURSUANT TO THE Planning and Zoning LAWS OF COLORADO the Norwood Public Schools HAS REQUESTED THE LICENSING OFFICIALS OF THE TOWN OF NORWOOD TO: Approve Application and Set for Public Hearing APPLICATION FOR Re-Zoning WAS FILED ON: March 09, 2026 BY OFFICER: Reilly O’ Brien ADDRESS OF PROPOSE</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>April 30-May 6, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>Other or not stated</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr"/>
       <c r="D32" s="14" t="n"/>
       <c r="E32" s="14" t="n"/>
-      <c r="F32" s="14" t="inlineStr"/>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G32" s="14" t="inlineStr"/>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>any neighbor or potentially affected property owner who, for any reason, has not received a copy of this notice, it would be appreciated if you would inform them of this public hearing. 4/30 COL-000119</t>
+          <t>Top Telluride GC seeks experienced superintendent. Top benefits and pay. DOE. Email resume to: telluridesuper@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>May 7-13, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr"/>
       <c r="D33" s="14" t="n"/>
       <c r="E33" s="14" t="n"/>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F33" s="14" t="inlineStr"/>
       <c r="G33" s="14" t="inlineStr"/>
       <c r="H33" s="15" t="inlineStr">
         <is>
-          <t>Top Telluride GC seeks experienced superintendent. Top beneﬁts and pay. DOE. Email resume to: telluridesuper@gmail.com</t>
+          <t>Looking for a part-time teacher well-versed in AI/Claude/Agents applications to educate an ambitious 14 yr old boy going into 9th grade. Qualified coaches only please. Email jmasst@me.com or text (310)916-6132.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>May 7-13, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="inlineStr">
-        <is>
-          <t>$50,000.00-$60,000.00/year</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>60000</v>
-      </c>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
       <c r="F34" s="14" t="inlineStr"/>
       <c r="G34" s="14" t="inlineStr"/>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>Front Desk Administrator (FT) Luxury real estate oﬃce seeking professional front desk support. Duties include greeting clients, answering phones, and assisting advisors. Req: Experience, strong communication &amp; organization skills. Hours: Mon–Fri | Pay: $50K–$60K+ beneﬁts. Please email lkropuenske@li</t>
+          <t>Looking for a private part-time educator for a 14 yr old boy going into 9th grade. Mostly afternoons. Qualified educators only who can develop a creative curriculum. If interested please email jmasst@me.com or text (310) 916-6132.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>May 7-13, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="inlineStr"/>
-      <c r="D35" s="14" t="n"/>
-      <c r="E35" s="14" t="n"/>
-      <c r="F35" s="14" t="inlineStr"/>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>$45,000.00-$50,000.00/year</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G35" s="14" t="inlineStr"/>
       <c r="H35" s="15" t="inlineStr">
         <is>
-          <t>Notice to First Mortgagees Regarding Consent to First Amendment to Declaration Village Creek Condominium Association, a Colorado nonproﬁt corporation Property: Village Creek Condominiums, as established by the Condominium Declaration recorded December 23, 1987 in Book 441, page 232, Reception No. 25</t>
+          <t xml:space="preserve">Telluride Mountain School is hiring a Montessori Assistant Teacher Guide and inspire students in pre-school through kindergarten in developing their academic, social, and emotional growth. This is currently a full-time position. Salary in the $45k-50k range based on experience. To apply please send </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>May 7-13, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
@@ -3063,33 +3288,21 @@
           <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>$45,000.00-$50,000.00/year</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="n">
-        <v>45000</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="C36" s="14" t="inlineStr"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="14" t="n"/>
+      <c r="F36" s="14" t="inlineStr"/>
       <c r="G36" s="14" t="inlineStr"/>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telluride Mountain School is hiring a Montessori Assistant Teacher Guide and inspire students in pre-school through kindergarten in developing their academic, social, and emotional growth. This is currently a full-time position. Salary in the $45k-50k range based on experience. To apply please send </t>
+          <t xml:space="preserve">Teachers Wanted West End Public Schools RE-2 located in Nucla, CO is seeking the following certified teaching positions (ATL candidates encouraged to apply) for the upcoming 26-27 school year: Kindergarten Teacher, K-12th Grade Performing Arts Teacher, Special Education Teacher/ Generalist. For job </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>May 7-13, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
@@ -3097,299 +3310,259 @@
           <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr"/>
-      <c r="D37" s="14" t="n"/>
-      <c r="E37" s="14" t="n"/>
-      <c r="F37" s="14" t="inlineStr"/>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>$30,000.00-$50,000.00/year</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G37" s="14" t="inlineStr"/>
       <c r="H37" s="15" t="inlineStr">
         <is>
-          <t>Teachers Wanted West End Public Schools RE–2. located in Nucla, CO is seeking the following certiﬁed teaching positions (ATL candidates encouraged to apply) for the upcoming 26– 27 school year: Kindergarten Teacher, K–12th Grade Performing Arts Teacher, Special Education Teacher/Generalist For job d</t>
+          <t>Telluride Mountain School is hiring an All School Art Teacher Teach and inspire students in kindergarten through 8th grade in developing artistic skill, creative confidence, visual literacy, and habits of observation and expression. This is currently an exempt, part-time position. Salary in the $30K</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>May 7-13, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>$30,000.00-$50,000.00/year</t>
+          <t>$26.00-$28.00/hour</t>
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>30000</v>
+        <v>54080</v>
       </c>
       <c r="E38" s="16" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F38" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+        <v>58240</v>
+      </c>
+      <c r="F38" s="14" t="inlineStr"/>
       <c r="G38" s="14" t="inlineStr"/>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>Telluride Mountain School is hiring an All School Art Teacher Teach and inspire students in kindergarten through 8th grade in developing artistic skill, creative conﬁdence, visual literacy, and habits of observation and expression. This is currently an exempt, parttime position. Salary in the $30K-5</t>
+          <t>Office Admin Coldwell Banker; Hiring for Part-time Receptionist/Office Mgr. Must be professional, friendly &amp;organized. Responsibilities: Front desk reception, office operations, agent support, &amp; marketing assistance. 20 hours/week; $26 - $28/hour. Send resume to: resume@cbdistinctive.com</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>May 7-13, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="inlineStr">
-        <is>
-          <t>$30,000.00-$35,000.00/year</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F39" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="14" t="inlineStr"/>
       <c r="G39" s="14" t="inlineStr"/>
       <c r="H39" s="15" t="inlineStr">
         <is>
-          <t>Telluride Mountain School is hiring a Middle School Humanities Teacher Teach and inspire students in 5th through 8th grades in developing strong reading, writing, discussion, and critical thinking skills, while deepening their understanding of history, literature, and the human experience.This is cu</t>
+          <t>Norwood Public Schools is looking for a High School Volleyball Coach. Please check out the full job description at https://www.norwoodk12.org/jobs and «click here for job listings and to apply online.» We will be accepting applications on an ongoing basis until positions are filled.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>May 7-13, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="inlineStr">
-        <is>
-          <t>$26.00-$28.00/hour</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="n">
-        <v>54080</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>58240</v>
-      </c>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr"/>
+      <c r="D40" s="14" t="n"/>
+      <c r="E40" s="14" t="n"/>
       <c r="F40" s="14" t="inlineStr"/>
       <c r="G40" s="14" t="inlineStr"/>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Oﬃce Admin Coldwell Banker; Hiring for Part-time Receptionist/Ofﬁce Mgr. Must be professional, friendly &amp;organized. Responsibilities: Front desk reception, oﬃce operations, agent support, &amp; marketing assistance. 20 hours/week; $26 - $28/hour. Send resume to: resume@cbdistinctive.com</t>
+          <t>Telluride R-1 School District is hiring IT Systems Administrator, School Nurse (2026-27 school year). To learn more and apply tellurideschool.org/employment</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>May 7-13, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr"/>
-      <c r="D41" s="14" t="n"/>
-      <c r="E41" s="14" t="n"/>
-      <c r="F41" s="14" t="inlineStr"/>
+          <t>33-0000 Protective Service</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>$18.00/hour; $30,000.00-$35,000.00/year; $80,000.00/year; $100,000.00/year</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G41" s="14" t="inlineStr"/>
       <c r="H41" s="15" t="inlineStr">
         <is>
-          <t>Norwood Public Schools is looking for a High School Volleyball Coach. Please check out the full job description at https://www.norwoodk12.org/jobs and «click here for job listings and to apply online.» We will be accepting applications on an ongoing basis until positions are ﬁlled.</t>
+          <t>Telluride Mountain School is hiring a Middle School Humanities Teacher Teach and inspire students in 5th through 8th grades in developing strong reading, writing, discussion, and critical thinking skills, while deepening their understanding of history, literature, and the human experience.This is cu</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>May 7-13, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>33-0000 Protective Service</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="inlineStr">
-        <is>
-          <t>$30.00-$35.00/hour; $18.00/hour</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="n">
-        <v>37440</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>72800</v>
-      </c>
-      <c r="F42" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr"/>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="14" t="n"/>
+      <c r="F42" s="14" t="inlineStr"/>
       <c r="G42" s="14" t="inlineStr"/>
       <c r="H42" s="15" t="inlineStr">
         <is>
-          <t>Summer Program Director Fulltime Seasonal (May–October), Telluride Adaptive Sports Program (TASP) is seeking a Summer Program Director to help lead our seasonal adaptive recreation programs in the San Juan Mountains. This full-time role oversees daily operations, instructor coordination, and multida</t>
+          <t>Reservationist Telluride Outside is hiring a summer/fall reservationist. Please contact Kristen Haaker: reservations@tellurideoutside.com / (970) 728-3895 ext 1. https://www.sanmiguelcountyco. gov/198/Planning The official designated posting place for all meeting notices is online at https://www.san</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>May 7-13, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="inlineStr">
-        <is>
-          <t>$25.00-$30.00/hour; $20.00-$22.00/hour; $23.00/hour</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="n">
-        <v>41600</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>62400</v>
-      </c>
-      <c r="F43" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr"/>
+      <c r="D43" s="14" t="n"/>
+      <c r="E43" s="14" t="n"/>
+      <c r="F43" s="14" t="inlineStr"/>
+      <c r="G43" s="14" t="inlineStr"/>
       <c r="H43" s="15" t="inlineStr">
         <is>
-          <t>Lumiere by Dunton: Come join our 5* hotel and restaurant! *Housing Available* Maintenance Tech FT ($25-$30hr DOE), PM Bellman $20hr FT/PT, AM Concierge $25hr FT/PT. Dunton Kitchen: Breakfast Cook $23hr+ DOE, PM Line Cook $25hr+ DOE, Dishwasher $20-$22hr, Bartender, Server, Breakfast Server. Email: f</t>
+          <t>Retail P/T, 20 hrs to start. Committed, hard working team player wanted for our busy retail shoppe in town. Prefer year-round commitment. Send resume and brief letter of interest to: info@eftoyshoppe.com</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>May 7-13, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
+          <t>41-0000 Sales and Related</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>$18.00-$23.00/hour</t>
+          <t>$25.00/hour</t>
         </is>
       </c>
       <c r="D44" s="16" t="n">
-        <v>37440</v>
+        <v>52000</v>
       </c>
       <c r="E44" s="16" t="n">
-        <v>47840</v>
+        <v>52000</v>
       </c>
       <c r="F44" s="14" t="inlineStr"/>
       <c r="G44" s="14" t="inlineStr"/>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>Guest Services, Drivers, Housepersons Bear Creek Lodge is hiring for several positions: guest services, drivers, and housepersons ($18-$23/hr). Housing opportunities available. View job descriptions and apply online at telluridelodging.com/careers.</t>
+          <t>The Telluride Toggery is hiring! Join our fun and motivated sales team at Telluride’s longest running clothing store. Full-time salesperson positions are now available starting at $25/hr. Apply in person at 109 East Colorado Ave or email: wendy@thetelluridetoggery.com</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>May 7-13, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="inlineStr">
-        <is>
-          <t>$25.00/hour</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>52000</v>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>52000</v>
-      </c>
+          <t>43-0000 Office and Administrative Support</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr"/>
+      <c r="D45" s="14" t="n"/>
+      <c r="E45" s="14" t="n"/>
       <c r="F45" s="14" t="inlineStr"/>
       <c r="G45" s="14" t="inlineStr"/>
       <c r="H45" s="15" t="inlineStr">
         <is>
-          <t>The Telluride Toggery is hiring! Join our fun and motivated sales team at Telluride’s longest running clothing store. Full-time salesperson positions are now available starting at $25/hr. Apply in person at 109 East Colorado Ave or email: wendy@thetelluridetoggery.com</t>
+          <t>Store Clerk Summer season is quickly approaching, work in the middle of all the beauty and happenings! Morning and Afternoon shifts available, Part time or Full time at the Ridgway Conoco! Discounts and Perks included! Starting pay $16 and up for experience or willingness to learn. Apply on indeed o</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>May 21-27, 2026</t>
+          <t>April 23-29, 2026</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>47-0000 Construction and Extraction</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr"/>
       <c r="D46" s="14" t="n"/>
       <c r="E46" s="14" t="n"/>
-      <c r="F46" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F46" s="14" t="inlineStr"/>
       <c r="G46" s="14" t="inlineStr"/>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>Wilson Mesa Home For Rent 3 bed/1 bath. Mountain views + wood burning stove. No drugs/alcohol. Maybe 1 cat. 6 months-1 year lease. $2900/month + electricity + trash. Call Polly 970-728-0600. Superintendent Top Telluride GC seeks experienced superintendent. Top beneﬁts and pay DOE. Email resume to: t</t>
+          <t>PUBLIC HEARING NOTICE The San Miguel County Planning Commission has been asked to consider an application submitted by John Miller, Ponderosa Planning &amp; Design, on behalf of Kurt Works Inc. and Kurt Crockett, owner of a 44.13-acre parcel, located at 488 S. Avalon Dr., Norwood, CO, Parcel #4527261030</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>May 21-27, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
@@ -3397,110 +3570,86 @@
           <t>11-0000 Management</t>
         </is>
       </c>
-      <c r="C47" s="14" t="inlineStr">
-        <is>
-          <t>$65,000.00/year</t>
-        </is>
-      </c>
-      <c r="D47" s="16" t="n">
-        <v>65000</v>
-      </c>
-      <c r="E47" s="16" t="n">
-        <v>65000</v>
-      </c>
-      <c r="F47" s="14" t="inlineStr"/>
+      <c r="C47" s="14" t="inlineStr"/>
+      <c r="D47" s="14" t="n"/>
+      <c r="E47" s="14" t="n"/>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G47" s="14" t="inlineStr"/>
       <c r="H47" s="15" t="inlineStr">
         <is>
-          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
+          <t>Top Telluride GC seeks experienced superintendent. Top benefits and pay. DOE. Email resume to: telluridesuper@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>May 21-27, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="inlineStr">
-        <is>
-          <t>$50,000.00-$60,000.00/year</t>
-        </is>
-      </c>
-      <c r="D48" s="16" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>60000</v>
-      </c>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr"/>
+      <c r="D48" s="14" t="n"/>
+      <c r="E48" s="14" t="n"/>
       <c r="F48" s="14" t="inlineStr"/>
       <c r="G48" s="14" t="inlineStr"/>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>Front Desk Administrator (FT) Luxury real estate oﬃce seeking professional front desk support. Duties include greeting clients, answering phones, and assisting advisors. Req: Experience, strong communication &amp; organi- zation skills. Hours: Mon–Fri | Pay: $50K–$60K+ beneﬁts. Please email lkropuenske@</t>
+          <t>Looking for a part-time teacher well-versed in AI/Claude/Agents applications to educate an ambitious 14 yr old boy going into 9th grade. Qualified coaches only please. Email jmasst@me.com or text (310)916-6132.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>May 21-27, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="inlineStr">
-        <is>
-          <t>$30.00/hour; $20.00/hour; $25.00/hour</t>
-        </is>
-      </c>
-      <c r="D49" s="16" t="n">
-        <v>41600</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>62400</v>
-      </c>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr"/>
+      <c r="D49" s="14" t="n"/>
+      <c r="E49" s="14" t="n"/>
       <c r="F49" s="14" t="inlineStr"/>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G49" s="14" t="inlineStr"/>
       <c r="H49" s="15" t="inlineStr">
         <is>
-          <t>Lumiere by Dunton/Dunton Kitchen is hiring: Join our 5* hotel &amp; restaurant! *housing available* Maintenance Tech (FT $30hr +beneﬁts), PM Bellman ($20hr FT/PT), PM Concierge ($25hr). Dunton Kitchen: Dining Room Manager, Lead Bartender, PM Server, PM Line Cook ($25+hr), AM Prep Cook ($23+hr), Breakfas</t>
+          <t>Looking for a private part-time educator for a 14 yr old boy going into 9th grade. Mostly afternoons. Qualified educators only who can develop a creative curriculum. If interested please email jmasst@me.com or text (310)916-6132.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>May 21-27, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>$20.00-$25.00/hour; $18.00/hour; $12.16/hour; $65,000.00/year</t>
+          <t>$45,000.00-$50,000.00/year</t>
         </is>
       </c>
       <c r="D50" s="16" t="n">
-        <v>25293</v>
+        <v>45000</v>
       </c>
       <c r="E50" s="16" t="n">
-        <v>65000</v>
+        <v>50000</v>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
@@ -3510,19 +3659,19 @@
       <c r="G50" s="14" t="inlineStr"/>
       <c r="H50" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telluride Brewing Craft Kitchen and Pizza is hiring (Lawson Hill Location). Kitchen Manager: $65,000 (could increase based on experience)+Beneﬁts; Back of the House: $20-$25/hour based on experience (weekends required); Food Runner: $18/hour plus tips (weekends required); Bartender:$12.16/hour plus </t>
+          <t xml:space="preserve">Telluride Mountain School is hiring a Montessori Assistant Teacher Guide and inspire students in pre-school through kindergarten in developing their academic, social, and emotional growth. This is currently a full-time position. Salary in the $45k-50k range based on experience. To apply please send </t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>May 21-27, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>15-0000 Computer and Mathematical</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr"/>
@@ -3532,136 +3681,152 @@
       <c r="G51" s="14" t="inlineStr"/>
       <c r="H51" s="15" t="inlineStr">
         <is>
-          <t>Chief Financial Oﬃcer &amp; Manager of Information Technology San Miguel Power Association, Inc. is seeking to ﬁll a Chief Financial Oﬃcer and Manager of IT to report out of our Nucla or Ridgway oﬃce location. Please visit our website for full job details and application. www.smpa.com</t>
+          <t>Teachers Wanted West End Public Schools RE–2. located in Nucla, CO is seeking the following certified teaching positions (ATL candidates encouraged to apply) for the upcoming 26–27 school year: Kindergarten Teacher, K–12th Grade Performing Arts Teacher, Special Education Teacher/Generalist For job d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>May 21-27, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
-        </is>
-      </c>
-      <c r="C52" s="14" t="inlineStr"/>
-      <c r="D52" s="14" t="n"/>
-      <c r="E52" s="14" t="n"/>
-      <c r="F52" s="14" t="inlineStr"/>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>$30,000.00-$50,000.00/year</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G52" s="14" t="inlineStr"/>
       <c r="H52" s="15" t="inlineStr">
         <is>
-          <t>Norwood Public Schools is lookingfor a High School Volleyball Coach. Please check out the full job description at https://www.norwoodk12.org/jobs and «click here for job listings and to apply online.» We will be accepting applications on an ongoing basis until positions are ﬁlled.</t>
+          <t>Telluride Mountain School is hiring an All School Art Teacher Teach and inspire students in kindergarten through 8th grade in developing artistic skill, creative confidence, visual literacy, and habits of observation and expression. This is currently an exempt, part-time position. Salary in the $30K</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>May 21-27, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>33-0000 Protective Service</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
-          <t>$18.00/hour</t>
+          <t>$30,000.00-$35,000.00/year</t>
         </is>
       </c>
       <c r="D53" s="16" t="n">
-        <v>37440</v>
+        <v>30000</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>37440</v>
-      </c>
-      <c r="F53" s="14" t="inlineStr"/>
+        <v>35000</v>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G53" s="14" t="inlineStr"/>
       <c r="H53" s="15" t="inlineStr">
         <is>
-          <t>Teachers Wanted West End Public Schools RE–2. located in Nucla, CO is seeking the following certiﬁed teaching positions (ATL candidates encouraged to apply) for the upcoming 26–27 school year: Kindergarten Teacher, K–12th Grade SERVICES Vacation Rental Specialist Cleaning Call our team for your vaca</t>
+          <t>Telluride Mountain School is hiring a Middle School Humanities Teacher Teach and inspire students in 5th through 8th grades in developing strong reading, writing, discussion, and critical thinking skills, while deepening their understanding of history, literature, and the human experience.This is cu</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>May 21-27, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>$18.00-$23.00/hour</t>
+          <t>$26.00-$28.00/hour</t>
         </is>
       </c>
       <c r="D54" s="16" t="n">
-        <v>37440</v>
+        <v>54080</v>
       </c>
       <c r="E54" s="16" t="n">
-        <v>47840</v>
+        <v>58240</v>
       </c>
       <c r="F54" s="14" t="inlineStr"/>
       <c r="G54" s="14" t="inlineStr"/>
       <c r="H54" s="15" t="inlineStr">
         <is>
-          <t>Guest Services, Drivers, Housepersons Bear Creek Lodge is hiring for several positions: guest services, drivers, and housepersons ($18-$23/hr). Housing opportunities available. View job descriptions and apply online at telluridelodging.com/careers.</t>
+          <t>Office Admin Coldwell Banker; Hiring for Part-time Receptionist/ Office Mgr. Must be professional, friendly &amp;organized. Responsibilities: Front desk reception, office operations, agent support, &amp; marketing assistance. 20 hours/week; $26 - $28/hour. Send resume to: resume@cbdistinctive.com</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>May 21-27, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="inlineStr">
-        <is>
-          <t>$24.00-$27.00/hour; $70,000.00/year</t>
-        </is>
-      </c>
-      <c r="D55" s="16" t="n">
-        <v>49920</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>70000</v>
-      </c>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr"/>
+      <c r="D55" s="14" t="n"/>
+      <c r="E55" s="14" t="n"/>
       <c r="F55" s="14" t="inlineStr"/>
       <c r="G55" s="14" t="inlineStr"/>
       <c r="H55" s="15" t="inlineStr">
         <is>
-          <t>Scarpe is hiring! Seeking FullTime and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility. Stop by Sc</t>
+          <t>Norwood Public Schools is looking for a High School Volleyball Coach. Please check out the full job description at https://www.norwoodk12.org/jobs and «Click here for job listings and to apply online.» We will be accepting applications on an ongoing basis until positions are filled.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>May 28-June 3, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="inlineStr"/>
-      <c r="D56" s="14" t="n"/>
-      <c r="E56" s="14" t="n"/>
+          <t>33-0000 Protective Service</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>$20.00-$25.00/hour; $18.00/hour; $12.16/hour; $65,000.00/year; $80,000.00/year; $100,000.00/year; $158,000.00/year</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="n">
+        <v>25293</v>
+      </c>
+      <c r="E56" s="16" t="n">
+        <v>158000</v>
+      </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3670,19 +3835,19 @@
       <c r="G56" s="14" t="inlineStr"/>
       <c r="H56" s="15" t="inlineStr">
         <is>
-          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top benefits and pay DOE. Email resume to: telluridesuper@gmail.com</t>
+          <t>Telluride Brewing Craft Kitchen and Pizza is hiring (Lawson Hill Location). Kitchen Manager: $65,000 (could increase based on experience)+Benefits; Back of the House: $20-$25/hour based on experience (weekends required); Food Runner: $18/hour plus tips (weekends required); Bartender: $12.16/hour plu</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
-          <t>May 28-June 3, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>13-0000 Business and Financial Operations</t>
+          <t>41-0000 Sales and Related</t>
         </is>
       </c>
       <c r="C57" s="14" t="inlineStr"/>
@@ -3692,161 +3857,161 @@
       <c r="G57" s="14" t="inlineStr"/>
       <c r="H57" s="15" t="inlineStr">
         <is>
-          <t>Wedding &amp; Special-Events Coordinator Telluride Ski &amp; Golf is seeking a detail-oriented, energetic Wedding &amp; Special Events Coordinator to join our team! For full details on compensation, benefits, and to apply, please visit www. tellurideskiresort.com/employment or reach out to Rae Perry at rperry@t</t>
+          <t>Retail P/T, 20 hrs to start. Committed, hard working team player wanted for our busy retail shoppe in town. Prefer year-round commitment. Send resume and brief letter of interest to: info@eftoyshoppe.com</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>May 28-June 3, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>15-0000 Computer and Mathematical</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="inlineStr"/>
-      <c r="D58" s="14" t="n"/>
-      <c r="E58" s="14" t="n"/>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>$25.00/hour</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E58" s="16" t="n">
+        <v>52000</v>
+      </c>
       <c r="F58" s="14" t="inlineStr"/>
       <c r="G58" s="14" t="inlineStr"/>
       <c r="H58" s="15" t="inlineStr">
         <is>
-          <t>Chief Financial Officer &amp; Manager of Information Technology San Miguel Power Association, Inc. is seeking to fill a Chief Financial Officer and Manager of IT to report out of our Nucla or Ridgway office location. Please visit our website for full job details and application. www.smpa.com</t>
+          <t>The Telluride Toggery is hiring! Join our fun and motivated sales team at Telluride’s longest running clothing store. Full-time salesperson positions are now available starting at $25/hr. Apply in person at 109 East Colorado Ave or email: wendy@thetelluridetoggery.com</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="14" t="inlineStr">
         <is>
-          <t>May 28-June 3, 2026</t>
+          <t>April 30-May 6, 2026</t>
         </is>
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>17-0000 Architecture and Engineering</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="inlineStr">
-        <is>
-          <t>$24.00-$26.00/hour; $20.00-$22.50/hour; $24.00-$34.00/hour; $19.06-$20.00/hour; $19.50-$21.00/hour; $22.00-$24.00/hour; $22.95/hour; $19.82/hour; $30.00/hour; $22.28/hour; $13.50/hour; $11.79/hour</t>
-        </is>
-      </c>
-      <c r="D59" s="16" t="n">
-        <v>24523</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>70720</v>
-      </c>
+          <t>Other or not stated</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr"/>
+      <c r="D59" s="14" t="n"/>
+      <c r="E59" s="14" t="n"/>
       <c r="F59" s="14" t="inlineStr"/>
-      <c r="G59" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G59" s="14" t="inlineStr"/>
       <c r="H59" s="15" t="inlineStr">
         <is>
-          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* We›re Hiring: Night Auditor (Season- al/$24-$26/hr), Front Desk Agent ($22.95/hr), Reservations Agent ($20-$22.50/hr), Bell/Valet (Seasonal/$19.82/hr + tips), Engineer ($25 $30/hr), Concierge (Seasonal/$22.28/hr), Room Attendant (Seasonal/Piece Rate, $24</t>
+          <t>any neighbor or potentially affected property owner who, for any reason, has not received a copy of this notice, it would be appreciated if you would inform them of this public hearing. 4/30 COL-000119</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>May 28-June 3, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>23-0000 Legal</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr"/>
       <c r="D60" s="14" t="n"/>
       <c r="E60" s="14" t="n"/>
-      <c r="F60" s="14" t="inlineStr"/>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G60" s="14" t="inlineStr"/>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>Assistant General Manager Telluride Conference Center is seeking said Evidence of Debt secured by the Deed of Trust, plus attorneys’ fees, the expenses of sale and other items allowed by law, and will issue to the purchaser a Certificate of Purchase, all as provided by law. First Publication 5/21/20</t>
+          <t>Top Telluride GC seeks experienced superintendent. Top beneﬁts and pay. DOE. Email resume to: telluridesuper@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="14" t="inlineStr">
         <is>
-          <t>May 28-June 3, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
-        </is>
-      </c>
-      <c r="C61" s="14" t="inlineStr"/>
-      <c r="D61" s="14" t="n"/>
-      <c r="E61" s="14" t="n"/>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>$50,000.00-$60,000.00/year</t>
+        </is>
+      </c>
+      <c r="D61" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>60000</v>
+      </c>
       <c r="F61" s="14" t="inlineStr"/>
       <c r="G61" s="14" t="inlineStr"/>
       <c r="H61" s="15" t="inlineStr">
         <is>
-          <t>Norwood Public Schools is looking for a High School Volleyball Coach. Please check out the full job description at https://www.nor- woodk12.org/jobs and «click here for job listings and to apply online.» We will be accepting applications on an ongoing basis until positions are filled.</t>
+          <t>Front Desk Administrator (FT) Luxury real estate oﬃce seeking professional front desk support. Duties include greeting clients, answering phones, and assisting advisors. Req: Experience, strong communication &amp; organization skills. Hours: Mon–Fri | Pay: $50K–$60K+ beneﬁts. Please email lkropuenske@li</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>May 28-June 3, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="inlineStr">
-        <is>
-          <t>$25.00/hour; $27.00/hour</t>
-        </is>
-      </c>
-      <c r="D62" s="16" t="n">
-        <v>52000</v>
-      </c>
-      <c r="E62" s="16" t="n">
-        <v>56160</v>
-      </c>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr"/>
+      <c r="D62" s="14" t="n"/>
+      <c r="E62" s="14" t="n"/>
       <c r="F62" s="14" t="inlineStr"/>
       <c r="G62" s="14" t="inlineStr"/>
       <c r="H62" s="15" t="inlineStr">
         <is>
-          <t>Gallery Associate. The Gordon Collection is hiring! Come join our team! Looking for individuals with interest in Southwestern Native American Arts. Part-Time/ Full-Time Summer Sales Associate - Starting at $25/hour - based on hourly + Commission. YearRound Gallery Associate position to include websi</t>
+          <t>Notice to First Mortgagees Regarding Consent to First Amendment to Declaration Village Creek Condominium Association, a Colorado nonproﬁt corporation Property: Village Creek Condominiums, as established by the Condominium Declaration recorded December 23, 1987 in Book 441, page 232, Reception No. 25</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="14" t="inlineStr">
         <is>
-          <t>May 28-June 3, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>29-0000 Healthcare Practitioners and Technical</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C63" s="14" t="inlineStr">
         <is>
-          <t>$23.00-$40.00/hour; $158,000.00/year</t>
+          <t>$45,000.00-$50,000.00/year</t>
         </is>
       </c>
       <c r="D63" s="16" t="n">
-        <v>47840</v>
+        <v>45000</v>
       </c>
       <c r="E63" s="16" t="n">
-        <v>158000</v>
+        <v>50000</v>
       </c>
       <c r="F63" s="14" t="inlineStr">
         <is>
@@ -3856,84 +4021,88 @@
       <c r="G63" s="14" t="inlineStr"/>
       <c r="H63" s="15" t="inlineStr">
         <is>
-          <t>Telluride Whole Health is seeking a Medical Assistant or RN. Parttime with the potential for full-time. $23-40/hr DOE. Call 970-239-8674 to apply. � THE TELLURIDE TIMES WEEK OF MAY 28-JUNE 3, 2026 CLASSIFIEDS A39 Join our one-of-a-kind team! Open roles in Guest Services, F&amp;B, Culinary, Housekeeping,</t>
+          <t xml:space="preserve">Telluride Mountain School is hiring a Montessori Assistant Teacher Guide and inspire students in pre-school through kindergarten in developing their academic, social, and emotional growth. This is currently a full-time position. Salary in the $45k-50k range based on experience. To apply please send </t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>May 28-June 3, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="inlineStr">
-        <is>
-          <t>$18.00-$23.00/hour</t>
-        </is>
-      </c>
-      <c r="D64" s="16" t="n">
-        <v>37440</v>
-      </c>
-      <c r="E64" s="16" t="n">
-        <v>47840</v>
-      </c>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr"/>
+      <c r="D64" s="14" t="n"/>
+      <c r="E64" s="14" t="n"/>
       <c r="F64" s="14" t="inlineStr"/>
       <c r="G64" s="14" t="inlineStr"/>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>Guest Services, Drivers, Housepersons Bear Creek Lodge is hiring for several positions: guest services, drivers, and housepersons ($18-$23/hr). Housing opportunities available. View job descriptions and apply online at telluridelodging. com/careers.</t>
+          <t>Teachers Wanted West End Public Schools RE–2. located in Nucla, CO is seeking the following certiﬁed teaching positions (ATL candidates encouraged to apply) for the upcoming 26– 27 school year: Kindergarten Teacher, K–12th Grade Performing Arts Teacher, Special Education Teacher/Generalist For job d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="14" t="inlineStr">
         <is>
-          <t>May 28-June 3, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
+          <t>25-0000 Educational Instruction and Library</t>
         </is>
       </c>
       <c r="C65" s="14" t="inlineStr">
         <is>
-          <t>$24.00-$27.00/hour; $70,000.00/year</t>
+          <t>$30,000.00-$50,000.00/year</t>
         </is>
       </c>
       <c r="D65" s="16" t="n">
-        <v>49920</v>
+        <v>30000</v>
       </c>
       <c r="E65" s="16" t="n">
-        <v>70000</v>
-      </c>
-      <c r="F65" s="14" t="inlineStr"/>
+        <v>50000</v>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G65" s="14" t="inlineStr"/>
       <c r="H65" s="15" t="inlineStr">
         <is>
-          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/ hr for part-time, $60-$70k/year for full-time depending on qualifications and schedule flexibili</t>
+          <t>Telluride Mountain School is hiring an All School Art Teacher Teach and inspire students in kindergarten through 8th grade in developing artistic skill, creative conﬁdence, visual literacy, and habits of observation and expression. This is currently an exempt, parttime position. Salary in the $30K-5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>June 4-10, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
-        </is>
-      </c>
-      <c r="C66" s="14" t="inlineStr"/>
-      <c r="D66" s="14" t="n"/>
-      <c r="E66" s="14" t="n"/>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>$30,000.00-$35,000.00/year</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>35000</v>
+      </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3942,164 +4111,168 @@
       <c r="G66" s="14" t="inlineStr"/>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top benefits and pay DOE. Email resume to: telluridesuper@ gmail.com</t>
+          <t>Telluride Mountain School is hiring a Middle School Humanities Teacher Teach and inspire students in 5th through 8th grades in developing strong reading, writing, discussion, and critical thinking skills, while deepening their understanding of history, literature, and the human experience.This is cu</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="14" t="inlineStr">
         <is>
-          <t>June 4-10, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
         </is>
       </c>
       <c r="C67" s="14" t="inlineStr">
         <is>
-          <t>$65,000.00/year</t>
+          <t>$26.00-$28.00/hour</t>
         </is>
       </c>
       <c r="D67" s="16" t="n">
-        <v>65000</v>
+        <v>54080</v>
       </c>
       <c r="E67" s="16" t="n">
-        <v>65000</v>
+        <v>58240</v>
       </c>
       <c r="F67" s="14" t="inlineStr"/>
       <c r="G67" s="14" t="inlineStr"/>
       <c r="H67" s="15" t="inlineStr">
         <is>
-          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
+          <t>Oﬃce Admin Coldwell Banker; Hiring for Part-time Receptionist/Ofﬁce Mgr. Must be professional, friendly &amp;organized. Responsibilities: Front desk reception, oﬃce operations, agent support, &amp; marketing assistance. 20 hours/week; $26 - $28/hour. Send resume to: resume@cbdistinctive.com</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>June 4-10, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="inlineStr">
-        <is>
-          <t>$30.00/hour; $20.00/hour; $25.00/hour</t>
-        </is>
-      </c>
-      <c r="D68" s="16" t="n">
-        <v>41600</v>
-      </c>
-      <c r="E68" s="16" t="n">
-        <v>62400</v>
-      </c>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr"/>
+      <c r="D68" s="14" t="n"/>
+      <c r="E68" s="14" t="n"/>
       <c r="F68" s="14" t="inlineStr"/>
-      <c r="G68" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G68" s="14" t="inlineStr"/>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>Lumiere by Dunton/Dunton Kitchen is hiring: Join our 5* hotel &amp; restaurant! *housing available* Maintenance Tech (FT $30hr +benefits), PM Bellman ($20hr FT/PT), PM Concierge ($25hr). Dunton Kitchen: Dining Room Manager, Lead Bartender, PM Server, PM Line Cook ($25+hr), AM Prep Cook ($23+hr), Breakfa</t>
+          <t>Norwood Public Schools is looking for a High School Volleyball Coach. Please check out the full job description at https://www.norwoodk12.org/jobs and «click here for job listings and to apply online.» We will be accepting applications on an ongoing basis until positions are ﬁlled.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="14" t="inlineStr">
         <is>
-          <t>June 4-10, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>15-0000 Computer and Mathematical</t>
-        </is>
-      </c>
-      <c r="C69" s="14" t="inlineStr"/>
-      <c r="D69" s="14" t="n"/>
-      <c r="E69" s="14" t="n"/>
-      <c r="F69" s="14" t="inlineStr"/>
+          <t>33-0000 Protective Service</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>$30.00-$35.00/hour; $18.00/hour</t>
+        </is>
+      </c>
+      <c r="D69" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E69" s="16" t="n">
+        <v>72800</v>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G69" s="14" t="inlineStr"/>
       <c r="H69" s="15" t="inlineStr">
         <is>
-          <t>Chief Financial Officer &amp; Manager of Information Technology San Miguel Power Association, Inc. is seeking to fill a Chief Financial Officer and Manager of IT to report out of our Nucla or Ridgway office location. Please visit our website for full job details and application. www. smpa.com</t>
+          <t>Summer Program Director Fulltime Seasonal (May–October), Telluride Adaptive Sports Program (TASP) is seeking a Summer Program Director to help lead our seasonal adaptive recreation programs in the San Juan Mountains. This full-time role oversees daily operations, instructor coordination, and multida</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>June 4-10, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+          <t>35-0000 Food Preparation and Serving Related</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>$25.00/hour; $27.00/hour</t>
+          <t>$25.00-$30.00/hour; $20.00-$22.00/hour; $23.00/hour</t>
         </is>
       </c>
       <c r="D70" s="16" t="n">
-        <v>52000</v>
+        <v>41600</v>
       </c>
       <c r="E70" s="16" t="n">
-        <v>56160</v>
-      </c>
-      <c r="F70" s="14" t="inlineStr"/>
-      <c r="G70" s="14" t="inlineStr"/>
+        <v>62400</v>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>Gallery Associate. The Gordon Collection is hiring! Come join our team! Looking for individuals with interest in Southwestern Native American Arts. Part-Time/Full-Time Summer Sales Associate - Starting at $25/hour - based on hourly + Commission. Year-Round Gallery Associate position to include websi</t>
+          <t>Lumiere by Dunton: Come join our 5* hotel and restaurant! *Housing Available* Maintenance Tech FT ($25-$30hr DOE), PM Bellman $20hr FT/PT, AM Concierge $25hr FT/PT. Dunton Kitchen: Breakfast Cook $23hr+ DOE, PM Line Cook $25hr+ DOE, Dishwasher $20-$22hr, Bartender, Server, Breakfast Server. Email: f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="14" t="inlineStr">
         <is>
-          <t>June 4-10, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>29-0000 Healthcare Practitioners and Technical</t>
+          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
         </is>
       </c>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>$23.00-$40.00/hour</t>
+          <t>$18.00-$23.00/hour</t>
         </is>
       </c>
       <c r="D71" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E71" s="16" t="n">
         <v>47840</v>
       </c>
-      <c r="E71" s="16" t="n">
-        <v>83200</v>
-      </c>
-      <c r="F71" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F71" s="14" t="inlineStr"/>
       <c r="G71" s="14" t="inlineStr"/>
       <c r="H71" s="15" t="inlineStr">
         <is>
-          <t>Telluride Whole Health is seeking a Medical Assistant or RN. Parttime or full-time. $23-40/hr DOE. Call 970-239-8674 to apply.</t>
+          <t>Guest Services, Drivers, Housepersons Bear Creek Lodge is hiring for several positions: guest services, drivers, and housepersons ($18-$23/hr). Housing opportunities available. View job descriptions and apply online at telluridelodging.com/careers.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>June 4-10, 2026</t>
+          <t>May 7-13, 2026</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
@@ -4109,49 +4282,57 @@
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>$24.00-$27.00/hour; $70,000.00/year</t>
+          <t>$25.00/hour</t>
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>49920</v>
+        <v>52000</v>
       </c>
       <c r="E72" s="16" t="n">
-        <v>70000</v>
+        <v>52000</v>
       </c>
       <c r="F72" s="14" t="inlineStr"/>
       <c r="G72" s="14" t="inlineStr"/>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/ hr for part-time, $60-$70k/year for full-time depending on qualifications and schedule flexibili</t>
+          <t>The Telluride Toggery is hiring! Join our fun and motivated sales team at Telluride’s longest running clothing store. Full-time salesperson positions are now available starting at $25/hr. Apply in person at 109 East Colorado Ave or email: wendy@thetelluridetoggery.com</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="14" t="inlineStr">
         <is>
-          <t>June 4-10, 2026</t>
+          <t>May 14-20, 2026</t>
         </is>
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>53-0000 Transportation and Material Moving</t>
-        </is>
-      </c>
-      <c r="C73" s="14" t="inlineStr"/>
-      <c r="D73" s="14" t="n"/>
-      <c r="E73" s="14" t="n"/>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>$65,000.00/year</t>
+        </is>
+      </c>
+      <c r="D73" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>65000</v>
+      </c>
       <c r="F73" s="14" t="inlineStr"/>
       <c r="G73" s="14" t="inlineStr"/>
       <c r="H73" s="15" t="inlineStr">
         <is>
-          <t>Delivery Driver Blue Grouse Bread hiring delivery driver for Monday and Wednesday route. Email resume to bluegrousebread@gmail. com for more info.</t>
+          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>May 14-20, 2026</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
@@ -4161,27 +4342,27 @@
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>$65,000.00/year</t>
+          <t>$50,000.00-$60,000.00/year</t>
         </is>
       </c>
       <c r="D74" s="16" t="n">
-        <v>65000</v>
+        <v>50000</v>
       </c>
       <c r="E74" s="16" t="n">
-        <v>65000</v>
+        <v>60000</v>
       </c>
       <c r="F74" s="14" t="inlineStr"/>
       <c r="G74" s="14" t="inlineStr"/>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
+          <t>Front Desk Administrator (FT) Luxury real estate oﬃce seeking professional front desk support. Duties include greeting clients, answering phones, and assisting advisors. Req: Experience, strong communication &amp; organization skills. Hours: Mon–Fri | Pay: $50K–$60K+ beneﬁts. Please email lkropuenske@li</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>May 14-20, 2026</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
@@ -4189,9 +4370,17 @@
           <t>11-0000 Management</t>
         </is>
       </c>
-      <c r="C75" s="14" t="inlineStr"/>
-      <c r="D75" s="14" t="n"/>
-      <c r="E75" s="14" t="n"/>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>$20.00-$25.00/hour; $18.00/hour; $12.16/hour; $65,000.00/year</t>
+        </is>
+      </c>
+      <c r="D75" s="16" t="n">
+        <v>25293</v>
+      </c>
+      <c r="E75" s="16" t="n">
+        <v>65000</v>
+      </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -4200,190 +4389,178 @@
       <c r="G75" s="14" t="inlineStr"/>
       <c r="H75" s="15" t="inlineStr">
         <is>
-          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top benefits and pay DOE. Email resume to: telluridesuper@gmail.com</t>
+          <t xml:space="preserve">Telluride Brewing Craft Kitchen and Pizza is hiring (Lawson Hill Location). Kitchen Manager: $65,000 (could increase based on experience)+Beneﬁts; Back of the House: $20-$25/hour based on experience (weekends required); Food Runner: $18/hour plus tips (weekends required); Bartender:$12.16/hour plus </t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>May 14-20, 2026</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>17-0000 Architecture and Engineering</t>
-        </is>
-      </c>
-      <c r="C76" s="14" t="inlineStr">
-        <is>
-          <t>$26.00-$28.00/hour; $20.00-$22.50/hour; $25.00-$30.00/hour; $24.00-$34.00/hour; $22.00-$24.00/hour; $12.14-$14.00/hour; $12.14-$14.00/hour; $19.06/hour; $13.39/hour; $11.79/hour</t>
-        </is>
-      </c>
-      <c r="D76" s="16" t="n">
-        <v>24523</v>
-      </c>
-      <c r="E76" s="16" t="n">
-        <v>70720</v>
-      </c>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="inlineStr"/>
+      <c r="D76" s="14" t="n"/>
+      <c r="E76" s="14" t="n"/>
       <c r="F76" s="14" t="inlineStr"/>
-      <c r="G76" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G76" s="14" t="inlineStr"/>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Night Auditor (Seasonal/$26-$28/hr), Reservations Agent ($20-$22.50/hr), Engineer ($25-$30/hr), Room Attendant (Seasonal/Piece Rate, $24-$34/hr), AM/ PM Houseperson (Seasonal/$19.06/ hr), Public Area Attendant (Seasonal/$19.06/hr), Host (Seasonal/$13.39/</t>
+          <t>Notice to First Mortgagees Regarding Consent to First Amendment to Declaration Village Creek Condominium Association, a Colorado nonprofit corpora- tion Property: Village Creek Condominiums , as established by the Condominium Declaration recorded December 23, 1987 in Book 441, page 232, Reception No</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>May 14-20, 2026</t>
         </is>
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
-        </is>
-      </c>
-      <c r="C77" s="14" t="inlineStr">
-        <is>
-          <t>$15,000.00-$25,000.00/year</t>
-        </is>
-      </c>
-      <c r="D77" s="16" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E77" s="16" t="n">
-        <v>25000</v>
-      </c>
-      <c r="F77" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>15-0000 Computer and Mathematical</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="inlineStr"/>
+      <c r="D77" s="14" t="n"/>
+      <c r="E77" s="14" t="n"/>
+      <c r="F77" s="14" t="inlineStr"/>
       <c r="G77" s="14" t="inlineStr"/>
       <c r="H77" s="15" t="inlineStr">
         <is>
-          <t>Junior Nordic Director and Head Coach TSSC seeking experienced Nordic Director and Head Coach. Part time Oct-Mar. 15K-25K DOE. Email nordic@tssc.org https://tssc.org/wanted-nordicdirector/</t>
+          <t>Chief Financial Oﬃcer &amp; Manager of Information Technology San Miguel Power Association, Inc. is seeking to ﬁll a Chief Financial Oﬃcer and Manager of IT to report out of our Nucla or Ridgway oﬃce location. Please visit our website for full job details and application. www.smpa.com</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>May 14-20, 2026</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>29-0000 Healthcare Practitioners and Technical</t>
-        </is>
-      </c>
-      <c r="C78" s="14" t="inlineStr">
-        <is>
-          <t>$23.00-$40.00/hour</t>
-        </is>
-      </c>
-      <c r="D78" s="16" t="n">
-        <v>47840</v>
-      </c>
-      <c r="E78" s="16" t="n">
-        <v>83200</v>
-      </c>
-      <c r="F78" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr"/>
+      <c r="D78" s="14" t="n"/>
+      <c r="E78" s="14" t="n"/>
+      <c r="F78" s="14" t="inlineStr"/>
       <c r="G78" s="14" t="inlineStr"/>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Telluride Whole Health is seeking a Medical Assistant or RN. Part-time or full-time. $23-40/hr DOE. Call 970239-8674 to apply.</t>
+          <t>Teachers Wanted West End Public Schools RE–2. located in Nucla, CO is seeking the following certiﬁed teaching positions (ATL candidates encouraged to apply) for the upcoming 26–27 school year: –Kindergarten Teacher –K–12th Grade Performing Arts Teacher –Special Education Teacher/Generalist For job d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>May 14-20, 2026</t>
         </is>
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>29-0000 Healthcare Practitioners and Technical</t>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
         </is>
       </c>
       <c r="C79" s="14" t="inlineStr">
         <is>
-          <t>$19.00-$21.00/hour; $19.00-$20.00/hour; $50.00/hour</t>
+          <t>$25.00/hour; $27.00/hour</t>
         </is>
       </c>
       <c r="D79" s="16" t="n">
-        <v>39520</v>
+        <v>52000</v>
       </c>
       <c r="E79" s="16" t="n">
-        <v>104000</v>
+        <v>56160</v>
       </c>
       <c r="F79" s="14" t="inlineStr"/>
       <c r="G79" s="14" t="inlineStr"/>
       <c r="H79" s="15" t="inlineStr">
         <is>
-          <t>1099 Handyman/Maintenance Runner needed. $50/hr. Experience required. Send resume to vendors@avantstay.com � A46 CLASSIFIEDS THE TELLURIDE TIMES WEEK OF JUNE 18-24, 2026 NOW HIRING: Dental Assistant (Will Train) Full-Time | $19–$21/hour While previous dental or healthcare experience is preferred, we</t>
+          <t>Gallery Associate. The Gordon Collection is hiring! Come join our team! Looking for individuals with interest in Southwestern Native American Arts. Part-Time/Full-Time Summer Sales Associate - Starting at $25/hour - based on hourly + Commission. Year-Round Gallery Associate position to include websi</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>May 14-20, 2026</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
-        </is>
-      </c>
-      <c r="C80" s="14" t="inlineStr"/>
-      <c r="D80" s="14" t="n"/>
-      <c r="E80" s="14" t="n"/>
-      <c r="F80" s="14" t="inlineStr"/>
-      <c r="G80" s="14" t="inlineStr"/>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>$25.00-$30.00/hour; $20.00-$22.00/hour; $23.00/hour</t>
+        </is>
+      </c>
+      <c r="D80" s="16" t="n">
+        <v>41600</v>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>62400</v>
+      </c>
+      <c r="F80" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>Paddle Board Guide Telluride Outside is hiring a Paddle Board Guide for the summer. Please contact reservations@tellurideoutside.com.</t>
+          <t>Lumiere by Dunton: Come join our 5* hotel and restaurant! *Housing Available* Maintenance Tech FT ($25-$30hr DOE), PM Bellman $20hr FT/PT, AM Concierge $25hr PT. Dunton Kitchen: Breakfast Cook $23hr+ DOE, PM Line Cook $25hr+ DOE, Dishwasher $20-$22hr, Bartender, Server, Breakfast Server. Email: fama</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>May 14-20, 2026</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
-        </is>
-      </c>
-      <c r="C81" s="14" t="inlineStr"/>
-      <c r="D81" s="14" t="n"/>
-      <c r="E81" s="14" t="n"/>
+          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
+        </is>
+      </c>
+      <c r="C81" s="14" t="inlineStr">
+        <is>
+          <t>$18.00-$23.00/hour</t>
+        </is>
+      </c>
+      <c r="D81" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>47840</v>
+      </c>
       <c r="F81" s="14" t="inlineStr"/>
       <c r="G81" s="14" t="inlineStr"/>
       <c r="H81" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enchanted Forest Toy Shoppe is hiring! Our fast-paced, fun shoppe needs a committed and energetic person to join our team! 20 hours to start. Retail experience preferred. Yearround commitment a plus. Competitive wages and immediate start. Please send us a brief letter of interest and your resume to </t>
+          <t>Guest Services, Drivers, Housepersons Bear Creek Lodge is hiring for several positions: guest services, drivers, and housepersons ($18-$23/hr). Housing opportunities available. View job descriptions and apply online at telluridelodging.com/careers.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>May 14-20, 2026</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
@@ -4406,19 +4583,19 @@
       <c r="G82" s="14" t="inlineStr"/>
       <c r="H82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for full-time depending on qualifications and schedule flexibil- </t>
+          <t xml:space="preserve">Scarpe is hiring! Seeking FullTime and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60$70k/year for full-time depending on • Page A25 qualiﬁcations and schedule ﬂexibility. </t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>49-0000 Installation, Maintenance, and Repair</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
       <c r="C83" s="14" t="inlineStr"/>
@@ -4432,44 +4609,44 @@
       <c r="G83" s="14" t="inlineStr"/>
       <c r="H83" s="15" t="inlineStr">
         <is>
-          <t>Farmers Water Development Co. full-time, year-round Ditch Rider. Equipment/CDL preferred. Pay DOE. Send resume to farmerswdc@yahoo.com. Deadline 6/26/26</t>
+          <t>Wilson Mesa Home For Rent 3 bed/1 bath. Mountain views + wood burning stove. No drugs/alcohol. Maybe 1 cat. 6 months-1 year lease. $2900/month + electricity + trash. Call Polly 970-728-0600. Superintendent Top Telluride GC seeks experienced superintendent. Top beneﬁts and pay DOE. Email resume to: t</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>June 18-24, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>53-0000 Transportation and Material Moving</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>$22.00/hour; $33.00/hour</t>
+          <t>$65,000.00/year</t>
         </is>
       </c>
       <c r="D84" s="16" t="n">
-        <v>45760</v>
+        <v>65000</v>
       </c>
       <c r="E84" s="16" t="n">
-        <v>68640</v>
+        <v>65000</v>
       </c>
       <c r="F84" s="14" t="inlineStr"/>
       <c r="G84" s="14" t="inlineStr"/>
       <c r="H84" s="15" t="inlineStr">
         <is>
-          <t>DESTINATION SYSTEMS dba Telluride Express HIRING CDL and Non CDL Drivers LIVE IN THE MOUNTAINS. DRIVE WITH PURPOSE. GET PAID WELL. Destination Systems is NOW HIRING drivers in Telluride &amp; Mountain Village! Whether you want full-time work or just extra income a few days a week, we have flexible sched</t>
+          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
@@ -4477,25 +4654,29 @@
           <t>11-0000 Management</t>
         </is>
       </c>
-      <c r="C85" s="14" t="inlineStr"/>
-      <c r="D85" s="14" t="n"/>
-      <c r="E85" s="14" t="n"/>
-      <c r="F85" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>$50,000.00-$60,000.00/year</t>
+        </is>
+      </c>
+      <c r="D85" s="16" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F85" s="14" t="inlineStr"/>
       <c r="G85" s="14" t="inlineStr"/>
       <c r="H85" s="15" t="inlineStr">
         <is>
-          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top beneﬁts and pay DOE. Email resume to: telluridesuper@gmail.com</t>
+          <t>Front Desk Administrator (FT) Luxury real estate oﬃce seeking professional front desk support. Duties include greeting clients, answering phones, and assisting advisors. Req: Experience, strong communication &amp; organi- zation skills. Hours: Mon–Fri | Pay: $50K–$60K+ beneﬁts. Please email lkropuenske@</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
@@ -4505,66 +4686,70 @@
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>$65,000.00/year</t>
+          <t>$30.00/hour; $20.00/hour; $25.00/hour</t>
         </is>
       </c>
       <c r="D86" s="16" t="n">
-        <v>65000</v>
+        <v>41600</v>
       </c>
       <c r="E86" s="16" t="n">
-        <v>65000</v>
+        <v>62400</v>
       </c>
       <c r="F86" s="14" t="inlineStr"/>
-      <c r="G86" s="14" t="inlineStr"/>
+      <c r="G86" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
+          <t>Lumiere by Dunton/Dunton Kitchen is hiring: Join our 5* hotel &amp; restaurant! *housing available* Maintenance Tech (FT $30hr +beneﬁts), PM Bellman ($20hr FT/PT), PM Concierge ($25hr). Dunton Kitchen: Dining Room Manager, Lead Bartender, PM Server, PM Line Cook ($25+hr), AM Prep Cook ($23+hr), Breakfas</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>13-0000 Business and Financial Operations</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
       <c r="C87" s="14" t="inlineStr">
         <is>
-          <t>$26.00-$28.00/hour; $20.00-$22.50/hour; $23.00-$25.00/hour; $24.00-$34.00/hour; $22.00-$24.00/hour; $12.14-$14.00/hour; $12.14-$14.00/hour; $19.06/hour; $13.39/hour; $11.79/hour</t>
+          <t>$20.00-$25.00/hour; $18.00/hour; $12.16/hour; $65,000.00/year</t>
         </is>
       </c>
       <c r="D87" s="16" t="n">
-        <v>24523</v>
+        <v>25293</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>70720</v>
-      </c>
-      <c r="F87" s="14" t="inlineStr"/>
-      <c r="G87" s="14" t="inlineStr">
+        <v>65000</v>
+      </c>
+      <c r="F87" s="14" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="G87" s="14" t="inlineStr"/>
       <c r="H87" s="15" t="inlineStr">
         <is>
-          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Night Auditor (Seasonal/$26-$28/hr), Reservations Agent ($20- $22.50/hr), Expo - Seasonal (EXPOS)/Service Worker ($23-$25/hr), Room Attendant (Seasonal/Piece Rate, $24-$34/ hr), AM/PM Houseperson (Seasonal/$19.06/hr), Public Area Attendant (Seasonal/$19.</t>
+          <t xml:space="preserve">Telluride Brewing Craft Kitchen and Pizza is hiring (Lawson Hill Location). Kitchen Manager: $65,000 (could increase based on experience)+Beneﬁts; Back of the House: $20-$25/hour based on experience (weekends required); Food Runner: $18/hour plus tips (weekends required); Bartender:$12.16/hour plus </t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
+          <t>15-0000 Computer and Mathematical</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr"/>
@@ -4574,96 +4759,96 @@
       <c r="G88" s="14" t="inlineStr"/>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>Rainbow Preschool is seeking a loving and dedicated PT Preschool Teacher to join our nurturing early childhood education program. Experience in ECE preferred. We oﬀer a supportive, friendly work environment, opportunities for professional development and competitive pay. Please email resume to rainb</t>
+          <t>Chief Financial Oﬃcer &amp; Manager of Information Technology San Miguel Power Association, Inc. is seeking to ﬁll a Chief Financial Oﬃcer and Manager of IT to report out of our Nucla or Ridgway oﬃce location. Please visit our website for full job details and application. www.smpa.com</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>29-0000 Healthcare Practitioners and Technical</t>
-        </is>
-      </c>
-      <c r="C89" s="14" t="inlineStr">
-        <is>
-          <t>$20.00-$22.00/hour; $19.00-$20.00/hour; $19.00-$21.00/hour; $25.00/hour; $18.00/hour; $35.00/hour; $158,000.00/year</t>
-        </is>
-      </c>
-      <c r="D89" s="16" t="n">
-        <v>37440</v>
-      </c>
-      <c r="E89" s="16" t="n">
-        <v>158000</v>
-      </c>
-      <c r="F89" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G89" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="inlineStr"/>
+      <c r="D89" s="14" t="n"/>
+      <c r="E89" s="14" t="n"/>
+      <c r="F89" s="14" t="inlineStr"/>
+      <c r="G89" s="14" t="inlineStr"/>
       <c r="H89" s="15" t="inlineStr">
         <is>
-          <t>Lumiere by Dunton Come join our 5* hotel and restaurant! Housing available PM Bell PT ($20hr +tips), PM Concierge (PT $25hr +tips), Bartender ($18hr +tips or $35hr), PM Server ($18 +tips or $35hr), AM Server ($22hr +tips). Email: famaral@lumieretelluride.com ■ $75 caviar-topped tots. A day’s pay wor</t>
+          <t>Norwood Public Schools is lookingfor a High School Volleyball Coach. Please check out the full job description at https://www.norwoodk12.org/jobs and «click here for job listings and to apply online.» We will be accepting applications on an ongoing basis until positions are ﬁlled.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
-        </is>
-      </c>
-      <c r="C90" s="14" t="inlineStr"/>
-      <c r="D90" s="14" t="n"/>
-      <c r="E90" s="14" t="n"/>
+          <t>33-0000 Protective Service</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="inlineStr">
+        <is>
+          <t>$18.00/hour</t>
+        </is>
+      </c>
+      <c r="D90" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>37440</v>
+      </c>
       <c r="F90" s="14" t="inlineStr"/>
       <c r="G90" s="14" t="inlineStr"/>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>Paddle Board Guide Telluride Outside is hiring a Paddle Board Guide for the summer. Please contact reservations@tellurideoutside.com.</t>
+          <t>Teachers Wanted West End Public Schools RE–2. located in Nucla, CO is seeking the following certiﬁed teaching positions (ATL candidates encouraged to apply) for the upcoming 26–27 school year: Kindergarten Teacher, K–12th Grade SERVICES Vacation Rental Specialist Cleaning Call our team for your vaca</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
-        </is>
-      </c>
-      <c r="C91" s="14" t="inlineStr"/>
-      <c r="D91" s="14" t="n"/>
-      <c r="E91" s="14" t="n"/>
+          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
+        </is>
+      </c>
+      <c r="C91" s="14" t="inlineStr">
+        <is>
+          <t>$18.00-$23.00/hour</t>
+        </is>
+      </c>
+      <c r="D91" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>47840</v>
+      </c>
       <c r="F91" s="14" t="inlineStr"/>
       <c r="G91" s="14" t="inlineStr"/>
       <c r="H91" s="15" t="inlineStr">
         <is>
-          <t>Enchanted Forest Toy Shoppe is hiring! Our fast-paced, fun shoppe needs a committed and energetic person to join our team! 20 hours to start. Retail experience preferred. Year-round commitment a plus. Competitive wages and immediate start. Please send us a brief letter of interest and your resume to</t>
+          <t>Guest Services, Drivers, Housepersons Bear Creek Lodge is hiring for several positions: guest services, drivers, and housepersons ($18-$23/hr). Housing opportunities available. View job descriptions and apply online at telluridelodging.com/careers.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>May 21-27, 2026</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
@@ -4686,19 +4871,19 @@
       <c r="G92" s="14" t="inlineStr"/>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility.</t>
+          <t>Scarpe is hiring! Seeking FullTime and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility. Stop by Sc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>May 28-June 3, 2026</t>
         </is>
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>49-0000 Installation, Maintenance, and Repair</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
       <c r="C93" s="14" t="inlineStr"/>
@@ -4712,276 +4897,260 @@
       <c r="G93" s="14" t="inlineStr"/>
       <c r="H93" s="15" t="inlineStr">
         <is>
-          <t>Farmers Water Development Co. full-time, year-round Ditch Rider. Equipment/CDL preferred. Pay DOE. Send resume to farmerswdc@yahoo.com. Deadline 6/26/26</t>
+          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top benefits and pay DOE. Email resume to: telluridesuper@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>June 25-July 1, 2026</t>
+          <t>May 28-June 3, 2026</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>53-0000 Transportation and Material Moving</t>
-        </is>
-      </c>
-      <c r="C94" s="14" t="inlineStr">
-        <is>
-          <t>$22.00/hour; $33.00/hour</t>
-        </is>
-      </c>
-      <c r="D94" s="16" t="n">
-        <v>45760</v>
-      </c>
-      <c r="E94" s="16" t="n">
-        <v>68640</v>
-      </c>
+          <t>13-0000 Business and Financial Operations</t>
+        </is>
+      </c>
+      <c r="C94" s="14" t="inlineStr"/>
+      <c r="D94" s="14" t="n"/>
+      <c r="E94" s="14" t="n"/>
       <c r="F94" s="14" t="inlineStr"/>
       <c r="G94" s="14" t="inlineStr"/>
       <c r="H94" s="15" t="inlineStr">
         <is>
-          <t>DESTINATION SYSTEMS dba Telluride Express HIRING CDL and Non CDL Drivers LIVE IN THE MOUNTAINS. DRIVE WITH PURPOSE. GET PAID WELL. Destination Systems is NOW HIRING drivers in • Page A45 Telluride &amp; Mountain Village! Whether you want full-time work or just extra income a few days a week, we have ﬂex</t>
+          <t>Wedding &amp; Special-Events Coordinator Telluride Ski &amp; Golf is seeking a detail-oriented, energetic Wedding &amp; Special Events Coordinator to join our team! For full details on compensation, benefits, and to apply, please visit www. tellurideskiresort.com/employment or reach out to Rae Perry at rperry@t</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="14" t="inlineStr">
         <is>
-          <t>July 2-8, 2026</t>
+          <t>May 28-June 3, 2026</t>
         </is>
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>15-0000 Computer and Mathematical</t>
         </is>
       </c>
       <c r="C95" s="14" t="inlineStr"/>
       <c r="D95" s="14" t="n"/>
       <c r="E95" s="14" t="n"/>
-      <c r="F95" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F95" s="14" t="inlineStr"/>
       <c r="G95" s="14" t="inlineStr"/>
       <c r="H95" s="15" t="inlineStr">
         <is>
-          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top beneﬁts and pay DOE. Email resume to: telluridesuper@gmail.com</t>
+          <t>Chief Financial Officer &amp; Manager of Information Technology San Miguel Power Association, Inc. is seeking to fill a Chief Financial Officer and Manager of IT to report out of our Nucla or Ridgway office location. Please visit our website for full job details and application. www.smpa.com</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>July 2-8, 2026</t>
+          <t>May 28-June 3, 2026</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>17-0000 Architecture and Engineering</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>$65,000.00/year</t>
+          <t>$24.00-$26.00/hour; $20.00-$22.50/hour; $24.00-$34.00/hour; $19.06-$20.00/hour; $19.50-$21.00/hour; $22.00-$24.00/hour; $22.95/hour; $19.82/hour; $30.00/hour; $22.28/hour; $13.50/hour; $11.79/hour</t>
         </is>
       </c>
       <c r="D96" s="16" t="n">
-        <v>65000</v>
+        <v>24523</v>
       </c>
       <c r="E96" s="16" t="n">
-        <v>65000</v>
+        <v>70720</v>
       </c>
       <c r="F96" s="14" t="inlineStr"/>
-      <c r="G96" s="14" t="inlineStr"/>
+      <c r="G96" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H96" s="15" t="inlineStr">
         <is>
-          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
+          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* We›re Hiring: Night Auditor (Season- al/$24-$26/hr), Front Desk Agent ($22.95/hr), Reservations Agent ($20-$22.50/hr), Bell/Valet (Seasonal/$19.82/hr + tips), Engineer ($25 $30/hr), Concierge (Seasonal/$22.28/hr), Room Attendant (Seasonal/Piece Rate, $24</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="14" t="inlineStr">
         <is>
-          <t>July 2-8, 2026</t>
+          <t>May 28-June 3, 2026</t>
         </is>
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>29-0000 Healthcare Practitioners and Technical</t>
-        </is>
-      </c>
-      <c r="C97" s="14" t="inlineStr">
-        <is>
-          <t>$24.00-$27.00/hour; $20.00-$22.00/hour; $19.00-$21.00/hour; $19.00-$20.00/hour; $70,000.00/year</t>
-        </is>
-      </c>
-      <c r="D97" s="16" t="n">
-        <v>39520</v>
-      </c>
-      <c r="E97" s="16" t="n">
-        <v>70000</v>
-      </c>
-      <c r="F97" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>23-0000 Legal</t>
+        </is>
+      </c>
+      <c r="C97" s="14" t="inlineStr"/>
+      <c r="D97" s="14" t="n"/>
+      <c r="E97" s="14" t="n"/>
+      <c r="F97" s="14" t="inlineStr"/>
       <c r="G97" s="14" t="inlineStr"/>
       <c r="H97" s="15" t="inlineStr">
         <is>
-          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility.</t>
+          <t>Assistant General Manager Telluride Conference Center is seeking said Evidence of Debt secured by the Deed of Trust, plus attorneys’ fees, the expenses of sale and other items allowed by law, and will issue to the purchaser a Certificate of Purchase, all as provided by law. First Publication 5/21/20</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>July 2-8, 2026</t>
+          <t>May 28-June 3, 2026</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
-        </is>
-      </c>
-      <c r="C98" s="14" t="inlineStr">
-        <is>
-          <t>$20.00/hour; $25.00/hour; $18.00/hour; $35.00/hour; $22.00/hour</t>
-        </is>
-      </c>
-      <c r="D98" s="16" t="n">
-        <v>37440</v>
-      </c>
-      <c r="E98" s="16" t="n">
-        <v>72800</v>
-      </c>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="inlineStr"/>
+      <c r="D98" s="14" t="n"/>
+      <c r="E98" s="14" t="n"/>
       <c r="F98" s="14" t="inlineStr"/>
-      <c r="G98" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G98" s="14" t="inlineStr"/>
       <c r="H98" s="15" t="inlineStr">
         <is>
-          <t>Lumiere by Dunton Come join our 5* hotel and restaurant! Housing available. PM Bell PT ($20hr +tips), PM Concierge (PT $25hr +tips), Bartender ($18hr +tips or $35hr), PM Server ($18 +tips or $35hr), AM Server ($22hr +tips). Email: famaral@lumieretelluride.com</t>
+          <t>Norwood Public Schools is looking for a High School Volleyball Coach. Please check out the full job description at https://www.nor- woodk12.org/jobs and «click here for job listings and to apply online.» We will be accepting applications on an ongoing basis until positions are filled.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="14" t="inlineStr">
         <is>
-          <t>July 2-8, 2026</t>
+          <t>May 28-June 3, 2026</t>
         </is>
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
         </is>
       </c>
       <c r="C99" s="14" t="inlineStr">
         <is>
-          <t>$20.00-$22.50/hour; $24.00-$34.00/hour</t>
+          <t>$25.00/hour; $27.00/hour</t>
         </is>
       </c>
       <c r="D99" s="16" t="n">
-        <v>41600</v>
+        <v>52000</v>
       </c>
       <c r="E99" s="16" t="n">
-        <v>70720</v>
+        <v>56160</v>
       </c>
       <c r="F99" s="14" t="inlineStr"/>
-      <c r="G99" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G99" s="14" t="inlineStr"/>
       <c r="H99" s="15" t="inlineStr">
         <is>
-          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Reservations Agent ($20-$22.50/hr), Room Attendant (Seasonal/Piece Rate, $24-$34/hr). We oﬀer amazing beneﬁts and a really fun, creative and innovative work atmosphere. Season Ski Pass, Employee Meals, Employee Shuttle, Discounted Room Rates, Discounts a</t>
+          <t>Gallery Associate. The Gordon Collection is hiring! Come join our team! Looking for individuals with interest in Southwestern Native American Arts. Part-Time/ Full-Time Summer Sales Associate - Starting at $25/hour - based on hourly + Commission. YearRound Gallery Associate position to include websi</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>July 2-8, 2026</t>
+          <t>May 28-June 3, 2026</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
-        </is>
-      </c>
-      <c r="C100" s="14" t="inlineStr"/>
-      <c r="D100" s="14" t="n"/>
-      <c r="E100" s="14" t="n"/>
-      <c r="F100" s="14" t="inlineStr"/>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
+        </is>
+      </c>
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>$23.00-$40.00/hour; $18.00/hour; $158,000.00/year; $100,000.00/year</t>
+        </is>
+      </c>
+      <c r="D100" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E100" s="16" t="n">
+        <v>158000</v>
+      </c>
+      <c r="F100" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G100" s="14" t="inlineStr"/>
       <c r="H100" s="15" t="inlineStr">
         <is>
-          <t>Paddle Board Guide Telluride Outside is hiring a Paddle Board Guide for the summer. Please contact reservations@tellurideoutside.com.</t>
+          <t>Telluride Whole Health is seeking a Medical Assistant or RN. Parttime with the potential for full-time. $23-40/hr DOE. Call 970-239-8674 to apply. � THE TELLURIDE TIMES WEEK OF MAY 28-JUNE 3, 2026 CLASSIFIEDS A39 Join our one-of-a-kind team! Open roles in Guest Services, F&amp;B, Culinary, Housekeeping,</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="14" t="inlineStr">
         <is>
-          <t>July 2-8, 2026</t>
+          <t>May 28-June 3, 2026</t>
         </is>
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
-        </is>
-      </c>
-      <c r="C101" s="14" t="inlineStr"/>
-      <c r="D101" s="14" t="n"/>
-      <c r="E101" s="14" t="n"/>
+          <t>37-0000 Building and Grounds Cleaning and Maintenance</t>
+        </is>
+      </c>
+      <c r="C101" s="14" t="inlineStr">
+        <is>
+          <t>$18.00-$23.00/hour</t>
+        </is>
+      </c>
+      <c r="D101" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>47840</v>
+      </c>
       <c r="F101" s="14" t="inlineStr"/>
       <c r="G101" s="14" t="inlineStr"/>
       <c r="H101" s="15" t="inlineStr">
         <is>
-          <t>Enchanted Forest Toy Shoppe is hiring! Our fast-paced, fun shoppe needs a committed and energetic person to join our team! 20 hours to start. Retail experience preferred. Year-round commitment a plus. Competitive wages and immediate start. Please send us a brief letter of interest and your resume to</t>
+          <t>Guest Services, Drivers, Housepersons Bear Creek Lodge is hiring for several positions: guest services, drivers, and housepersons ($18-$23/hr). Housing opportunities available. View job descriptions and apply online at telluridelodging. com/careers.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>July 9-15, 2026</t>
+          <t>May 28-June 3, 2026</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>41-0000 Sales and Related</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>$65,000.00/year</t>
+          <t>$24.00-$27.00/hour; $70,000.00/year</t>
         </is>
       </c>
       <c r="D102" s="16" t="n">
-        <v>65000</v>
+        <v>49920</v>
       </c>
       <c r="E102" s="16" t="n">
-        <v>65000</v>
+        <v>70000</v>
       </c>
       <c r="F102" s="14" t="inlineStr"/>
       <c r="G102" s="14" t="inlineStr"/>
       <c r="H102" s="15" t="inlineStr">
         <is>
-          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
+          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/ hr for part-time, $60-$70k/year for full-time depending on qualifications and schedule flexibili</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="14" t="inlineStr">
         <is>
-          <t>July 9-15, 2026</t>
+          <t>June 4-10, 2026</t>
         </is>
       </c>
       <c r="B103" s="14" t="inlineStr">
@@ -5000,53 +5169,61 @@
       <c r="G103" s="14" t="inlineStr"/>
       <c r="H103" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norwood Public Schools is looking for a Director of Technology. Please check out the full job description at https://www.norwoodk12.org/jobs and “Click here for job listings and to apply online.” We will be accepting applications on an ongoing basis until positions are ﬁlled. ■ Who says a vegetable </t>
+          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top benefits and pay DOE. Email resume to: telluridesuper@ gmail.com</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>July 9-15, 2026</t>
+          <t>June 4-10, 2026</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
-        </is>
-      </c>
-      <c r="C104" s="14" t="inlineStr"/>
-      <c r="D104" s="14" t="n"/>
-      <c r="E104" s="14" t="n"/>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C104" s="14" t="inlineStr">
+        <is>
+          <t>$65,000.00/year</t>
+        </is>
+      </c>
+      <c r="D104" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E104" s="16" t="n">
+        <v>65000</v>
+      </c>
       <c r="F104" s="14" t="inlineStr"/>
       <c r="G104" s="14" t="inlineStr"/>
       <c r="H104" s="15" t="inlineStr">
         <is>
-          <t>Telluride School District R-1 Request for Proposal for Custodial Services The Telluride School District (TSD) is requesting proposals for custodial services to be performed at the following school building facilities: Telluride Elementary School; Telluride Intermediate School; and Telluride Middle/H</t>
+          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="14" t="inlineStr">
         <is>
-          <t>July 9-15, 2026</t>
+          <t>June 4-10, 2026</t>
         </is>
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>33-0000 Protective Service</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
       <c r="C105" s="14" t="inlineStr">
         <is>
-          <t>$20.00/hour; $25.00/hour; $18.00/hour; $35.00/hour</t>
+          <t>$30.00/hour; $20.00/hour; $25.00/hour</t>
         </is>
       </c>
       <c r="D105" s="16" t="n">
-        <v>37440</v>
+        <v>41600</v>
       </c>
       <c r="E105" s="16" t="n">
-        <v>72800</v>
+        <v>62400</v>
       </c>
       <c r="F105" s="14" t="inlineStr"/>
       <c r="G105" s="14" t="inlineStr">
@@ -5056,135 +5233,135 @@
       </c>
       <c r="H105" s="15" t="inlineStr">
         <is>
-          <t>Lumiere by Dunton Come join our 5* hotel and restaurant! Housing available. PM Bell PT ($20hr +tips), PM Concierge (PT $25hr +tips), Bartender ($18hr +tips or $35hr), PM Server ($18 +tips or $35hr), San Miguel County is Hiring! The following positions are full-time, yearround and include competitive</t>
+          <t>Lumiere by Dunton/Dunton Kitchen is hiring: Join our 5* hotel &amp; restaurant! *housing available* Maintenance Tech (FT $30hr +benefits), PM Bellman ($20hr FT/PT), PM Concierge ($25hr). Dunton Kitchen: Dining Room Manager, Lead Bartender, PM Server, PM Line Cook ($25+hr), AM Prep Cook ($23+hr), Breakfa</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>July 9-15, 2026</t>
+          <t>June 4-10, 2026</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
-        </is>
-      </c>
-      <c r="C106" s="14" t="inlineStr">
-        <is>
-          <t>$22.00/hour</t>
-        </is>
-      </c>
-      <c r="D106" s="16" t="n">
-        <v>45760</v>
-      </c>
-      <c r="E106" s="16" t="n">
-        <v>45760</v>
-      </c>
+          <t>15-0000 Computer and Mathematical</t>
+        </is>
+      </c>
+      <c r="C106" s="14" t="inlineStr"/>
+      <c r="D106" s="14" t="n"/>
+      <c r="E106" s="14" t="n"/>
       <c r="F106" s="14" t="inlineStr"/>
       <c r="G106" s="14" t="inlineStr"/>
       <c r="H106" s="15" t="inlineStr">
         <is>
-          <t>AM Server ($22hr +tips). Email: famaral@lumieretelluride.com</t>
+          <t>Chief Financial Officer &amp; Manager of Information Technology San Miguel Power Association, Inc. is seeking to fill a Chief Financial Officer and Manager of IT to report out of our Nucla or Ridgway office location. Please visit our website for full job details and application. www. smpa.com</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="14" t="inlineStr">
         <is>
-          <t>July 9-15, 2026</t>
+          <t>June 4-10, 2026</t>
         </is>
       </c>
       <c r="B107" s="14" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
         </is>
       </c>
       <c r="C107" s="14" t="inlineStr">
         <is>
-          <t>$20.00-$22.50/hour; $24.00-$34.00/hour</t>
+          <t>$23.00-$40.00/hour</t>
         </is>
       </c>
       <c r="D107" s="16" t="n">
-        <v>41600</v>
+        <v>47840</v>
       </c>
       <c r="E107" s="16" t="n">
-        <v>70720</v>
-      </c>
-      <c r="F107" s="14" t="inlineStr"/>
-      <c r="G107" s="14" t="inlineStr">
+        <v>83200</v>
+      </c>
+      <c r="F107" s="14" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="G107" s="14" t="inlineStr"/>
       <c r="H107" s="15" t="inlineStr">
         <is>
-          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Reservations Agent ($20-$22.50/ hr), Room Attendant (Seasonal/ Piece Rate, $24-$34/hr). We oﬀer amazing beneﬁts and a really fun, creative and innovative work atmosphere. Season Ski Pass, Employee Meals, Employee Shuttle, Discounted Room Rates, Discounts</t>
+          <t>Telluride Whole Health is seeking a Medical Assistant or RN. Parttime or full-time. $23-40/hr DOE. Call 970-239-8674 to apply.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>July 9-15, 2026</t>
+          <t>June 4-10, 2026</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
+          <t>33-0000 Protective Service</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>$24.00-$27.00/hour; $70,000.00/year</t>
+          <t>$25.00/hour; $27.00/hour; $18.00/hour; $20.00/hour</t>
         </is>
       </c>
       <c r="D108" s="16" t="n">
-        <v>49920</v>
+        <v>37440</v>
       </c>
       <c r="E108" s="16" t="n">
-        <v>70000</v>
+        <v>56160</v>
       </c>
       <c r="F108" s="14" t="inlineStr"/>
       <c r="G108" s="14" t="inlineStr"/>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/ hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility</t>
+          <t>Gallery Associate. The Gordon Collection is hiring! Come join our team! Looking for individuals with interest in Southwestern Native American Arts. Part-Time/Full-Time Summer Sales Associate - Starting at $25/hour - based on hourly + Commission. Year-Round Gallery Associate position to include websi</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="14" t="inlineStr">
         <is>
-          <t>July 9-15, 2026</t>
+          <t>June 4-10, 2026</t>
         </is>
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>43-0000 Office and Administrative Support</t>
-        </is>
-      </c>
-      <c r="C109" s="14" t="inlineStr"/>
-      <c r="D109" s="14" t="n"/>
-      <c r="E109" s="14" t="n"/>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C109" s="14" t="inlineStr">
+        <is>
+          <t>$24.00-$27.00/hour; $70,000.00/year</t>
+        </is>
+      </c>
+      <c r="D109" s="16" t="n">
+        <v>49920</v>
+      </c>
+      <c r="E109" s="16" t="n">
+        <v>70000</v>
+      </c>
       <c r="F109" s="14" t="inlineStr"/>
       <c r="G109" s="14" t="inlineStr"/>
       <c r="H109" s="15" t="inlineStr">
         <is>
-          <t>The Farmers’ Water Development Company (FWDC) has received written request to replace a lost, destroyed or wrongfully taken share certificate #887 currently issued in the name A.F. Newans M.D.,C.P.. Unless written notice of objection to the issuance of a replacement share certificate is filed with F</t>
+          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/ hr for part-time, $60-$70k/year for full-time depending on qualifications and schedule flexibili</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>July 23-29, 2026</t>
+          <t>June 4-10, 2026</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>11-0000 Management</t>
+          <t>53-0000 Transportation and Material Moving</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr"/>
@@ -5194,93 +5371,121 @@
       <c r="G110" s="14" t="inlineStr"/>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>Norwood Public Schools is looking for a Director of Technology. Please check out the full job description at https://www.norwoodk12.org/jobs and “Click here for job listings and to apply online.” We will be accepting applications on an ongoing basis until positions are ﬁlled.</t>
+          <t>Delivery Driver Blue Grouse Bread hiring delivery driver for Monday and Wednesday route. Email resume to bluegrousebread@gmail. com for more info.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="14" t="inlineStr">
         <is>
-          <t>July 23-29, 2026</t>
+          <t>June 11-17, 2026</t>
         </is>
       </c>
       <c r="B111" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
-        </is>
-      </c>
-      <c r="C111" s="14" t="inlineStr"/>
-      <c r="D111" s="14" t="n"/>
-      <c r="E111" s="14" t="n"/>
-      <c r="F111" s="14" t="inlineStr"/>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C111" s="14" t="inlineStr">
+        <is>
+          <t>$18.00/hour; $20.00/hour</t>
+        </is>
+      </c>
+      <c r="D111" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E111" s="16" t="n">
+        <v>41600</v>
+      </c>
+      <c r="F111" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G111" s="14" t="inlineStr"/>
       <c r="H111" s="15" t="inlineStr">
         <is>
-          <t>Norwood Public Schools is seeking a 3rd Grade Teacher. Please check out the full job description at https://www.norwoodk12.org/ jobs and “Click here for job listings and to apply online.” We will be ac- cepting applications on an ongoing basis until positions are ﬁlled.</t>
+          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top beneﬁts and pay DOE. Email resume to: telluridesuper@gmail.com WE ARE HIRING! THE DOG HOUSE tELLURIDE If you love dogs of all shapes, sizes, and personalities, join us at The Dog House! This job is fun, but it’s also hard work. Yo</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>July 23-29, 2026</t>
+          <t>June 11-17, 2026</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
-        </is>
-      </c>
-      <c r="C112" s="14" t="inlineStr"/>
-      <c r="D112" s="14" t="n"/>
-      <c r="E112" s="14" t="n"/>
-      <c r="F112" s="14" t="inlineStr"/>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
+        </is>
+      </c>
+      <c r="C112" s="14" t="inlineStr">
+        <is>
+          <t>$23.00-$40.00/hour</t>
+        </is>
+      </c>
+      <c r="D112" s="16" t="n">
+        <v>47840</v>
+      </c>
+      <c r="E112" s="16" t="n">
+        <v>83200</v>
+      </c>
+      <c r="F112" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G112" s="14" t="inlineStr"/>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>Rainbow Preschool is seeking a loving and dedicated PT Preschool Teacher to join our nurturing early childhood education program. Experience in ECE preferred. We oﬀer a supportive, friendly work environment, opportunities for professional development and com- petitive pay. Please email resume to rai</t>
+          <t>Telluride Whole Health is seeking a Medical Assistant or RN. Parttime or full-time. $23-40/hr DOE. Call 970-239-8674 to apply.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="14" t="inlineStr">
         <is>
-          <t>July 23-29, 2026</t>
+          <t>June 11-17, 2026</t>
         </is>
       </c>
       <c r="B113" s="14" t="inlineStr">
         <is>
-          <t>33-0000 Protective Service</t>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
         </is>
       </c>
       <c r="C113" s="14" t="inlineStr">
         <is>
-          <t>$24.00-$27.00/hour; $20.00-$22.00/hour; $70,000.00/year</t>
+          <t>$26.00-$28.00/hour; $24.00-$34.00/hour; $19.06-$20.00/hour; $19.50-$21.00/hour; $19.00-$21.00/hour; $19.00-$20.00/hour; $11.79/hour</t>
         </is>
       </c>
       <c r="D113" s="16" t="n">
-        <v>41600</v>
+        <v>24523</v>
       </c>
       <c r="E113" s="16" t="n">
-        <v>70000</v>
+        <v>70720</v>
       </c>
       <c r="F113" s="14" t="inlineStr"/>
-      <c r="G113" s="14" t="inlineStr"/>
+      <c r="G113" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="H113" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scarpe is hiring! Seeking year-round Full-Time and PartTime Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for fulltime depending on qualiﬁcations and schedule ﬂexibility. </t>
+          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* We’re Hiring: Night Auditor (Seasonal/$26-$28/hr), Room Attendant (Seasonal/Piece Rate, $24-$34/hr), AM/PM Houseperson (Seasonal/$19.06- 20/hr), Public Area Attendant (Seasonal/$19.50-$21/hr), Server/Bartender (Seasonal/$11.79/ hr + tips), Barista (Seaso</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>July 23-29, 2026</t>
+          <t>June 11-17, 2026</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
+          <t>39-0000 Personal Care and Service</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr"/>
@@ -5290,158 +5495,162 @@
       <c r="G114" s="14" t="inlineStr"/>
       <c r="H114" s="15" t="inlineStr">
         <is>
-          <t>Excellent Second Level Oﬃce Suite For Lease / 119 W Colorado Private Oﬃces, Conference Room, Reception Area, Kitchen &amp; Bath, Plus One Dedicated Parking Spot. Immediately available. Inquire at 970-729-1577. Blue Grouse Bread Hiring delivery driver. Fun folks, free bread, beneﬁts after 1 yr. Email res</t>
+          <t>Paddle Board Guide Telluride Outside is hiring a Paddle Board Guide for the summer. Please contact reservations@tellurideoutside.com.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="14" t="inlineStr">
         <is>
-          <t>July 23-29, 2026</t>
+          <t>June 11-17, 2026</t>
         </is>
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>35-0000 Food Preparation and Serving Related</t>
-        </is>
-      </c>
-      <c r="C115" s="14" t="inlineStr">
-        <is>
-          <t>$20.00-$22.50/hour; $24.00-$34.00/hour</t>
-        </is>
-      </c>
-      <c r="D115" s="16" t="n">
-        <v>41600</v>
-      </c>
-      <c r="E115" s="16" t="n">
-        <v>70720</v>
-      </c>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C115" s="14" t="inlineStr"/>
+      <c r="D115" s="14" t="n"/>
+      <c r="E115" s="14" t="n"/>
       <c r="F115" s="14" t="inlineStr"/>
-      <c r="G115" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="G115" s="14" t="inlineStr"/>
       <c r="H115" s="15" t="inlineStr">
         <is>
-          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Reservations Agent ($20-$22.50/ hr), Room Attendant (Seasonal/ Piece Rate, $24-$34/hr). We offer amazing beneﬁts and a really fun, creative and innovative work atmosphere. Season Ski Pass, Employee Meals, Employee Shuttle, Discounted Room Rates, Discount</t>
+          <t>Enchanted Forest Toy Shoppe is hiring! Our fast-paced, fun shoppe needs a committed and energetic person to join our team! 20 hours to start. Retail experience preferred. Year-round commitment a plus. Competitive wages and immediate start. Please send us a brief letter of interest and your resume to</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>July 23-29, 2026</t>
+          <t>June 11-17, 2026</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
-        </is>
-      </c>
-      <c r="C116" s="14" t="inlineStr">
-        <is>
-          <t>$25.00/hour</t>
-        </is>
-      </c>
-      <c r="D116" s="16" t="n">
-        <v>52000</v>
-      </c>
-      <c r="E116" s="16" t="n">
-        <v>52000</v>
-      </c>
-      <c r="F116" s="14" t="inlineStr"/>
+          <t>49-0000 Installation, Maintenance, and Repair</t>
+        </is>
+      </c>
+      <c r="C116" s="14" t="inlineStr"/>
+      <c r="D116" s="14" t="n"/>
+      <c r="E116" s="14" t="n"/>
+      <c r="F116" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G116" s="14" t="inlineStr"/>
       <c r="H116" s="15" t="inlineStr">
         <is>
-          <t>The Telluride Toggery is seeking a salesperson to join our team! Come and work at Telluride’s lon- • Week of July 23-29, 2026 gest running clothing store located in the heart of downtown Telluride. Pay is based upon experience starting at $25 hour for full-time employment. Apply in person or contact</t>
+          <t>Farmers Water Development Co. full-time, year-round Ditch Rider. Equipment/CDL preferred. Pay DOE. Send resume to farmerswdc@yahoo.com. Deadline 6/26/26</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="14" t="inlineStr">
         <is>
-          <t>July 30-August 5, 2026</t>
+          <t>June 11-17, 2026</t>
         </is>
       </c>
       <c r="B117" s="14" t="inlineStr">
         <is>
-          <t>19-0000 Life, Physical, and Social Science</t>
-        </is>
-      </c>
-      <c r="C117" s="14" t="inlineStr"/>
-      <c r="D117" s="14" t="n"/>
-      <c r="E117" s="14" t="n"/>
+          <t>53-0000 Transportation and Material Moving</t>
+        </is>
+      </c>
+      <c r="C117" s="14" t="inlineStr">
+        <is>
+          <t>$22.00/hour; $33.00/hour</t>
+        </is>
+      </c>
+      <c r="D117" s="16" t="n">
+        <v>45760</v>
+      </c>
+      <c r="E117" s="16" t="n">
+        <v>68640</v>
+      </c>
       <c r="F117" s="14" t="inlineStr"/>
       <c r="G117" s="14" t="inlineStr"/>
       <c r="H117" s="15" t="inlineStr">
         <is>
-          <t>Service Planner I-V San Miguel Power Association, Inc. (SMPA) is seeking to ﬁll the position of Service Planner I-V out of our Ridgway oﬃce location. To view the complete job posting, beneﬁts, compensation, and howto apply, please visit our website www.smpa.com.</t>
+          <t>DESTINATION SYSTEMS dba Telluride Express HIRING CDL and Non CDL Drivers LIVE IN THE MOUNTAINS. DRIVE WITH PURPOSE. GET PAID WELL. Destination Systems is NOW HIRING drivers in Telluride &amp; Mountain Village! Whether you want full-time work or just extra income a few days a week, we have ﬂexible schedu</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>July 30-August 5, 2026</t>
+          <t>June 18-24, 2026</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
-        </is>
-      </c>
-      <c r="C118" s="14" t="inlineStr"/>
-      <c r="D118" s="14" t="n"/>
-      <c r="E118" s="14" t="n"/>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C118" s="14" t="inlineStr">
+        <is>
+          <t>$65,000.00/year</t>
+        </is>
+      </c>
+      <c r="D118" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E118" s="16" t="n">
+        <v>65000</v>
+      </c>
       <c r="F118" s="14" t="inlineStr"/>
       <c r="G118" s="14" t="inlineStr"/>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Norwood Public Schools is seeking a 3rd Grade Teacher. Please check out the full job description at https://www.norwoodk12.org/ jobs and “Click here for job listings and to apply online.” We will be accepting applications on an ongoing basis until positions are ﬁlled.</t>
+          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="14" t="inlineStr">
         <is>
-          <t>July 30-August 5, 2026</t>
+          <t>June 18-24, 2026</t>
         </is>
       </c>
       <c r="B119" s="14" t="inlineStr">
         <is>
-          <t>25-0000 Educational Instruction and Library</t>
+          <t>11-0000 Management</t>
         </is>
       </c>
       <c r="C119" s="14" t="inlineStr"/>
       <c r="D119" s="14" t="n"/>
       <c r="E119" s="14" t="n"/>
-      <c r="F119" s="14" t="inlineStr"/>
+      <c r="F119" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G119" s="14" t="inlineStr"/>
       <c r="H119" s="15" t="inlineStr">
         <is>
-          <t>Rainbow Preschool is seeking a loving and dedicated PT Preschool Teacher to join our nurturing early childhood education program. Experience in ECE preferred. We oﬀer a supportive, friendly work environment, opportunities for professional development and competitive pay. Please email resume to rainb</t>
+          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top benefits and pay DOE. Email resume to: telluridesuper@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>July 30-August 5, 2026</t>
+          <t>June 18-24, 2026</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>29-0000 Healthcare Practitioners and Technical</t>
+          <t>17-0000 Architecture and Engineering</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
         <is>
-          <t>$20.00-$22.50/hour; $24.00-$34.00/hour; $20.00-$22.00/hour; $19.00-$20.00/hour; $26.00/hour; $22.95/hour; $19.82/hour</t>
+          <t>$26.00-$28.00/hour; $20.00-$22.50/hour; $25.00-$30.00/hour; $24.00-$34.00/hour; $22.00-$24.00/hour; $12.14-$14.00/hour; $12.14-$14.00/hour; $19.06/hour; $13.39/hour; $11.79/hour</t>
         </is>
       </c>
       <c r="D120" s="16" t="n">
-        <v>39520</v>
+        <v>24523</v>
       </c>
       <c r="E120" s="16" t="n">
         <v>70720</v>
@@ -5454,135 +5663,139 @@
       </c>
       <c r="H120" s="15" t="inlineStr">
         <is>
-          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Reservations Agent ($20-$22.50/hr), Room Attendant (Seasonal/Piece Rate, $24-$34/hr), Banquet Captain ($23$26/hr), Front Desk Agent/Seasonal ($22.95/hr), Bell Valet/Seasonal ($19.82/hr plus tips ). We oﬀer amazing beneﬁts and a really fun, creative and i</t>
+          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Night Auditor (Seasonal/$26-$28/hr), Reservations Agent ($20-$22.50/hr), Engineer ($25-$30/hr), Room Attendant (Seasonal/Piece Rate, $24-$34/hr), AM/ PM Houseperson (Seasonal/$19.06/ hr), Public Area Attendant (Seasonal/$19.06/hr), Host (Seasonal/$13.39/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="14" t="inlineStr">
         <is>
-          <t>July 30-August 5, 2026</t>
+          <t>June 18-24, 2026</t>
         </is>
       </c>
       <c r="B121" s="14" t="inlineStr">
         <is>
-          <t>39-0000 Personal Care and Service</t>
+          <t>27-0000 Arts, Design, Entertainment, Sports, and Media</t>
         </is>
       </c>
       <c r="C121" s="14" t="inlineStr">
         <is>
-          <t>$21.00-$23.00/hour</t>
+          <t>$15,000.00-$25,000.00/year</t>
         </is>
       </c>
       <c r="D121" s="16" t="n">
-        <v>43680</v>
+        <v>15000</v>
       </c>
       <c r="E121" s="16" t="n">
-        <v>47840</v>
-      </c>
-      <c r="F121" s="14" t="inlineStr"/>
+        <v>25000</v>
+      </c>
+      <c r="F121" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G121" s="14" t="inlineStr"/>
       <c r="H121" s="15" t="inlineStr">
         <is>
-          <t>Guest Services Associate PT &amp; FT Guest Service positions available at Bear Creek Lodge. $21-$23/hour. Apply: telluridelodging.com/careers</t>
+          <t>Junior Nordic Director and Head Coach TSSC seeking experienced Nordic Director and Head Coach. Part time Oct-Mar. 15K-25K DOE. Email nordic@tssc.org https://tssc.org/wanted-nordicdirector/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>July 30-August 5, 2026</t>
+          <t>June 18-24, 2026</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>$25.00/hour</t>
+          <t>$23.00-$40.00/hour</t>
         </is>
       </c>
       <c r="D122" s="16" t="n">
-        <v>52000</v>
+        <v>47840</v>
       </c>
       <c r="E122" s="16" t="n">
-        <v>52000</v>
-      </c>
-      <c r="F122" s="14" t="inlineStr"/>
+        <v>83200</v>
+      </c>
+      <c r="F122" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="G122" s="14" t="inlineStr"/>
       <c r="H122" s="15" t="inlineStr">
         <is>
-          <t>The Telluride Toggery is seeking a salesperson to join our team! Come and work at Telluride’s longest running clothing store located in the heart of downtown Telluride. • Page A53 Pay is based upon experience starting at $25 hour for full-time employment. Apply in person or contact Wendy at (970)728</t>
+          <t>Telluride Whole Health is seeking a Medical Assistant or RN. Part-time or full-time. $23-40/hr DOE. Call 970239-8674 to apply.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="14" t="inlineStr">
         <is>
-          <t>July 30-August 5, 2026</t>
+          <t>June 18-24, 2026</t>
         </is>
       </c>
       <c r="B123" s="14" t="inlineStr">
         <is>
-          <t>41-0000 Sales and Related</t>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
         </is>
       </c>
       <c r="C123" s="14" t="inlineStr">
         <is>
-          <t>$24.00-$27.00/hour; $70,000.00/year</t>
+          <t>$19.00-$21.00/hour; $19.00-$20.00/hour; $50.00/hour; $18.00/hour</t>
         </is>
       </c>
       <c r="D123" s="16" t="n">
-        <v>49920</v>
+        <v>37440</v>
       </c>
       <c r="E123" s="16" t="n">
-        <v>70000</v>
+        <v>104000</v>
       </c>
       <c r="F123" s="14" t="inlineStr"/>
       <c r="G123" s="14" t="inlineStr"/>
       <c r="H123" s="15" t="inlineStr">
         <is>
-          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/ hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility</t>
+          <t>1099 Handyman/Maintenance Runner needed. $50/hr. Experience required. Send resume to vendors@avantstay.com � A46 CLASSIFIEDS THE TELLURIDE TIMES WEEK OF JUNE 18-24, 2026 NOW HIRING: Dental Assistant (Will Train) Full-Time | $19–$21/hour While previous dental or healthcare experience is preferred, we</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>July 30-August 5, 2026</t>
+          <t>June 18-24, 2026</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>47-0000 Construction and Extraction</t>
+          <t>39-0000 Personal Care and Service</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr"/>
       <c r="D124" s="14" t="n"/>
       <c r="E124" s="14" t="n"/>
-      <c r="F124" s="14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F124" s="14" t="inlineStr"/>
       <c r="G124" s="14" t="inlineStr"/>
       <c r="H124" s="15" t="inlineStr">
         <is>
-          <t>Machine Operator Dillsworth Technical Tree Services looking for experienced Excavator and Grapple operator. $35-$40 DOE. 716-713-2983</t>
+          <t>Paddle Board Guide Telluride Outside is hiring a Paddle Board Guide for the summer. Please contact reservations@tellurideoutside.com.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="14" t="inlineStr">
         <is>
-          <t>July 30-August 5, 2026</t>
+          <t>June 18-24, 2026</t>
         </is>
       </c>
       <c r="B125" s="14" t="inlineStr">
         <is>
-          <t>53-0000 Transportation and Material Moving</t>
+          <t>41-0000 Sales and Related</t>
         </is>
       </c>
       <c r="C125" s="14" t="inlineStr"/>
@@ -5592,12 +5805,1390 @@
       <c r="G125" s="14" t="inlineStr"/>
       <c r="H125" s="15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Enchanted Forest Toy Shoppe is hiring! Our fast-paced, fun shoppe needs a committed and energetic person to join our team! 20 hours to start. Retail experience preferred. Yearround commitment a plus. Competitive wages and immediate start. Please send us a brief letter of interest and your resume to </t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="14" t="inlineStr">
+        <is>
+          <t>June 18-24, 2026</t>
+        </is>
+      </c>
+      <c r="B126" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C126" s="14" t="inlineStr">
+        <is>
+          <t>$24.00-$27.00/hour; $70,000.00/year</t>
+        </is>
+      </c>
+      <c r="D126" s="16" t="n">
+        <v>49920</v>
+      </c>
+      <c r="E126" s="16" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F126" s="14" t="inlineStr"/>
+      <c r="G126" s="14" t="inlineStr"/>
+      <c r="H126" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for full-time depending on qualifications and schedule flexibil- </t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="14" t="inlineStr">
+        <is>
+          <t>June 18-24, 2026</t>
+        </is>
+      </c>
+      <c r="B127" s="14" t="inlineStr">
+        <is>
+          <t>49-0000 Installation, Maintenance, and Repair</t>
+        </is>
+      </c>
+      <c r="C127" s="14" t="inlineStr"/>
+      <c r="D127" s="14" t="n"/>
+      <c r="E127" s="14" t="n"/>
+      <c r="F127" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G127" s="14" t="inlineStr"/>
+      <c r="H127" s="15" t="inlineStr">
+        <is>
+          <t>Farmers Water Development Co. full-time, year-round Ditch Rider. Equipment/CDL preferred. Pay DOE. Send resume to farmerswdc@yahoo.com. Deadline 6/26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="14" t="inlineStr">
+        <is>
+          <t>June 18-24, 2026</t>
+        </is>
+      </c>
+      <c r="B128" s="14" t="inlineStr">
+        <is>
+          <t>53-0000 Transportation and Material Moving</t>
+        </is>
+      </c>
+      <c r="C128" s="14" t="inlineStr">
+        <is>
+          <t>$22.00/hour; $33.00/hour</t>
+        </is>
+      </c>
+      <c r="D128" s="16" t="n">
+        <v>45760</v>
+      </c>
+      <c r="E128" s="16" t="n">
+        <v>68640</v>
+      </c>
+      <c r="F128" s="14" t="inlineStr"/>
+      <c r="G128" s="14" t="inlineStr"/>
+      <c r="H128" s="15" t="inlineStr">
+        <is>
+          <t>DESTINATION SYSTEMS dba Telluride Express HIRING CDL and Non CDL Drivers LIVE IN THE MOUNTAINS. DRIVE WITH PURPOSE. GET PAID WELL. Destination Systems is NOW HIRING drivers in Telluride &amp; Mountain Village! Whether you want full-time work or just extra income a few days a week, we have flexible sched</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B129" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C129" s="14" t="inlineStr"/>
+      <c r="D129" s="14" t="n"/>
+      <c r="E129" s="14" t="n"/>
+      <c r="F129" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G129" s="14" t="inlineStr"/>
+      <c r="H129" s="15" t="inlineStr">
+        <is>
+          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top beneﬁts and pay DOE. Email resume to: telluridesuper@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B130" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C130" s="14" t="inlineStr">
+        <is>
+          <t>$65,000.00/year</t>
+        </is>
+      </c>
+      <c r="D130" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E130" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="F130" s="14" t="inlineStr"/>
+      <c r="G130" s="14" t="inlineStr"/>
+      <c r="H130" s="15" t="inlineStr">
+        <is>
+          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B131" s="14" t="inlineStr">
+        <is>
+          <t>13-0000 Business and Financial Operations</t>
+        </is>
+      </c>
+      <c r="C131" s="14" t="inlineStr">
+        <is>
+          <t>$26.00-$28.00/hour; $20.00-$22.50/hour; $23.00-$25.00/hour; $24.00-$34.00/hour; $22.00-$24.00/hour; $12.14-$14.00/hour; $12.14-$14.00/hour; $19.06/hour; $13.39/hour; $11.79/hour</t>
+        </is>
+      </c>
+      <c r="D131" s="16" t="n">
+        <v>24523</v>
+      </c>
+      <c r="E131" s="16" t="n">
+        <v>70720</v>
+      </c>
+      <c r="F131" s="14" t="inlineStr"/>
+      <c r="G131" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H131" s="15" t="inlineStr">
+        <is>
+          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Night Auditor (Seasonal/$26-$28/hr), Reservations Agent ($20- $22.50/hr), Expo - Seasonal (EXPOS)/Service Worker ($23-$25/hr), Room Attendant (Seasonal/Piece Rate, $24-$34/ hr), AM/PM Houseperson (Seasonal/$19.06/hr), Public Area Attendant (Seasonal/$19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B132" s="14" t="inlineStr">
+        <is>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C132" s="14" t="inlineStr"/>
+      <c r="D132" s="14" t="n"/>
+      <c r="E132" s="14" t="n"/>
+      <c r="F132" s="14" t="inlineStr"/>
+      <c r="G132" s="14" t="inlineStr"/>
+      <c r="H132" s="15" t="inlineStr">
+        <is>
+          <t>Rainbow Preschool is seeking a loving and dedicated PT Preschool Teacher to join our nurturing early childhood education program. Experience in ECE preferred. We oﬀer a supportive, friendly work environment, opportunities for professional development and competitive pay. Please email resume to rainb</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B133" s="14" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+      <c r="C133" s="14" t="inlineStr"/>
+      <c r="D133" s="14" t="n"/>
+      <c r="E133" s="14" t="n"/>
+      <c r="F133" s="14" t="inlineStr"/>
+      <c r="G133" s="14" t="inlineStr"/>
+      <c r="H133" s="15" t="inlineStr">
+        <is>
+          <t>Paddle Board Guide Telluride Outside is hiring a Paddle Board Guide for the summer. Please contact reservations@tellurideoutside.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B134" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C134" s="14" t="inlineStr"/>
+      <c r="D134" s="14" t="n"/>
+      <c r="E134" s="14" t="n"/>
+      <c r="F134" s="14" t="inlineStr"/>
+      <c r="G134" s="14" t="inlineStr"/>
+      <c r="H134" s="15" t="inlineStr">
+        <is>
+          <t>Enchanted Forest Toy Shoppe is hiring! Our fast-paced, fun shoppe needs a committed and energetic person to join our team! 20 hours to start. Retail experience preferred. Year-round commitment a plus. Competitive wages and immediate start. Please send us a brief letter of interest and your resume to</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B135" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C135" s="14" t="inlineStr">
+        <is>
+          <t>$24.00-$27.00/hour; $70,000.00/year</t>
+        </is>
+      </c>
+      <c r="D135" s="16" t="n">
+        <v>49920</v>
+      </c>
+      <c r="E135" s="16" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F135" s="14" t="inlineStr"/>
+      <c r="G135" s="14" t="inlineStr"/>
+      <c r="H135" s="15" t="inlineStr">
+        <is>
+          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B136" s="14" t="inlineStr">
+        <is>
+          <t>49-0000 Installation, Maintenance, and Repair</t>
+        </is>
+      </c>
+      <c r="C136" s="14" t="inlineStr"/>
+      <c r="D136" s="14" t="n"/>
+      <c r="E136" s="14" t="n"/>
+      <c r="F136" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G136" s="14" t="inlineStr"/>
+      <c r="H136" s="15" t="inlineStr">
+        <is>
+          <t>Farmers Water Development Co. full-time, year-round Ditch Rider. Equipment/CDL preferred. Pay DOE. Send resume to farmerswdc@yahoo.com. Deadline 6/26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="14" t="inlineStr">
+        <is>
+          <t>June 25-July 1, 2026</t>
+        </is>
+      </c>
+      <c r="B137" s="14" t="inlineStr">
+        <is>
+          <t>53-0000 Transportation and Material Moving</t>
+        </is>
+      </c>
+      <c r="C137" s="14" t="inlineStr">
+        <is>
+          <t>$22.00/hour; $33.00/hour</t>
+        </is>
+      </c>
+      <c r="D137" s="16" t="n">
+        <v>45760</v>
+      </c>
+      <c r="E137" s="16" t="n">
+        <v>68640</v>
+      </c>
+      <c r="F137" s="14" t="inlineStr"/>
+      <c r="G137" s="14" t="inlineStr"/>
+      <c r="H137" s="15" t="inlineStr">
+        <is>
+          <t>DESTINATION SYSTEMS dba Telluride Express HIRING CDL and Non CDL Drivers LIVE IN THE MOUNTAINS. DRIVE WITH PURPOSE. GET PAID WELL. Destination Systems is NOW HIRING drivers in • Page A45 Telluride &amp; Mountain Village! Whether you want full-time work or just extra income a few days a week, we have ﬂex</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="14" t="inlineStr">
+        <is>
+          <t>July 2-8, 2026</t>
+        </is>
+      </c>
+      <c r="B138" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C138" s="14" t="inlineStr"/>
+      <c r="D138" s="14" t="n"/>
+      <c r="E138" s="14" t="n"/>
+      <c r="F138" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G138" s="14" t="inlineStr"/>
+      <c r="H138" s="15" t="inlineStr">
+        <is>
+          <t>Superintendent Top Telluride GC seeks experienced superintendent. Top beneﬁts and pay DOE. Email resume to: telluridesuper@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="14" t="inlineStr">
+        <is>
+          <t>July 2-8, 2026</t>
+        </is>
+      </c>
+      <c r="B139" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C139" s="14" t="inlineStr">
+        <is>
+          <t>$65,000.00/year</t>
+        </is>
+      </c>
+      <c r="D139" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E139" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="F139" s="14" t="inlineStr"/>
+      <c r="G139" s="14" t="inlineStr"/>
+      <c r="H139" s="15" t="inlineStr">
+        <is>
+          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="14" t="inlineStr">
+        <is>
+          <t>July 2-8, 2026</t>
+        </is>
+      </c>
+      <c r="B140" s="14" t="inlineStr">
+        <is>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C140" s="14" t="inlineStr"/>
+      <c r="D140" s="14" t="n"/>
+      <c r="E140" s="14" t="n"/>
+      <c r="F140" s="14" t="inlineStr"/>
+      <c r="G140" s="14" t="inlineStr"/>
+      <c r="H140" s="15" t="inlineStr">
+        <is>
+          <t>Telluride School District R-1 Request for Proposal for Custodial Services The Telluride School District (TSD) is requesting proposals for custodial services to be performed at the following school building facilities: Telluride Elementary School; Telluride Intermediate School; and Telluride Middle/H</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="14" t="inlineStr">
+        <is>
+          <t>July 2-8, 2026</t>
+        </is>
+      </c>
+      <c r="B141" s="14" t="inlineStr">
+        <is>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
+        </is>
+      </c>
+      <c r="C141" s="14" t="inlineStr">
+        <is>
+          <t>$24.00-$27.00/hour; $20.00-$22.00/hour; $19.00-$21.00/hour; $19.00-$20.00/hour; $70,000.00/year</t>
+        </is>
+      </c>
+      <c r="D141" s="16" t="n">
+        <v>39520</v>
+      </c>
+      <c r="E141" s="16" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F141" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G141" s="14" t="inlineStr"/>
+      <c r="H141" s="15" t="inlineStr">
+        <is>
+          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="14" t="inlineStr">
+        <is>
+          <t>July 2-8, 2026</t>
+        </is>
+      </c>
+      <c r="B142" s="14" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="C142" s="14" t="inlineStr">
+        <is>
+          <t>$20.00/hour; $25.00/hour; $18.00/hour; $35.00/hour; $22.00/hour</t>
+        </is>
+      </c>
+      <c r="D142" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E142" s="16" t="n">
+        <v>72800</v>
+      </c>
+      <c r="F142" s="14" t="inlineStr"/>
+      <c r="G142" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H142" s="15" t="inlineStr">
+        <is>
+          <t>Lumiere by Dunton Come join our 5* hotel and restaurant! Housing available. PM Bell PT ($20hr +tips), PM Concierge (PT $25hr +tips), Bartender ($18hr +tips or $35hr), PM Server ($18 +tips or $35hr), AM Server ($22hr +tips). Email: famaral@lumieretelluride.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="14" t="inlineStr">
+        <is>
+          <t>July 2-8, 2026</t>
+        </is>
+      </c>
+      <c r="B143" s="14" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="C143" s="14" t="inlineStr">
+        <is>
+          <t>$20.00-$22.50/hour; $24.00-$34.00/hour</t>
+        </is>
+      </c>
+      <c r="D143" s="16" t="n">
+        <v>41600</v>
+      </c>
+      <c r="E143" s="16" t="n">
+        <v>70720</v>
+      </c>
+      <c r="F143" s="14" t="inlineStr"/>
+      <c r="G143" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H143" s="15" t="inlineStr">
+        <is>
+          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Reservations Agent ($20-$22.50/hr), Room Attendant (Seasonal/Piece Rate, $24-$34/hr). We oﬀer amazing beneﬁts and a really fun, creative and innovative work atmosphere. Season Ski Pass, Employee Meals, Employee Shuttle, Discounted Room Rates, Discounts a</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="14" t="inlineStr">
+        <is>
+          <t>July 2-8, 2026</t>
+        </is>
+      </c>
+      <c r="B144" s="14" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+      <c r="C144" s="14" t="inlineStr"/>
+      <c r="D144" s="14" t="n"/>
+      <c r="E144" s="14" t="n"/>
+      <c r="F144" s="14" t="inlineStr"/>
+      <c r="G144" s="14" t="inlineStr"/>
+      <c r="H144" s="15" t="inlineStr">
+        <is>
+          <t>Paddle Board Guide Telluride Outside is hiring a Paddle Board Guide for the summer. Please contact reservations@tellurideoutside.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="14" t="inlineStr">
+        <is>
+          <t>July 2-8, 2026</t>
+        </is>
+      </c>
+      <c r="B145" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C145" s="14" t="inlineStr"/>
+      <c r="D145" s="14" t="n"/>
+      <c r="E145" s="14" t="n"/>
+      <c r="F145" s="14" t="inlineStr"/>
+      <c r="G145" s="14" t="inlineStr"/>
+      <c r="H145" s="15" t="inlineStr">
+        <is>
+          <t>Enchanted Forest Toy Shoppe is hiring! Our fast-paced, fun shoppe needs a committed and energetic person to join our team! 20 hours to start. Retail experience preferred. Year-round commitment a plus. Competitive wages and immediate start. Please send us a brief letter of interest and your resume to</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="14" t="inlineStr">
+        <is>
+          <t>July 9-15, 2026</t>
+        </is>
+      </c>
+      <c r="B146" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C146" s="14" t="inlineStr">
+        <is>
+          <t>$65,000.00/year</t>
+        </is>
+      </c>
+      <c r="D146" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E146" s="16" t="n">
+        <v>65000</v>
+      </c>
+      <c r="F146" s="14" t="inlineStr"/>
+      <c r="G146" s="14" t="inlineStr"/>
+      <c r="H146" s="15" t="inlineStr">
+        <is>
+          <t>Assistant General Manager Telluride Conference Center is seeking an AGM, responsible for event coordination, scheduling, inventory, and more. Growth opportunity! $65K Email: tony@cadencehg.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="14" t="inlineStr">
+        <is>
+          <t>July 9-15, 2026</t>
+        </is>
+      </c>
+      <c r="B147" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C147" s="14" t="inlineStr"/>
+      <c r="D147" s="14" t="n"/>
+      <c r="E147" s="14" t="n"/>
+      <c r="F147" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G147" s="14" t="inlineStr"/>
+      <c r="H147" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Norwood Public Schools is looking for a Director of Technology. Please check out the full job description at https://www.norwoodk12.org/jobs and “Click here for job listings and to apply online.” We will be accepting applications on an ongoing basis until positions are ﬁlled. ■ Who says a vegetable </t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="14" t="inlineStr">
+        <is>
+          <t>July 9-15, 2026</t>
+        </is>
+      </c>
+      <c r="B148" s="14" t="inlineStr">
+        <is>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C148" s="14" t="inlineStr"/>
+      <c r="D148" s="14" t="n"/>
+      <c r="E148" s="14" t="n"/>
+      <c r="F148" s="14" t="inlineStr"/>
+      <c r="G148" s="14" t="inlineStr"/>
+      <c r="H148" s="15" t="inlineStr">
+        <is>
+          <t>Telluride School District R-1 Request for Proposal for Custodial Services The Telluride School District (TSD) is requesting proposals for custodial services to be performed at the following school building facilities: Telluride Elementary School; Telluride Intermediate School; and Telluride Middle/H</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="14" t="inlineStr">
+        <is>
+          <t>July 9-15, 2026</t>
+        </is>
+      </c>
+      <c r="B149" s="14" t="inlineStr">
+        <is>
+          <t>33-0000 Protective Service</t>
+        </is>
+      </c>
+      <c r="C149" s="14" t="inlineStr">
+        <is>
+          <t>$20.00/hour; $25.00/hour; $18.00/hour; $35.00/hour</t>
+        </is>
+      </c>
+      <c r="D149" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E149" s="16" t="n">
+        <v>72800</v>
+      </c>
+      <c r="F149" s="14" t="inlineStr"/>
+      <c r="G149" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H149" s="15" t="inlineStr">
+        <is>
+          <t>Lumiere by Dunton Come join our 5* hotel and restaurant! Housing available. PM Bell PT ($20hr +tips), PM Concierge (PT $25hr +tips), Bartender ($18hr +tips or $35hr), PM Server ($18 +tips or $35hr), San Miguel County is Hiring! The following positions are full-time, yearround and include competitive</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="14" t="inlineStr">
+        <is>
+          <t>July 9-15, 2026</t>
+        </is>
+      </c>
+      <c r="B150" s="14" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="C150" s="14" t="inlineStr">
+        <is>
+          <t>$22.00/hour</t>
+        </is>
+      </c>
+      <c r="D150" s="16" t="n">
+        <v>45760</v>
+      </c>
+      <c r="E150" s="16" t="n">
+        <v>45760</v>
+      </c>
+      <c r="F150" s="14" t="inlineStr"/>
+      <c r="G150" s="14" t="inlineStr"/>
+      <c r="H150" s="15" t="inlineStr">
+        <is>
+          <t>AM Server ($22hr +tips). Email: famaral@lumieretelluride.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="14" t="inlineStr">
+        <is>
+          <t>July 9-15, 2026</t>
+        </is>
+      </c>
+      <c r="B151" s="14" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="C151" s="14" t="inlineStr">
+        <is>
+          <t>$20.00-$22.50/hour; $24.00-$34.00/hour</t>
+        </is>
+      </c>
+      <c r="D151" s="16" t="n">
+        <v>41600</v>
+      </c>
+      <c r="E151" s="16" t="n">
+        <v>70720</v>
+      </c>
+      <c r="F151" s="14" t="inlineStr"/>
+      <c r="G151" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H151" s="15" t="inlineStr">
+        <is>
+          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Reservations Agent ($20-$22.50/ hr), Room Attendant (Seasonal/ Piece Rate, $24-$34/hr). We oﬀer amazing beneﬁts and a really fun, creative and innovative work atmosphere. Season Ski Pass, Employee Meals, Employee Shuttle, Discounted Room Rates, Discounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="14" t="inlineStr">
+        <is>
+          <t>July 9-15, 2026</t>
+        </is>
+      </c>
+      <c r="B152" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C152" s="14" t="inlineStr">
+        <is>
+          <t>$24.00-$27.00/hour; $70,000.00/year</t>
+        </is>
+      </c>
+      <c r="D152" s="16" t="n">
+        <v>49920</v>
+      </c>
+      <c r="E152" s="16" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F152" s="14" t="inlineStr"/>
+      <c r="G152" s="14" t="inlineStr"/>
+      <c r="H152" s="15" t="inlineStr">
+        <is>
+          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/ hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="14" t="inlineStr">
+        <is>
+          <t>July 9-15, 2026</t>
+        </is>
+      </c>
+      <c r="B153" s="14" t="inlineStr">
+        <is>
+          <t>43-0000 Office and Administrative Support</t>
+        </is>
+      </c>
+      <c r="C153" s="14" t="inlineStr"/>
+      <c r="D153" s="14" t="n"/>
+      <c r="E153" s="14" t="n"/>
+      <c r="F153" s="14" t="inlineStr"/>
+      <c r="G153" s="14" t="inlineStr"/>
+      <c r="H153" s="15" t="inlineStr">
+        <is>
+          <t>The Farmers’ Water Development Company (FWDC) has received written request to replace a lost, destroyed or wrongfully taken share certificate #887 currently issued in the name A.F. Newans M.D.,C.P.. Unless written notice of objection to the issuance of a replacement share certificate is filed with F</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="14" t="inlineStr">
+        <is>
+          <t>July 16-22, 2026</t>
+        </is>
+      </c>
+      <c r="B154" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C154" s="14" t="inlineStr"/>
+      <c r="D154" s="14" t="n"/>
+      <c r="E154" s="14" t="n"/>
+      <c r="F154" s="14" t="inlineStr"/>
+      <c r="G154" s="14" t="inlineStr"/>
+      <c r="H154" s="15" t="inlineStr">
+        <is>
+          <t>Norwood Public Schools is looking for a Director of Technology. Please check out the full job description at https://www.norwoodk12.org/ jobs and «Click here for job listings and to apply online.» We will be ac- cepting applications on an ongoing basis until positions are ﬁlled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="14" t="inlineStr">
+        <is>
+          <t>July 16-22, 2026</t>
+        </is>
+      </c>
+      <c r="B155" s="14" t="inlineStr">
+        <is>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C155" s="14" t="inlineStr"/>
+      <c r="D155" s="14" t="n"/>
+      <c r="E155" s="14" t="n"/>
+      <c r="F155" s="14" t="inlineStr"/>
+      <c r="G155" s="14" t="inlineStr"/>
+      <c r="H155" s="15" t="inlineStr">
+        <is>
+          <t>Rainbow Preschool is seeking a loving and dedicated PT Preschool Teacher to join our nurturing early childhood education program. Experience in ECE preferred. We oﬀer a supportive, friendly work environment, opportunities for profess ional development and competitive pay. Please email resume to rain</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="14" t="inlineStr">
+        <is>
+          <t>July 16-22, 2026</t>
+        </is>
+      </c>
+      <c r="B156" s="14" t="inlineStr">
+        <is>
+          <t>29-0000 Healthcare Practitioners and Technical</t>
+        </is>
+      </c>
+      <c r="C156" s="14" t="inlineStr">
+        <is>
+          <t>$20.00-$22.00/hour; $19.00-$20.00/hour; $25.00/hour</t>
+        </is>
+      </c>
+      <c r="D156" s="16" t="n">
+        <v>39520</v>
+      </c>
+      <c r="E156" s="16" t="n">
+        <v>52000</v>
+      </c>
+      <c r="F156" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G156" s="14" t="inlineStr"/>
+      <c r="H156" s="15" t="inlineStr">
+        <is>
+          <t>The Telluride Toggery is seeking a salesperson to join our team! Come and work at Telluride’s longest running clothing store located in the heart of downtown Telluride. Pay is based upon experience starting at $25 hour for full-time employment. Apply in person or contact Wendy at (970)728-3338 wendy</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="14" t="inlineStr">
+        <is>
+          <t>July 16-22, 2026</t>
+        </is>
+      </c>
+      <c r="B157" s="14" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="C157" s="14" t="inlineStr">
+        <is>
+          <t>$20.00/hour; $25.00/hour; $18.00/hour; $35.00/hour; $22.00/hour</t>
+        </is>
+      </c>
+      <c r="D157" s="16" t="n">
+        <v>37440</v>
+      </c>
+      <c r="E157" s="16" t="n">
+        <v>72800</v>
+      </c>
+      <c r="F157" s="14" t="inlineStr"/>
+      <c r="G157" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H157" s="15" t="inlineStr">
+        <is>
+          <t>Lumiere by Dunton Come join our 5* hotel and restaurant! Housing available. PM Bell PT ($20hr +tips), PM Concierge (PT $25hr +tips), Bartender ($18hr +tips or $35hr), PM Server ($18 +tips or $35hr), AM Server ($22hr +tips). Email: famaral@lumieretelluride.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="14" t="inlineStr">
+        <is>
+          <t>July 16-22, 2026</t>
+        </is>
+      </c>
+      <c r="B158" s="14" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="C158" s="14" t="inlineStr">
+        <is>
+          <t>$20.00-$22.50/hour; $24.00-$34.00/hour</t>
+        </is>
+      </c>
+      <c r="D158" s="16" t="n">
+        <v>41600</v>
+      </c>
+      <c r="E158" s="16" t="n">
+        <v>70720</v>
+      </c>
+      <c r="F158" s="14" t="inlineStr"/>
+      <c r="G158" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H158" s="15" t="inlineStr">
+        <is>
+          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Reservations Agent ($20-$22.50/hr), Room Attendant (Seasonal/Piece Rate, $24-$34/hr). We oﬀer amazing beneﬁts and a really fun, creative and innovative work atmosphere. Season Ski Pass, Employee Meals, Employee Shuttle, Discounted Room Rates, Discounts a</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="14" t="inlineStr">
+        <is>
+          <t>July 16-22, 2026</t>
+        </is>
+      </c>
+      <c r="B159" s="14" t="inlineStr">
+        <is>
+          <t>43-0000 Office and Administrative Support</t>
+        </is>
+      </c>
+      <c r="C159" s="14" t="inlineStr"/>
+      <c r="D159" s="14" t="n"/>
+      <c r="E159" s="14" t="n"/>
+      <c r="F159" s="14" t="inlineStr"/>
+      <c r="G159" s="14" t="inlineStr"/>
+      <c r="H159" s="15" t="inlineStr">
+        <is>
+          <t>Order Processing Specialist GoodLight Candles is looking for a highly organized, detail-oriented team member to manually process &amp; manage the lifecycle of customer orders, and provide outstanding email-based customer support. Work full-time in our Telluride oﬃce M-F. For details &amp; to apply, go to: g</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="14" t="inlineStr">
+        <is>
+          <t>July 16-22, 2026</t>
+        </is>
+      </c>
+      <c r="B160" s="14" t="inlineStr">
+        <is>
+          <t>53-0000 Transportation and Material Moving</t>
+        </is>
+      </c>
+      <c r="C160" s="14" t="inlineStr"/>
+      <c r="D160" s="14" t="n"/>
+      <c r="E160" s="14" t="n"/>
+      <c r="F160" s="14" t="inlineStr"/>
+      <c r="G160" s="14" t="inlineStr"/>
+      <c r="H160" s="15" t="inlineStr">
+        <is>
           <t>Blue Grouse Bread Hiring delivery driver. Fun folks, free bread, beneﬁts after 1 yr. Email resume to bluegrousebread@gmail.com.</t>
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" s="14" t="inlineStr">
+        <is>
+          <t>July 23-29, 2026</t>
+        </is>
+      </c>
+      <c r="B161" s="14" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="C161" s="14" t="inlineStr"/>
+      <c r="D161" s="14" t="n"/>
+      <c r="E161" s="14" t="n"/>
+      <c r="F161" s="14" t="inlineStr"/>
+      <c r="G161" s="14" t="inlineStr"/>
+      <c r="H161" s="15" t="inlineStr">
+        <is>
+          <t>Norwood Public Schools is looking for a Director of Technology. Please check out the full job description at https://www.norwoodk12.org/jobs and “Click here for job listings and to apply online.” We will be accepting applications on an ongoing basis until positions are ﬁlled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="14" t="inlineStr">
+        <is>
+          <t>July 23-29, 2026</t>
+        </is>
+      </c>
+      <c r="B162" s="14" t="inlineStr">
+        <is>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C162" s="14" t="inlineStr"/>
+      <c r="D162" s="14" t="n"/>
+      <c r="E162" s="14" t="n"/>
+      <c r="F162" s="14" t="inlineStr"/>
+      <c r="G162" s="14" t="inlineStr"/>
+      <c r="H162" s="15" t="inlineStr">
+        <is>
+          <t>Norwood Public Schools is seeking a 3rd Grade Teacher. Please check out the full job description at https://www.norwoodk12.org/ jobs and “Click here for job listings and to apply online.” We will be ac- cepting applications on an ongoing basis until positions are ﬁlled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="14" t="inlineStr">
+        <is>
+          <t>July 23-29, 2026</t>
+        </is>
+      </c>
+      <c r="B163" s="14" t="inlineStr">
+        <is>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C163" s="14" t="inlineStr"/>
+      <c r="D163" s="14" t="n"/>
+      <c r="E163" s="14" t="n"/>
+      <c r="F163" s="14" t="inlineStr"/>
+      <c r="G163" s="14" t="inlineStr"/>
+      <c r="H163" s="15" t="inlineStr">
+        <is>
+          <t>Rainbow Preschool is seeking a loving and dedicated PT Preschool Teacher to join our nurturing early childhood education program. Experience in ECE preferred. We oﬀer a supportive, friendly work environment, opportunities for professional development and com- petitive pay. Please email resume to rai</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="14" t="inlineStr">
+        <is>
+          <t>July 23-29, 2026</t>
+        </is>
+      </c>
+      <c r="B164" s="14" t="inlineStr">
+        <is>
+          <t>33-0000 Protective Service</t>
+        </is>
+      </c>
+      <c r="C164" s="14" t="inlineStr">
+        <is>
+          <t>$24.00-$27.00/hour; $20.00-$22.00/hour; $70,000.00/year</t>
+        </is>
+      </c>
+      <c r="D164" s="16" t="n">
+        <v>41600</v>
+      </c>
+      <c r="E164" s="16" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F164" s="14" t="inlineStr"/>
+      <c r="G164" s="14" t="inlineStr"/>
+      <c r="H164" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scarpe is hiring! Seeking year-round Full-Time and PartTime Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/hr for part-time, $60-$70k/year for fulltime depending on qualiﬁcations and schedule ﬂexibility. </t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="14" t="inlineStr">
+        <is>
+          <t>July 23-29, 2026</t>
+        </is>
+      </c>
+      <c r="B165" s="14" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="C165" s="14" t="inlineStr"/>
+      <c r="D165" s="14" t="n"/>
+      <c r="E165" s="14" t="n"/>
+      <c r="F165" s="14" t="inlineStr"/>
+      <c r="G165" s="14" t="inlineStr"/>
+      <c r="H165" s="15" t="inlineStr">
+        <is>
+          <t>Excellent Second Level Oﬃce Suite For Lease / 119 W Colorado Private Oﬃces, Conference Room, Reception Area, Kitchen &amp; Bath, Plus One Dedicated Parking Spot. Immediately available. Inquire at 970-729-1577. Blue Grouse Bread Hiring delivery driver. Fun folks, free bread, beneﬁts after 1 yr. Email res</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="14" t="inlineStr">
+        <is>
+          <t>July 23-29, 2026</t>
+        </is>
+      </c>
+      <c r="B166" s="14" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="C166" s="14" t="inlineStr">
+        <is>
+          <t>$20.00-$22.50/hour; $24.00-$34.00/hour</t>
+        </is>
+      </c>
+      <c r="D166" s="16" t="n">
+        <v>41600</v>
+      </c>
+      <c r="E166" s="16" t="n">
+        <v>70720</v>
+      </c>
+      <c r="F166" s="14" t="inlineStr"/>
+      <c r="G166" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H166" s="15" t="inlineStr">
+        <is>
+          <t>Mountain Lodge is hiring! *HOUSING AVAILABLE* Reservations Agent ($20-$22.50/ hr), Room Attendant (Seasonal/ Piece Rate, $24-$34/hr). We offer amazing beneﬁts and a really fun, creative and innovative work atmosphere. Season Ski Pass, Employee Meals, Employee Shuttle, Discounted Room Rates, Discount</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="14" t="inlineStr">
+        <is>
+          <t>July 23-29, 2026</t>
+        </is>
+      </c>
+      <c r="B167" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C167" s="14" t="inlineStr">
+        <is>
+          <t>$25.00/hour</t>
+        </is>
+      </c>
+      <c r="D167" s="16" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E167" s="16" t="n">
+        <v>52000</v>
+      </c>
+      <c r="F167" s="14" t="inlineStr"/>
+      <c r="G167" s="14" t="inlineStr"/>
+      <c r="H167" s="15" t="inlineStr">
+        <is>
+          <t>The Telluride Toggery is seeking a salesperson to join our team! Come and work at Telluride’s lon- • Week of July 23-29, 2026 gest running clothing store located in the heart of downtown Telluride. Pay is based upon experience starting at $25 hour for full-time employment. Apply in person or contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="14" t="inlineStr">
+        <is>
+          <t>July 30-August 5, 2026</t>
+        </is>
+      </c>
+      <c r="B168" s="14" t="inlineStr">
+        <is>
+          <t>19-0000 Life, Physical, and Social Science</t>
+        </is>
+      </c>
+      <c r="C168" s="14" t="inlineStr"/>
+      <c r="D168" s="14" t="n"/>
+      <c r="E168" s="14" t="n"/>
+      <c r="F168" s="14" t="inlineStr"/>
+      <c r="G168" s="14" t="inlineStr"/>
+      <c r="H168" s="15" t="inlineStr">
+        <is>
+          <t>Service Planner I-V San Miguel Power Association, Inc. (SMPA) is seeking to ﬁll the position of Service Planner I-V out of our Ridgway oﬃce location. To view the complete job posting, beneﬁts, compensation, and howto apply, please visit our website www.smpa.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="14" t="inlineStr">
+        <is>
+          <t>July 30-August 5, 2026</t>
+        </is>
+      </c>
+      <c r="B169" s="14" t="inlineStr">
+        <is>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C169" s="14" t="inlineStr"/>
+      <c r="D169" s="14" t="n"/>
+      <c r="E169" s="14" t="n"/>
+      <c r="F169" s="14" t="inlineStr"/>
+      <c r="G169" s="14" t="inlineStr"/>
+      <c r="H169" s="15" t="inlineStr">
+        <is>
+          <t>Norwood Public Schools is seeking a 3rd Grade Teacher. Please check out the full job description at https://www.norwoodk12.org/ jobs and “Click here for job listings and to apply online.” We will be accepting applications on an ongoing basis until positions are ﬁlled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="14" t="inlineStr">
+        <is>
+          <t>July 30-August 5, 2026</t>
+        </is>
+      </c>
+      <c r="B170" s="14" t="inlineStr">
+        <is>
+          <t>25-0000 Educational Instruction and Library</t>
+        </is>
+      </c>
+      <c r="C170" s="14" t="inlineStr"/>
+      <c r="D170" s="14" t="n"/>
+      <c r="E170" s="14" t="n"/>
+      <c r="F170" s="14" t="inlineStr"/>
+      <c r="G170" s="14" t="inlineStr"/>
+      <c r="H170" s="15" t="inlineStr">
+        <is>
+          <t>Rainbow Preschool is seeking a loving and dedicated PT Preschool Teacher to join our nurturing early childhood education program. Experience in ECE preferred. We oﬀer a supportive, friendly work environment, opportunities for professional development and competitive pay. Please email resume to rainb</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="14" t="inlineStr">
+        <is>
+          <t>July 30-August 5, 2026</t>
+        </is>
+      </c>
+      <c r="B171" s="14" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+      <c r="C171" s="14" t="inlineStr">
+        <is>
+          <t>$21.00-$23.00/hour</t>
+        </is>
+      </c>
+      <c r="D171" s="16" t="n">
+        <v>43680</v>
+      </c>
+      <c r="E171" s="16" t="n">
+        <v>47840</v>
+      </c>
+      <c r="F171" s="14" t="inlineStr"/>
+      <c r="G171" s="14" t="inlineStr"/>
+      <c r="H171" s="15" t="inlineStr">
+        <is>
+          <t>Guest Services Associate PT &amp; FT Guest Service positions available at Bear Creek Lodge. $21-$23/hour. Apply: telluridelodging.com/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="14" t="inlineStr">
+        <is>
+          <t>July 30-August 5, 2026</t>
+        </is>
+      </c>
+      <c r="B172" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C172" s="14" t="inlineStr">
+        <is>
+          <t>$25.00/hour</t>
+        </is>
+      </c>
+      <c r="D172" s="16" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E172" s="16" t="n">
+        <v>52000</v>
+      </c>
+      <c r="F172" s="14" t="inlineStr"/>
+      <c r="G172" s="14" t="inlineStr"/>
+      <c r="H172" s="15" t="inlineStr">
+        <is>
+          <t>The Telluride Toggery is seeking a salesperson to join our team! Come and work at Telluride’s longest running clothing store located in the heart of downtown Telluride. • Page A53 Pay is based upon experience starting at $25 hour for full-time employment. Apply in person or contact Wendy at (970)728</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="14" t="inlineStr">
+        <is>
+          <t>July 30-August 5, 2026</t>
+        </is>
+      </c>
+      <c r="B173" s="14" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="C173" s="14" t="inlineStr">
+        <is>
+          <t>$24.00-$27.00/hour; $70,000.00/year</t>
+        </is>
+      </c>
+      <c r="D173" s="16" t="n">
+        <v>49920</v>
+      </c>
+      <c r="E173" s="16" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F173" s="14" t="inlineStr"/>
+      <c r="G173" s="14" t="inlineStr"/>
+      <c r="H173" s="15" t="inlineStr">
+        <is>
+          <t>Scarpe is hiring! Seeking yearround Full-Time and Part-Time Sales Associates. Ideal candidate is highly energetic with good social skills, capable of multitasking, and has a passion for fashion. $24-$27/ hr for part-time, $60-$70k/year for full-time depending on qualiﬁcations and schedule ﬂexibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="14" t="inlineStr">
+        <is>
+          <t>July 30-August 5, 2026</t>
+        </is>
+      </c>
+      <c r="B174" s="14" t="inlineStr">
+        <is>
+          <t>47-0000 Construction and Extraction</t>
+        </is>
+      </c>
+      <c r="C174" s="14" t="inlineStr"/>
+      <c r="D174" s="14" t="n"/>
+      <c r="E174" s="14" t="n"/>
+      <c r="F174" s="14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G174" s="14" t="inlineStr"/>
+      <c r="H174" s="15" t="inlineStr">
+        <is>
+          <t>Machine Operator Dillsworth Technical Tree Services looking for experienced Excavator and Grapple operator. $35-$40 DOE. 716-713-2983</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="14" t="inlineStr">
+        <is>
+          <t>July 30-August 5, 2026</t>
+        </is>
+      </c>
+      <c r="B175" s="14" t="inlineStr">
+        <is>
+          <t>53-0000 Transportation and Material Moving</t>
+        </is>
+      </c>
+      <c r="C175" s="14" t="inlineStr"/>
+      <c r="D175" s="14" t="n"/>
+      <c r="E175" s="14" t="n"/>
+      <c r="F175" s="14" t="inlineStr"/>
+      <c r="G175" s="14" t="inlineStr"/>
+      <c r="H175" s="15" t="inlineStr">
+        <is>
+          <t>Blue Grouse Bread Hiring delivery driver. Fun folks, free bread, beneﬁts after 1 yr. Email resume to bluegrousebread@gmail.com.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="14" t="inlineStr">
+        <is>
+          <t>July 30-August 5, 2026</t>
+        </is>
+      </c>
+      <c r="B176" s="14" t="inlineStr">
+        <is>
+          <t>Other or not stated</t>
+        </is>
+      </c>
+      <c r="C176" s="14" t="inlineStr"/>
+      <c r="D176" s="14" t="n"/>
+      <c r="E176" s="14" t="n"/>
+      <c r="F176" s="14" t="inlineStr"/>
+      <c r="G176" s="14" t="inlineStr"/>
+      <c r="H176" s="15" t="inlineStr">
+        <is>
+          <t>San Miguel County District Court San Miguel County, Colorado 305 W Colorado Avenue Telluride Colorado 81435 970-369-3310</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:H125"/>
+  <autoFilter ref="A4:H176"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5633,7 +7224,7 @@
       </c>
       <c r="B3" s="18" t="inlineStr">
         <is>
-          <t>The printed classified section of six weekly Telluride Times e-editions, from the week of April 23 through the week of July 30, 2026. Three weeks were not available: May 14-20, June 11-17, and July 16-22. Ads are taken from the HELP WANTED section only.</t>
+          <t>The printed classified section of six weekly Telluride Times e-editions, covering every weekly edition from April 9 through August 5, 2026, seventeen consecutive weeks with no gaps. Ads are taken from the HELP WANTED section only.</t>
         </is>
       </c>
     </row>
@@ -5708,7 +7299,7 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>This covers twelve editions from late April through early August, which spans the quiet shoulder season and the summer peak. Winter hiring is a separate season in a resort economy and is not represented here, so these counts should not be read as an annual picture.</t>
+          <t>This covers seventeen consecutive editions from early April through early August, which spans the quiet shoulder season and the summer peak. Winter hiring is a separate season in a resort economy and is not represented here, so these counts should not be read as an annual picture.</t>
         </is>
       </c>
     </row>

--- a/assets/Housing Study/Job Market/Telluride Times print help-wanted with pay.xlsx
+++ b/assets/Housing Study/Job Market/Telluride Times print help-wanted with pay.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Advertised pay" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Every ad" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method and limits" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Telski openings" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Every ad'!$A$4:$H$176</definedName>
@@ -24,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,6 +71,11 @@
       <b val="1"/>
       <color rgb="00B98A2F"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001D5C63"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -110,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -152,6 +158,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7336,4 +7343,1180 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Telluride Ski and Golf, all open positions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>A single-day snapshot taken from the company job board on August 2, 2026. This is one employer, not the whole market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Open positions</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Year round</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>BLS SOC major group</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Open positions</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Other or not stated</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>49-0000 Installation, Maintenance, and Repair</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>43-0000 Office and Administrative Support</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>15-0000 Computer and Mathematical</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>33-0000 Protective Service</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>53-0000 Transportation and Material Moving</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Position title</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Employment type</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>BLS SOC major group</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Administrative Coordinator</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Reception</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Year Round</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>43-0000 Office and Administrative Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Allred's AM Winter Sous Chef</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Allred's Restaurant</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Food and Beverage</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Bon Vivant Operations Manager</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Bon Vivant</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Food and Beverage</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Children's Group Ski Instructor</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Children's Instruction</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Ski School</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Children's Ski &amp; Snowboard School, Rental Technician Supervisor</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Ski School</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Ski School</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Children's Ski &amp; Snowboard School, Indoor Attendant</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Ski School</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Ski School</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Clubhouse Bartender</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Clubhouse</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Golf and Members' Club</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Clubhouse Cook</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Clubhouse</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Golf and Members' Club</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Fully Certified Ski Lesson Instructor</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Ski School</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Ski School</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Other or not stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Inn at Lost Creek Front Office Manager</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Inn at Lost Creek</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Inn at Lost Creek</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Year Round</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Lift Operator I (Winter)</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Lift Operations</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Mountain Operations</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Outside Services Attendant</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Outside Services</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Golf and Members' Club</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Peaks Resort &amp; Spa Cosmetologist</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Peaks Spa</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Spa at The Peaks Resort</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Peaks Resort &amp; Spa Massage Therapist</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Peaks Spa</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Spa at The Peaks Resort</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Private Lessons Supervisor</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Ski School</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Ski School</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Retail Sales Associate - Sunshine / Guest Service Store</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Retail Warehouse Associate/Driver</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>41-0000 Sales and Related</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Senior Systems Administrator</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Information Systems</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Year Round</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>15-0000 Computer and Mathematical</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Ski Cub Instructor</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Nursery</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Ski School</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Other or not stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Ski Patrol Manager - Training</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Ski Patrol</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Mountain Operations</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Year Round</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>33-0000 Protective Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Ski Valet Attendant</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Slopeside Lockers</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Resort Services</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Snowmaker</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Snowmaking</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Mountain Operations</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>49-0000 Installation, Maintenance, and Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Snowmaking Foreman</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Snowmaking</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Mountain Operations</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Snowmaking Technician</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Snowmaking</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Mountain Operations</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>49-0000 Installation, Maintenance, and Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Spa Concierge</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Peaks Spa</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Spa at The Peaks Resort</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Year Round</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Telluride Sports Cimarron Store Manager</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Telluride Sports Gondola Plaza Store Manager</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Year Round</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Telluride Sports Peaks Store Manager</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>11-0000 Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Tomboy Tavern Backwaiter</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Tomboy Tavern</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Food and Beverage</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Other or not stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Tomboy Tavern Bartender</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Tomboy Tavern</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Food and Beverage</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Tomboy Tavern Host</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Tomboy Tavern</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Food and Beverage</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Tomboy Tavern Server</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Tomboy Tavern</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Food and Beverage</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>35-0000 Food Preparation and Serving Related</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Trail Safety Team Member</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Trail Safety</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Mountain Operations</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Other or not stated</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Vehicle Mechanic II</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Vehicle Maintenance</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Mountain Operations</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Year Round</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>49-0000 Installation, Maintenance, and Repair</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Warehouse &amp; Delivery Attendant</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>F &amp; B Admin</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Food and Beverage</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Year Round</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>39-0000 Personal Care and Service</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Zipline Driver / First Responder</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Zipline Adventures</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Zipline Adventures</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>53-0000 Transportation and Material Moving</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>